--- a/research/traditional_assets/database/data/ireland/ireland_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_electronics_general.xlsx
@@ -650,10 +650,10 @@
         <v>0.2764262834386633</v>
       </c>
       <c r="X2">
-        <v>0.117631957374651</v>
+        <v>0.1175984111423698</v>
       </c>
       <c r="Y2">
-        <v>0.1587943260640123</v>
+        <v>0.1588278722962935</v>
       </c>
       <c r="Z2">
         <v>1.751015667345005</v>
@@ -662,10 +662,10 @@
         <v>0.3297361125266657</v>
       </c>
       <c r="AB2">
-        <v>0.1112868538196259</v>
+        <v>0.1112566308440331</v>
       </c>
       <c r="AC2">
-        <v>0.2184492587070399</v>
+        <v>0.2184794816826326</v>
       </c>
       <c r="AD2">
         <v>4302</v>
@@ -787,10 +787,10 @@
         <v>0.2764262834386633</v>
       </c>
       <c r="X3">
-        <v>0.117631957374651</v>
+        <v>0.1175984111423698</v>
       </c>
       <c r="Y3">
-        <v>0.1587943260640123</v>
+        <v>0.1588278722962935</v>
       </c>
       <c r="Z3">
         <v>1.751015667345005</v>
@@ -799,10 +799,10 @@
         <v>0.3297361125266657</v>
       </c>
       <c r="AB3">
-        <v>0.1112868538196259</v>
+        <v>0.1112566308440331</v>
       </c>
       <c r="AC3">
-        <v>0.2184492587070399</v>
+        <v>0.2184794816826326</v>
       </c>
       <c r="AD3">
         <v>4302</v>
@@ -1139,49 +1139,49 @@
         <v>43.7714285714286</v>
       </c>
       <c r="F2">
-        <v>9.33149163613492</v>
+        <v>8.82812064572979</v>
       </c>
       <c r="G2">
         <v>1.20900612439827</v>
       </c>
       <c r="H2">
-        <v>1.46450078634167</v>
+        <v>1.58654251853681</v>
       </c>
       <c r="I2">
         <v>0.0990649757793604</v>
       </c>
       <c r="J2">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="K2">
         <v>42771.2</v>
       </c>
       <c r="L2">
-        <v>42051.3915555304</v>
+        <v>41716.1323653658</v>
       </c>
       <c r="M2">
         <v>46155.2338239093</v>
       </c>
       <c r="N2">
-        <v>46429.2996143995</v>
+        <v>46568.782762474</v>
       </c>
       <c r="O2">
         <v>4703.03382390926</v>
       </c>
       <c r="P2">
-        <v>5696.90805886911</v>
+        <v>6171.6503971082</v>
       </c>
       <c r="Q2">
-        <v>0.111286853819626</v>
+        <v>0.111256630844033</v>
       </c>
       <c r="R2">
-        <v>0.11090029389932</v>
+        <v>0.110675350453999</v>
       </c>
       <c r="S2">
         <v>0.0535820395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.117631957374651</v>
+        <v>0.11759841114237</v>
       </c>
       <c r="X2">
-        <v>0.119145964942902</v>
+        <v>0.119860270469697</v>
       </c>
       <c r="Y2">
         <v>1.39948467147717</v>
       </c>
       <c r="Z2">
-        <v>1.42898171515673</v>
+        <v>1.44357251976332</v>
       </c>
       <c r="AA2">
         <v>4302</v>
@@ -1236,7 +1236,7 @@
         <v>42771.2</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1113273595428975</v>
+        <v>0.1112967576199604</v>
       </c>
       <c r="C2">
-        <v>47445.70297600314</v>
+        <v>47445.95668786737</v>
       </c>
       <c r="D2">
-        <v>46126.70297600314</v>
+        <v>46126.95668786737</v>
       </c>
       <c r="E2">
         <v>-4703.033823909261</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1113273595428975</v>
+        <v>0.1112967576199604</v>
       </c>
       <c r="T2">
         <v>1.276653715063877</v>
       </c>
       <c r="U2">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.111291770739266</v>
+        <v>0.1112489570687326</v>
       </c>
       <c r="C3">
-        <v>46996.02629343116</v>
+        <v>47004.90310579629</v>
       </c>
       <c r="D3">
-        <v>46151.76863167025</v>
+        <v>46160.64544403538</v>
       </c>
       <c r="E3">
         <v>-4228.291485670168</v>
@@ -1539,37 +1539,37 @@
         <v>3064</v>
       </c>
       <c r="M3">
-        <v>27.36254216256168</v>
+        <v>26.69790288902695</v>
       </c>
       <c r="N3">
-        <v>3036.637457837438</v>
+        <v>3037.302097110973</v>
       </c>
       <c r="O3">
-        <v>379.5796822296798</v>
+        <v>379.6627621388716</v>
       </c>
       <c r="P3">
-        <v>2657.057775607759</v>
+        <v>2657.639334972102</v>
       </c>
       <c r="Q3">
-        <v>3483.057775607759</v>
+        <v>3483.639334972102</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1119065154984534</v>
+        <v>0.1118756431039752</v>
       </c>
       <c r="T3">
         <v>1.287937270626311</v>
       </c>
       <c r="U3">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>111.977899633619</v>
+        <v>114.7655683944872</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1112561819356346</v>
+        <v>0.1112011565175048</v>
       </c>
       <c r="C4">
-        <v>46546.37686746567</v>
+        <v>46563.89876876006</v>
       </c>
       <c r="D4">
-        <v>46176.86154394385</v>
+        <v>46194.38344523824</v>
       </c>
       <c r="E4">
         <v>-3753.549147431076</v>
@@ -1621,37 +1621,37 @@
         <v>3064</v>
       </c>
       <c r="M4">
-        <v>54.72508432512335</v>
+        <v>53.3958057780539</v>
       </c>
       <c r="N4">
-        <v>3009.274915674877</v>
+        <v>3010.604194221946</v>
       </c>
       <c r="O4">
-        <v>376.1593644593596</v>
+        <v>376.3255242777433</v>
       </c>
       <c r="P4">
-        <v>2633.115551215517</v>
+        <v>2634.278669944203</v>
       </c>
       <c r="Q4">
-        <v>3459.115551215517</v>
+        <v>3460.278669944203</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1124974909633064</v>
+        <v>0.1124663425774597</v>
       </c>
       <c r="T4">
         <v>1.299451102832875</v>
       </c>
       <c r="U4">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>55.98894981680951</v>
+        <v>57.38278419724361</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1112205931320031</v>
+        <v>0.111153355966277</v>
       </c>
       <c r="C5">
-        <v>46096.7547425895</v>
+        <v>46122.94378481458</v>
       </c>
       <c r="D5">
-        <v>46201.98175730677</v>
+        <v>46228.17079953186</v>
       </c>
       <c r="E5">
         <v>-3278.806809191983</v>
@@ -1703,37 +1703,37 @@
         <v>3064</v>
       </c>
       <c r="M5">
-        <v>82.08762648768501</v>
+        <v>80.09370866708083</v>
       </c>
       <c r="N5">
-        <v>2981.912373512315</v>
+        <v>2983.906291332919</v>
       </c>
       <c r="O5">
-        <v>372.7390466890394</v>
+        <v>372.9882864166149</v>
       </c>
       <c r="P5">
-        <v>2609.173326823276</v>
+        <v>2610.918004916304</v>
       </c>
       <c r="Q5">
-        <v>3435.173326823276</v>
+        <v>3436.918004916304</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1131006514892903</v>
+        <v>0.1130692214215314</v>
       </c>
       <c r="T5">
         <v>1.311202333641637</v>
       </c>
       <c r="U5">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.32596654453967</v>
+        <v>38.25518946482907</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1111850043283717</v>
+        <v>0.1111055554150492</v>
       </c>
       <c r="C6">
-        <v>45647.15996338225</v>
+        <v>45682.03826233221</v>
       </c>
       <c r="D6">
-        <v>46227.12931633862</v>
+        <v>46262.00761528858</v>
       </c>
       <c r="E6">
         <v>-2804.064470952891</v>
@@ -1785,37 +1785,37 @@
         <v>3064</v>
       </c>
       <c r="M6">
-        <v>109.4501686502467</v>
+        <v>106.7916115561078</v>
       </c>
       <c r="N6">
-        <v>2954.549831349753</v>
+        <v>2957.208388443892</v>
       </c>
       <c r="O6">
-        <v>369.3187289187192</v>
+        <v>369.6510485554865</v>
       </c>
       <c r="P6">
-        <v>2585.231102431034</v>
+        <v>2587.557339888406</v>
       </c>
       <c r="Q6">
-        <v>3411.231102431034</v>
+        <v>3413.557339888406</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1137163778595656</v>
+        <v>0.1136846602415214</v>
       </c>
       <c r="T6">
         <v>1.323198381758914</v>
       </c>
       <c r="U6">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.99447490840475</v>
+        <v>28.6913920986218</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1111494155247402</v>
+        <v>0.1110577548638215</v>
       </c>
       <c r="C7">
-        <v>45197.59257452065</v>
+        <v>45241.18231000279</v>
       </c>
       <c r="D7">
-        <v>46252.30426571611</v>
+        <v>46295.89400119826</v>
       </c>
       <c r="E7">
         <v>-2329.322132713798</v>
@@ -1867,37 +1867,37 @@
         <v>3064</v>
       </c>
       <c r="M7">
-        <v>136.8127108128084</v>
+        <v>133.4895144451347</v>
       </c>
       <c r="N7">
-        <v>2927.187289187192</v>
+        <v>2930.510485554865</v>
       </c>
       <c r="O7">
-        <v>365.898411148399</v>
+        <v>366.3138106943582</v>
       </c>
       <c r="P7">
-        <v>2561.288878038793</v>
+        <v>2564.196674860507</v>
       </c>
       <c r="Q7">
-        <v>3387.288878038793</v>
+        <v>3390.196674860507</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1143450668902677</v>
+        <v>0.114313055668248</v>
       </c>
       <c r="T7">
         <v>1.335446978257608</v>
       </c>
       <c r="U7">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.3955799267238</v>
+        <v>22.95311367889744</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1111138267211088</v>
+        <v>0.1110099543125937</v>
       </c>
       <c r="C8">
-        <v>44748.05262077885</v>
+        <v>44800.37603683486</v>
       </c>
       <c r="D8">
-        <v>46277.50665021341</v>
+        <v>46329.83006626942</v>
       </c>
       <c r="E8">
         <v>-1854.579794474706</v>
@@ -1949,37 +1949,37 @@
         <v>3064</v>
       </c>
       <c r="M8">
-        <v>164.17525297537</v>
+        <v>160.1874173341617</v>
       </c>
       <c r="N8">
-        <v>2899.82474702463</v>
+        <v>2903.812582665838</v>
       </c>
       <c r="O8">
-        <v>362.4780933780788</v>
+        <v>362.9765728332298</v>
       </c>
       <c r="P8">
-        <v>2537.346653646551</v>
+        <v>2540.836009832608</v>
       </c>
       <c r="Q8">
-        <v>3363.346653646551</v>
+        <v>3366.836009832608</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1149871322833252</v>
+        <v>0.1149548212104369</v>
       </c>
       <c r="T8">
         <v>1.347956183192445</v>
       </c>
       <c r="U8">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.66298327226984</v>
+        <v>19.12759473241454</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1110782379174773</v>
+        <v>0.1109621537613659</v>
       </c>
       <c r="C9">
-        <v>44298.54014702858</v>
+        <v>44359.61955215682</v>
       </c>
       <c r="D9">
-        <v>46302.73651470223</v>
+        <v>46363.81591983047</v>
       </c>
       <c r="E9">
         <v>-1379.837456235613</v>
@@ -2031,37 +2031,37 @@
         <v>3064</v>
       </c>
       <c r="M9">
-        <v>191.5377951379317</v>
+        <v>186.8853202231886</v>
       </c>
       <c r="N9">
-        <v>2872.462204862068</v>
+        <v>2877.114679776811</v>
       </c>
       <c r="O9">
-        <v>359.0577756077585</v>
+        <v>359.6393349721014</v>
       </c>
       <c r="P9">
-        <v>2513.404429254309</v>
+        <v>2517.47534480471</v>
       </c>
       <c r="Q9">
-        <v>3339.404429254309</v>
+        <v>3343.47534480471</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.115643005534298</v>
+        <v>0.1156103881621352</v>
       </c>
       <c r="T9">
         <v>1.36073440328717</v>
       </c>
       <c r="U9">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.99684280480272</v>
+        <v>16.39508119921246</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1110426491138459</v>
+        <v>0.1109143532101382</v>
       </c>
       <c r="C10">
-        <v>43849.05519823951</v>
+        <v>43918.9129656181</v>
       </c>
       <c r="D10">
-        <v>46327.99390415225</v>
+        <v>46397.85167153084</v>
       </c>
       <c r="E10">
         <v>-905.09511799652</v>
@@ -2113,37 +2113,37 @@
         <v>3064</v>
       </c>
       <c r="M10">
-        <v>218.9003373004934</v>
+        <v>213.5832231122156</v>
       </c>
       <c r="N10">
-        <v>2845.099662699507</v>
+        <v>2850.416776887784</v>
       </c>
       <c r="O10">
-        <v>355.6374578374383</v>
+        <v>356.302097110973</v>
       </c>
       <c r="P10">
-        <v>2489.462204862068</v>
+        <v>2494.114679776811</v>
       </c>
       <c r="Q10">
-        <v>3315.462204862068</v>
+        <v>3320.114679776811</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1163131368994223</v>
+        <v>0.1162802065693052</v>
       </c>
       <c r="T10">
         <v>1.373790410775259</v>
       </c>
       <c r="U10">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>13.99723745420238</v>
+        <v>14.3456960493109</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1110070603102144</v>
+        <v>0.1108665526589104</v>
       </c>
       <c r="C11">
-        <v>43399.59781947951</v>
+        <v>43478.25638719035</v>
       </c>
       <c r="D11">
-        <v>46353.27886363134</v>
+        <v>46431.93743134219</v>
       </c>
       <c r="E11">
         <v>-430.3527797574279</v>
@@ -2195,37 +2195,37 @@
         <v>3064</v>
       </c>
       <c r="M11">
-        <v>246.2628794630551</v>
+        <v>240.2811260012425</v>
       </c>
       <c r="N11">
-        <v>2817.737120536945</v>
+        <v>2823.718873998757</v>
       </c>
       <c r="O11">
-        <v>352.2171400671181</v>
+        <v>352.9648592498447</v>
       </c>
       <c r="P11">
-        <v>2465.519980469827</v>
+        <v>2470.754014748913</v>
       </c>
       <c r="Q11">
-        <v>3291.519980469827</v>
+        <v>3296.754014748913</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1169979964264174</v>
+        <v>0.1169647462601492</v>
       </c>
       <c r="T11">
         <v>1.387133363482866</v>
       </c>
       <c r="U11">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.44198884817989</v>
+        <v>12.75172982160969</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.110971471506583</v>
+        <v>0.1108187521076826</v>
       </c>
       <c r="C12">
-        <v>42950.16805591482</v>
+        <v>43037.64992716863</v>
       </c>
       <c r="D12">
-        <v>46378.59143830575</v>
+        <v>46466.07330955955</v>
       </c>
       <c r="E12">
         <v>44.38955848166552</v>
@@ -2277,37 +2277,37 @@
         <v>3064</v>
       </c>
       <c r="M12">
-        <v>273.6254216256168</v>
+        <v>266.9790288902695</v>
       </c>
       <c r="N12">
-        <v>2790.374578374383</v>
+        <v>2797.02097110973</v>
       </c>
       <c r="O12">
-        <v>348.7968222967979</v>
+        <v>349.6276213887163</v>
       </c>
       <c r="P12">
-        <v>2441.577756077585</v>
+        <v>2447.393349721014</v>
       </c>
       <c r="Q12">
-        <v>3267.577756077585</v>
+        <v>3273.393349721014</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1176980750540125</v>
+        <v>0.1176644979441232</v>
       </c>
       <c r="T12">
         <v>1.400772826250643</v>
       </c>
       <c r="U12">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.1977899633619</v>
+        <v>11.47655683944872</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1109358827029515</v>
+        <v>0.1107709515564548</v>
       </c>
       <c r="C13">
-        <v>42500.76595281046</v>
+        <v>42597.09369617249</v>
       </c>
       <c r="D13">
-        <v>46403.93167344047</v>
+        <v>46500.25941680251</v>
       </c>
       <c r="E13">
         <v>519.1318967207571</v>
@@ -2359,37 +2359,37 @@
         <v>3064</v>
       </c>
       <c r="M13">
-        <v>300.9879637881784</v>
+        <v>293.6769317792964</v>
       </c>
       <c r="N13">
-        <v>2763.012036211821</v>
+        <v>2770.323068220704</v>
       </c>
       <c r="O13">
-        <v>345.3765045264777</v>
+        <v>346.2903835275879</v>
       </c>
       <c r="P13">
-        <v>2417.635531685344</v>
+        <v>2424.032684693116</v>
       </c>
       <c r="Q13">
-        <v>3243.635531685344</v>
+        <v>3250.032684693116</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1184138857855985</v>
+        <v>0.1183799743850404</v>
       </c>
       <c r="T13">
         <v>1.414718793799718</v>
       </c>
       <c r="U13">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.17980905760173</v>
+        <v>10.43323349040793</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1109002938993201</v>
+        <v>0.110723151005227</v>
       </c>
       <c r="C14">
-        <v>42051.3915555304</v>
+        <v>42156.58780514741</v>
       </c>
       <c r="D14">
-        <v>46429.2996143995</v>
+        <v>46534.49586401653</v>
       </c>
       <c r="E14">
         <v>993.8742349598497</v>
@@ -2441,37 +2441,37 @@
         <v>3064</v>
       </c>
       <c r="M14">
-        <v>328.3505059507401</v>
+        <v>320.3748346683233</v>
       </c>
       <c r="N14">
-        <v>2735.64949404926</v>
+        <v>2743.625165331677</v>
       </c>
       <c r="O14">
-        <v>341.9561867561575</v>
+        <v>342.9531456664596</v>
       </c>
       <c r="P14">
-        <v>2393.693307293102</v>
+        <v>2400.672019665217</v>
       </c>
       <c r="Q14">
-        <v>3219.693307293102</v>
+        <v>3226.672019665217</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1191459649429023</v>
+        <v>0.1191117116541602</v>
       </c>
       <c r="T14">
         <v>1.428981715156726</v>
       </c>
       <c r="U14">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.331491636134919</v>
+        <v>9.56379736620727</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1109898300956886</v>
+        <v>0.1106753504539993</v>
       </c>
       <c r="C15">
-        <v>41512.88002382313</v>
+        <v>41716.13236536575</v>
       </c>
       <c r="D15">
-        <v>46365.53042093133</v>
+        <v>46568.78276247396</v>
       </c>
       <c r="E15">
         <v>1468.616573198943</v>
@@ -2523,45 +2523,45 @@
         <v>3064</v>
       </c>
       <c r="M15">
-        <v>362.5018635501208</v>
+        <v>347.0727375573503</v>
       </c>
       <c r="N15">
-        <v>2701.498136449879</v>
+        <v>2716.92726244265</v>
       </c>
       <c r="O15">
-        <v>337.6872670562349</v>
+        <v>339.6159078053312</v>
       </c>
       <c r="P15">
-        <v>2363.810869393644</v>
+        <v>2377.311354637319</v>
       </c>
       <c r="Q15">
-        <v>3189.810869393644</v>
+        <v>3203.311354637319</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1198948735061211</v>
+        <v>0.1198602704696966</v>
       </c>
       <c r="T15">
         <v>1.443572519763321</v>
       </c>
       <c r="U15">
-        <v>0.05873661666253409</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05139453957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.452370340922013</v>
+        <v>8.828120645729786</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1109638662920572</v>
+        <v>0.1108112999027715</v>
       </c>
       <c r="C16">
-        <v>41056.61150544184</v>
+        <v>41144.00695132261</v>
       </c>
       <c r="D16">
-        <v>46384.00424078914</v>
+        <v>46471.39968666991</v>
       </c>
       <c r="E16">
         <v>1943.358911438036</v>
@@ -2605,37 +2605,37 @@
         <v>3064</v>
       </c>
       <c r="M16">
-        <v>390.3866222847455</v>
+        <v>383.7402295493982</v>
       </c>
       <c r="N16">
-        <v>2673.613377715255</v>
+        <v>2680.259770450602</v>
       </c>
       <c r="O16">
-        <v>334.2016722144068</v>
+        <v>335.0324713063252</v>
       </c>
       <c r="P16">
-        <v>2339.411705500848</v>
+        <v>2345.227299144276</v>
       </c>
       <c r="Q16">
-        <v>3165.411705500848</v>
+        <v>3171.227299144276</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1206611985475544</v>
+        <v>0.1206262376297803</v>
       </c>
       <c r="T16">
         <v>1.458502645407278</v>
       </c>
       <c r="U16">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.848629602284727</v>
+        <v>7.984568111604718</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1109379024884257</v>
+        <v>0.1107766243515437</v>
       </c>
       <c r="C17">
-        <v>40600.35771429653</v>
+        <v>40694.0646302673</v>
       </c>
       <c r="D17">
-        <v>46402.49278788292</v>
+        <v>46496.19970385369</v>
       </c>
       <c r="E17">
         <v>2418.101249677127</v>
@@ -2687,37 +2687,37 @@
         <v>3064</v>
       </c>
       <c r="M17">
-        <v>418.2713810193702</v>
+        <v>411.1502459457838</v>
       </c>
       <c r="N17">
-        <v>2645.72861898063</v>
+        <v>2652.849754054216</v>
       </c>
       <c r="O17">
-        <v>330.7160773725788</v>
+        <v>331.606219256777</v>
       </c>
       <c r="P17">
-        <v>2315.012541608051</v>
+        <v>2321.243534797439</v>
       </c>
       <c r="Q17">
-        <v>3141.012541608051</v>
+        <v>3147.243534797439</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1214455547664331</v>
+        <v>0.1214102275465719</v>
       </c>
       <c r="T17">
         <v>1.473784068125211</v>
       </c>
       <c r="U17">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.32538762879908</v>
+        <v>7.452263570831072</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1109119386847943</v>
+        <v>0.1107419488003159</v>
       </c>
       <c r="C18">
-        <v>40144.11866800497</v>
+        <v>40244.14879299577</v>
       </c>
       <c r="D18">
-        <v>46420.99607983045</v>
+        <v>46521.02620482125</v>
       </c>
       <c r="E18">
         <v>2892.843587916221</v>
@@ -2769,37 +2769,37 @@
         <v>3064</v>
       </c>
       <c r="M18">
-        <v>446.1561397539949</v>
+        <v>438.5602623421694</v>
       </c>
       <c r="N18">
-        <v>2617.843860246005</v>
+        <v>2625.439737657831</v>
       </c>
       <c r="O18">
-        <v>327.2304825307506</v>
+        <v>328.1799672072289</v>
       </c>
       <c r="P18">
-        <v>2290.613377715255</v>
+        <v>2297.259770450602</v>
       </c>
       <c r="Q18">
-        <v>3116.613377715255</v>
+        <v>3123.259770450602</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1222485861333804</v>
+        <v>0.1222128838899538</v>
       </c>
       <c r="T18">
         <v>1.48942933424119</v>
       </c>
       <c r="U18">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.867550901999135</v>
+        <v>6.98649709765413</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1112132248811628</v>
+        <v>0.1109601482490881</v>
       </c>
       <c r="C19">
-        <v>39455.56627276381</v>
+        <v>39613.62316470944</v>
       </c>
       <c r="D19">
-        <v>46207.18602282838</v>
+        <v>46365.24291477401</v>
       </c>
       <c r="E19">
         <v>3367.585926155313</v>
@@ -2851,37 +2851,37 @@
         <v>3064</v>
       </c>
       <c r="M19">
-        <v>491.7962619387616</v>
+        <v>479.6903323136647</v>
       </c>
       <c r="N19">
-        <v>2572.203738061238</v>
+        <v>2584.309667686335</v>
       </c>
       <c r="O19">
-        <v>321.5254672576548</v>
+        <v>323.0387084607919</v>
       </c>
       <c r="P19">
-        <v>2250.678270803583</v>
+        <v>2261.270959225543</v>
       </c>
       <c r="Q19">
-        <v>3076.678270803583</v>
+        <v>3087.270959225543</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1230709676537481</v>
+        <v>0.1230348813500436</v>
       </c>
       <c r="T19">
         <v>1.50545159472141</v>
       </c>
       <c r="U19">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05331953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.230222222350947</v>
+        <v>6.387454141970243</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1112065110775314</v>
+        <v>0.1109403476978604</v>
       </c>
       <c r="C20">
-        <v>38985.56697872945</v>
+        <v>39152.97435528877</v>
       </c>
       <c r="D20">
-        <v>46211.92906703312</v>
+        <v>46379.33644359243</v>
       </c>
       <c r="E20">
         <v>3842.328264394405</v>
@@ -2933,37 +2933,37 @@
         <v>3064</v>
       </c>
       <c r="M20">
-        <v>520.7254538175123</v>
+        <v>507.9074106850567</v>
       </c>
       <c r="N20">
-        <v>2543.274546182488</v>
+        <v>2556.092589314943</v>
       </c>
       <c r="O20">
-        <v>317.909318272811</v>
+        <v>319.5115736643679</v>
       </c>
       <c r="P20">
-        <v>2225.365227909677</v>
+        <v>2236.581015650575</v>
       </c>
       <c r="Q20">
-        <v>3051.365227909677</v>
+        <v>3062.581015650575</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1239134072599784</v>
+        <v>0.1238769275286723</v>
       </c>
       <c r="T20">
         <v>1.52186464204261</v>
       </c>
       <c r="U20">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05331953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.884098765553673</v>
+        <v>6.032595578527452</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1114491722738999</v>
+        <v>0.1109205471466326</v>
       </c>
       <c r="C21">
-        <v>38340.00996597903</v>
+        <v>38692.33411642384</v>
       </c>
       <c r="D21">
-        <v>46041.11439252178</v>
+        <v>46393.4385429666</v>
       </c>
       <c r="E21">
         <v>4317.070602633498</v>
@@ -3015,45 +3015,45 @@
         <v>3064</v>
       </c>
       <c r="M21">
-        <v>563.1848023360772</v>
+        <v>536.1244890564489</v>
       </c>
       <c r="N21">
-        <v>2500.815197663923</v>
+        <v>2527.875510943551</v>
       </c>
       <c r="O21">
-        <v>312.6018997079904</v>
+        <v>315.9844388679439</v>
       </c>
       <c r="P21">
-        <v>2188.213297955932</v>
+        <v>2211.891072075607</v>
       </c>
       <c r="Q21">
-        <v>3014.213297955932</v>
+        <v>3037.891072075607</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1247766478441403</v>
+        <v>0.1247397649709708</v>
       </c>
       <c r="T21">
         <v>1.538682949791494</v>
       </c>
       <c r="U21">
-        <v>0.06243661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05463203957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.440487717869163</v>
+        <v>5.715090548078638</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1114555834702685</v>
+        <v>0.1110407465954048</v>
       </c>
       <c r="C22">
-        <v>37860.77176295895</v>
+        <v>38132.11658008354</v>
       </c>
       <c r="D22">
-        <v>46036.61852774081</v>
+        <v>46307.96334486539</v>
       </c>
       <c r="E22">
         <v>4791.812940872592</v>
@@ -3097,37 +3097,37 @@
         <v>3064</v>
       </c>
       <c r="M22">
-        <v>592.8261077221865</v>
+        <v>571.9374448396665</v>
       </c>
       <c r="N22">
-        <v>2471.173892277814</v>
+        <v>2492.062555160333</v>
       </c>
       <c r="O22">
-        <v>308.8967365347267</v>
+        <v>311.5078193950417</v>
       </c>
       <c r="P22">
-        <v>2162.277155743087</v>
+        <v>2180.554735765292</v>
       </c>
       <c r="Q22">
-        <v>2988.277155743087</v>
+        <v>3006.554735765292</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1256614694429063</v>
+        <v>0.1256241733493267</v>
       </c>
       <c r="T22">
         <v>1.5559217152341</v>
       </c>
       <c r="U22">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.168463331975705</v>
+        <v>5.357229234849178</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.111461994666637</v>
+        <v>0.111027946044177</v>
       </c>
       <c r="C23">
-        <v>37381.53443788581</v>
+        <v>37666.46187211644</v>
       </c>
       <c r="D23">
-        <v>46032.12354090676</v>
+        <v>46317.05097513738</v>
       </c>
       <c r="E23">
         <v>5266.555279111683</v>
@@ -3179,37 +3179,37 @@
         <v>3064</v>
       </c>
       <c r="M23">
-        <v>622.4674131082958</v>
+        <v>600.5343170816496</v>
       </c>
       <c r="N23">
-        <v>2441.532586891704</v>
+        <v>2463.46568291835</v>
       </c>
       <c r="O23">
-        <v>305.191573361463</v>
+        <v>307.9332103647938</v>
       </c>
       <c r="P23">
-        <v>2136.341013530241</v>
+        <v>2155.532472553557</v>
       </c>
       <c r="Q23">
-        <v>2962.341013530241</v>
+        <v>2981.532472553557</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1265686915884764</v>
+        <v>0.1265309718132106</v>
       </c>
       <c r="T23">
         <v>1.573596905118292</v>
       </c>
       <c r="U23">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.922346030453053</v>
+        <v>5.102123080808742</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1114684058630056</v>
+        <v>0.1110151454929493</v>
       </c>
       <c r="C24">
-        <v>36902.29799050238</v>
+        <v>37200.81073162358</v>
       </c>
       <c r="D24">
-        <v>46027.62943176242</v>
+        <v>46326.14217288362</v>
       </c>
       <c r="E24">
         <v>5741.297617350775</v>
@@ -3261,37 +3261,37 @@
         <v>3064</v>
       </c>
       <c r="M24">
-        <v>652.108718494405</v>
+        <v>629.131189323633</v>
       </c>
       <c r="N24">
-        <v>2411.891281505595</v>
+        <v>2434.868810676367</v>
       </c>
       <c r="O24">
-        <v>301.4864101881994</v>
+        <v>304.3586013345459</v>
       </c>
       <c r="P24">
-        <v>2110.404871317396</v>
+        <v>2130.510209341821</v>
       </c>
       <c r="Q24">
-        <v>2936.404871317396</v>
+        <v>2956.510209341821</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1274991758403433</v>
+        <v>0.1274610215197583</v>
       </c>
       <c r="T24">
         <v>1.591725304999514</v>
       </c>
       <c r="U24">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.698603029068823</v>
+        <v>4.870208395317436</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1114748170593741</v>
+        <v>0.1110023449417215</v>
       </c>
       <c r="C25">
-        <v>36423.06242055168</v>
+        <v>36735.16316070612</v>
       </c>
       <c r="D25">
-        <v>46023.13620005081</v>
+        <v>46335.23694020525</v>
       </c>
       <c r="E25">
         <v>6216.039955589868</v>
@@ -3343,37 +3343,37 @@
         <v>3064</v>
       </c>
       <c r="M25">
-        <v>681.7500238805144</v>
+        <v>657.7280615656164</v>
       </c>
       <c r="N25">
-        <v>2382.249976119486</v>
+        <v>2406.271938434384</v>
       </c>
       <c r="O25">
-        <v>297.7812470149357</v>
+        <v>300.783992304298</v>
       </c>
       <c r="P25">
-        <v>2084.46872910455</v>
+        <v>2105.487946130086</v>
       </c>
       <c r="Q25">
-        <v>2910.46872910455</v>
+        <v>2931.487946130086</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1284538285143366</v>
+        <v>0.1284152283615409</v>
       </c>
       <c r="T25">
         <v>1.610324572410118</v>
       </c>
       <c r="U25">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.494315940848439</v>
+        <v>4.658460204216676</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1114812282557427</v>
+        <v>0.1109895443904937</v>
       </c>
       <c r="C26">
-        <v>35943.82772777674</v>
+        <v>36269.51916146679</v>
       </c>
       <c r="D26">
-        <v>46018.64384551496</v>
+        <v>46344.33527920501</v>
       </c>
       <c r="E26">
         <v>6690.78229382896</v>
@@ -3425,37 +3425,37 @@
         <v>3064</v>
       </c>
       <c r="M26">
-        <v>711.3913292666236</v>
+        <v>686.3249338075996</v>
       </c>
       <c r="N26">
-        <v>2352.608670733376</v>
+        <v>2377.675066192401</v>
       </c>
       <c r="O26">
-        <v>294.076083841672</v>
+        <v>297.2093832740501</v>
       </c>
       <c r="P26">
-        <v>2058.532586891704</v>
+        <v>2080.46568291835</v>
       </c>
       <c r="Q26">
-        <v>2884.532586891704</v>
+        <v>2906.46568291835</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1294336036271191</v>
+        <v>0.1293945459096862</v>
       </c>
       <c r="T26">
         <v>1.629413294226264</v>
       </c>
       <c r="U26">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.307052776646421</v>
+        <v>4.464357695707649</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1117938894521112</v>
+        <v>0.110976743839266</v>
       </c>
       <c r="C27">
-        <v>35251.06150339531</v>
+        <v>35803.87873600998</v>
       </c>
       <c r="D27">
-        <v>45800.61995937262</v>
+        <v>46353.43719198729</v>
       </c>
       <c r="E27">
         <v>7165.524632068054</v>
@@ -3507,45 +3507,45 @@
         <v>3064</v>
       </c>
       <c r="M27">
-        <v>757.6486164911014</v>
+        <v>714.921806049583</v>
       </c>
       <c r="N27">
-        <v>2306.351383508899</v>
+        <v>2349.078193950417</v>
       </c>
       <c r="O27">
-        <v>288.2939229386124</v>
+        <v>293.6347742438021</v>
       </c>
       <c r="P27">
-        <v>2018.057460570286</v>
+        <v>2055.443419706615</v>
       </c>
       <c r="Q27">
-        <v>2844.057460570286</v>
+        <v>2881.443419706615</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1304395060762426</v>
+        <v>0.1303999785924488</v>
       </c>
       <c r="T27">
         <v>1.649011048624175</v>
       </c>
       <c r="U27">
-        <v>0.0638366166625341</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05585703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.044091064523164</v>
+        <v>4.285783387879342</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1118125506484798</v>
+        <v>0.1111914432880382</v>
       </c>
       <c r="C28">
-        <v>34763.37171267229</v>
+        <v>35176.94435377546</v>
       </c>
       <c r="D28">
-        <v>45787.6725068887</v>
+        <v>46201.24514799187</v>
       </c>
       <c r="E28">
         <v>7640.266970307147</v>
@@ -3589,37 +3589,37 @@
         <v>3064</v>
       </c>
       <c r="M28">
-        <v>787.9545611507455</v>
+        <v>755.8619790857828</v>
       </c>
       <c r="N28">
-        <v>2276.045438849254</v>
+        <v>2308.138020914217</v>
       </c>
       <c r="O28">
-        <v>284.5056798561568</v>
+        <v>288.5172526142771</v>
       </c>
       <c r="P28">
-        <v>1991.539758993098</v>
+        <v>2019.62076829994</v>
       </c>
       <c r="Q28">
-        <v>2817.539758993098</v>
+        <v>2845.62076829994</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.131472595078045</v>
+        <v>0.1314325851315022</v>
       </c>
       <c r="T28">
         <v>1.669138472059867</v>
       </c>
       <c r="U28">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.888549100503041</v>
+        <v>4.053650117056975</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1118312118448483</v>
+        <v>0.1111873927368104</v>
       </c>
       <c r="C29">
-        <v>34275.68924015371</v>
+        <v>34705.06404294602</v>
       </c>
       <c r="D29">
-        <v>45774.73237260921</v>
+        <v>46204.10717540152</v>
       </c>
       <c r="E29">
         <v>8115.00930854624</v>
@@ -3671,37 +3671,37 @@
         <v>3064</v>
       </c>
       <c r="M29">
-        <v>818.2605058103895</v>
+        <v>784.9335936660052</v>
       </c>
       <c r="N29">
-        <v>2245.73949418961</v>
+        <v>2279.066406333995</v>
       </c>
       <c r="O29">
-        <v>280.7174367737013</v>
+        <v>284.8833007917493</v>
       </c>
       <c r="P29">
-        <v>1965.022057415909</v>
+        <v>1994.183105542245</v>
       </c>
       <c r="Q29">
-        <v>2791.022057415909</v>
+        <v>2820.183105542245</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.132533987888116</v>
+        <v>0.1324934822606667</v>
       </c>
       <c r="T29">
         <v>1.689817331754071</v>
       </c>
       <c r="U29">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.744528763447373</v>
+        <v>3.903514927536346</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1118498730412169</v>
+        <v>0.1111833421855826</v>
       </c>
       <c r="C30">
-        <v>33788.01407963666</v>
+        <v>34233.18408672645</v>
       </c>
       <c r="D30">
-        <v>45761.79955033126</v>
+        <v>46206.96955742104</v>
       </c>
       <c r="E30">
         <v>8589.751646785331</v>
@@ -3753,37 +3753,37 @@
         <v>3064</v>
       </c>
       <c r="M30">
-        <v>848.5664504700336</v>
+        <v>814.0052082462275</v>
       </c>
       <c r="N30">
-        <v>2215.433549529967</v>
+        <v>2249.994791753772</v>
       </c>
       <c r="O30">
-        <v>276.9291936912458</v>
+        <v>281.2493489692216</v>
       </c>
       <c r="P30">
-        <v>1938.504355838721</v>
+        <v>1968.745442784551</v>
       </c>
       <c r="Q30">
-        <v>2764.504355838721</v>
+        <v>2794.745442784551</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1336248638318001</v>
+        <v>0.1335838487545302</v>
       </c>
       <c r="T30">
         <v>1.711070604217558</v>
       </c>
       <c r="U30">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.610795593324253</v>
+        <v>3.764103680124334</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1118685342375855</v>
+        <v>0.1111792916343548</v>
       </c>
       <c r="C31">
-        <v>33300.3462249253</v>
+        <v>33761.30448518264</v>
       </c>
       <c r="D31">
-        <v>45748.87403385899</v>
+        <v>46209.83229411633</v>
       </c>
       <c r="E31">
         <v>9064.493985024423</v>
@@ -3835,37 +3835,37 @@
         <v>3064</v>
       </c>
       <c r="M31">
-        <v>878.8723951296776</v>
+        <v>843.0768228264499</v>
       </c>
       <c r="N31">
-        <v>2185.127604870323</v>
+        <v>2220.92317717355</v>
       </c>
       <c r="O31">
-        <v>273.1409506087903</v>
+        <v>277.6153971466938</v>
       </c>
       <c r="P31">
-        <v>1911.986654261532</v>
+        <v>1943.307780026857</v>
       </c>
       <c r="Q31">
-        <v>2737.986654261532</v>
+        <v>2769.307780026857</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1347464686753062</v>
+        <v>0.1347049297975166</v>
       </c>
       <c r="T31">
         <v>1.732922560412411</v>
       </c>
       <c r="U31">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.486285400451003</v>
+        <v>3.634307001499358</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.111887195433954</v>
+        <v>0.111175241083127</v>
       </c>
       <c r="C32">
-        <v>32812.68566983073</v>
+        <v>33289.42523838051</v>
       </c>
       <c r="D32">
-        <v>45735.95581700351</v>
+        <v>46212.69538555328</v>
       </c>
       <c r="E32">
         <v>9539.236323263514</v>
@@ -3917,37 +3917,37 @@
         <v>3064</v>
       </c>
       <c r="M32">
-        <v>909.1783397893215</v>
+        <v>872.1484374066723</v>
       </c>
       <c r="N32">
-        <v>2154.821660210679</v>
+        <v>2191.851562593328</v>
       </c>
       <c r="O32">
-        <v>269.3527075263348</v>
+        <v>273.981445324166</v>
       </c>
       <c r="P32">
-        <v>1885.468952684344</v>
+        <v>1917.870117269162</v>
       </c>
       <c r="Q32">
-        <v>2711.468952684344</v>
+        <v>2743.870117269162</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.135900119371484</v>
+        <v>0.1358580417274455</v>
       </c>
       <c r="T32">
         <v>1.755398858212831</v>
       </c>
       <c r="U32">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.370075887102637</v>
+        <v>3.513163434782712</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1119058566303226</v>
+        <v>0.1111711905318993</v>
       </c>
       <c r="C33">
-        <v>32325.03240817109</v>
+        <v>32817.54634638599</v>
       </c>
       <c r="D33">
-        <v>45723.04489358296</v>
+        <v>46215.55883179786</v>
       </c>
       <c r="E33">
         <v>10013.97866150261</v>
@@ -3999,37 +3999,37 @@
         <v>3064</v>
       </c>
       <c r="M33">
-        <v>939.4842844489657</v>
+        <v>901.2200519868948</v>
       </c>
       <c r="N33">
-        <v>2124.515715551034</v>
+        <v>2162.779948013105</v>
       </c>
       <c r="O33">
-        <v>265.5644644438793</v>
+        <v>270.3474935016382</v>
       </c>
       <c r="P33">
-        <v>1858.951251107155</v>
+        <v>1892.432454511467</v>
       </c>
       <c r="Q33">
-        <v>2684.951251107155</v>
+        <v>2718.432454511467</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1370872092182756</v>
+        <v>0.1370445771915752</v>
       </c>
       <c r="T33">
         <v>1.778526642906018</v>
       </c>
       <c r="U33">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.261363761712228</v>
+        <v>3.399835582047785</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1119245178266911</v>
+        <v>0.1111671399806715</v>
       </c>
       <c r="C34">
-        <v>31837.38643377144</v>
+        <v>32345.66780926509</v>
       </c>
       <c r="D34">
-        <v>45710.1412574224</v>
+        <v>46218.42263291605</v>
       </c>
       <c r="E34">
         <v>10488.7209997417</v>
@@ -4081,37 +4081,37 @@
         <v>3064</v>
       </c>
       <c r="M34">
-        <v>969.7902291086098</v>
+        <v>930.2916665671172</v>
       </c>
       <c r="N34">
-        <v>2094.20977089139</v>
+        <v>2133.708333432883</v>
       </c>
       <c r="O34">
-        <v>261.7762213614238</v>
+        <v>266.7135416791103</v>
       </c>
       <c r="P34">
-        <v>1832.433549529967</v>
+        <v>1866.994791753772</v>
       </c>
       <c r="Q34">
-        <v>2658.433549529967</v>
+        <v>2692.994791753772</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1383092134723258</v>
+        <v>0.1382660107575911</v>
       </c>
       <c r="T34">
         <v>1.802334656560768</v>
       </c>
       <c r="U34">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.159446144158721</v>
+        <v>3.293590720108792</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1119431790230597</v>
+        <v>0.1111630894294437</v>
       </c>
       <c r="C35">
-        <v>31349.74774046388</v>
+        <v>31873.78962708373</v>
       </c>
       <c r="D35">
-        <v>45697.24490235394</v>
+        <v>46221.28678897378</v>
       </c>
       <c r="E35">
         <v>10963.4633379808</v>
@@ -4163,37 +4163,37 @@
         <v>3064</v>
       </c>
       <c r="M35">
-        <v>1000.096173768254</v>
+        <v>959.3632811473396</v>
       </c>
       <c r="N35">
-        <v>2063.903826231746</v>
+        <v>2104.63671885266</v>
       </c>
       <c r="O35">
-        <v>257.9879782789683</v>
+        <v>263.0795898565825</v>
       </c>
       <c r="P35">
-        <v>1805.915847952778</v>
+        <v>1841.557128996078</v>
       </c>
       <c r="Q35">
-        <v>2631.915847952778</v>
+        <v>2667.557128996078</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1395676954653029</v>
+        <v>0.1395239050270702</v>
       </c>
       <c r="T35">
         <v>1.826853357190287</v>
       </c>
       <c r="U35">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.063705351911487</v>
+        <v>3.193784940711556</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1127353402194282</v>
+        <v>0.1111590388782159</v>
       </c>
       <c r="C36">
-        <v>30334.19117652689</v>
+        <v>31401.91179990791</v>
       </c>
       <c r="D36">
-        <v>45156.43067665603</v>
+        <v>46224.15130003706</v>
       </c>
       <c r="E36">
         <v>11438.20567621989</v>
@@ -4245,45 +4245,45 @@
         <v>3064</v>
       </c>
       <c r="M36">
-        <v>1072.369341128234</v>
+        <v>988.434895727562</v>
       </c>
       <c r="N36">
-        <v>1991.630658871766</v>
+        <v>2075.565104272438</v>
       </c>
       <c r="O36">
-        <v>248.9538323589708</v>
+        <v>259.4456380340548</v>
       </c>
       <c r="P36">
-        <v>1742.676826512796</v>
+        <v>1816.119466238383</v>
       </c>
       <c r="Q36">
-        <v>2568.676826512796</v>
+        <v>2642.119466238383</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.140864313276249</v>
+        <v>0.1408199173047152</v>
       </c>
       <c r="T36">
         <v>1.852115048747974</v>
       </c>
       <c r="U36">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.857224542410345</v>
+        <v>3.099850089514157</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1127767514157968</v>
+        <v>0.1111549883269882</v>
       </c>
       <c r="C37">
-        <v>29831.52897387924</v>
+        <v>30930.03432780367</v>
       </c>
       <c r="D37">
-        <v>45128.51081224748</v>
+        <v>46227.01616617191</v>
       </c>
       <c r="E37">
         <v>11912.94801445898</v>
@@ -4327,45 +4327,45 @@
         <v>3064</v>
       </c>
       <c r="M37">
-        <v>1103.909615867299</v>
+        <v>1017.506510307785</v>
       </c>
       <c r="N37">
-        <v>1960.090384132701</v>
+        <v>2046.493489692215</v>
       </c>
       <c r="O37">
-        <v>245.0112980165876</v>
+        <v>255.8116862115269</v>
       </c>
       <c r="P37">
-        <v>1715.079086116113</v>
+        <v>1790.681803480689</v>
       </c>
       <c r="Q37">
-        <v>2541.079086116113</v>
+        <v>2616.681803480688</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1422008270198395</v>
+        <v>0.1421558068832109</v>
       </c>
       <c r="T37">
         <v>1.87815402312282</v>
       </c>
       <c r="U37">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.775589555484334</v>
+        <v>3.011282944099467</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1128181626121653</v>
+        <v>0.1119384377757604</v>
       </c>
       <c r="C38">
-        <v>29328.90127516137</v>
+        <v>29907.70526765617</v>
       </c>
       <c r="D38">
-        <v>45100.6254517687</v>
+        <v>45679.4294442635</v>
       </c>
       <c r="E38">
         <v>12387.69035269807</v>
@@ -4409,37 +4409,37 @@
         <v>3064</v>
       </c>
       <c r="M38">
-        <v>1135.449890606365</v>
+        <v>1089.304935329525</v>
       </c>
       <c r="N38">
-        <v>1928.550109393635</v>
+        <v>1974.695064670475</v>
       </c>
       <c r="O38">
-        <v>241.0687636742044</v>
+        <v>246.8368830838094</v>
       </c>
       <c r="P38">
-        <v>1687.481345719431</v>
+        <v>1727.858181586666</v>
       </c>
       <c r="Q38">
-        <v>2513.481345719431</v>
+        <v>2553.858181586666</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1435791068179173</v>
+        <v>0.1435334430110346</v>
       </c>
       <c r="T38">
         <v>1.905006715446879</v>
       </c>
       <c r="U38">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.698489845609771</v>
+        <v>2.812802825567949</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1128595738085339</v>
+        <v>0.1119562622245326</v>
       </c>
       <c r="C39">
-        <v>28826.30801645177</v>
+        <v>29420.65554349931</v>
       </c>
       <c r="D39">
-        <v>45072.7745312982</v>
+        <v>45667.12205834574</v>
       </c>
       <c r="E39">
         <v>12862.43269093717</v>
@@ -4491,37 +4491,37 @@
         <v>3064</v>
       </c>
       <c r="M39">
-        <v>1166.990165345431</v>
+        <v>1119.563405755345</v>
       </c>
       <c r="N39">
-        <v>1897.009834654569</v>
+        <v>1944.436594244655</v>
       </c>
       <c r="O39">
-        <v>237.1262293318212</v>
+        <v>243.0545742805818</v>
       </c>
       <c r="P39">
-        <v>1659.883605322748</v>
+        <v>1701.382019964073</v>
       </c>
       <c r="Q39">
-        <v>2485.883605322748</v>
+        <v>2527.382019964073</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1450011415302198</v>
+        <v>0.1449548136191067</v>
       </c>
       <c r="T39">
         <v>1.932711874193925</v>
       </c>
       <c r="U39">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.625557687620317</v>
+        <v>2.736781127579626</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1129009850049024</v>
+        <v>0.1119740866733048</v>
       </c>
       <c r="C40">
-        <v>28323.74913398678</v>
+        <v>28933.61244950182</v>
       </c>
       <c r="D40">
-        <v>45044.9579870723</v>
+        <v>45654.82130258733</v>
       </c>
       <c r="E40">
         <v>13337.17502917626</v>
@@ -4573,37 +4573,37 @@
         <v>3064</v>
       </c>
       <c r="M40">
-        <v>1198.530440084496</v>
+        <v>1149.821876181165</v>
       </c>
       <c r="N40">
-        <v>1865.469559915504</v>
+        <v>1914.178123818835</v>
       </c>
       <c r="O40">
-        <v>233.183694989438</v>
+        <v>239.2722654773543</v>
       </c>
       <c r="P40">
-        <v>1632.285864926066</v>
+        <v>1674.90585834148</v>
       </c>
       <c r="Q40">
-        <v>2458.285864926066</v>
+        <v>2500.90585834148</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1464690483300158</v>
+        <v>0.1464220348919552</v>
       </c>
       <c r="T40">
         <v>1.961310747739263</v>
       </c>
       <c r="U40">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.556464064261887</v>
+        <v>2.664760571590688</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.113863771201271</v>
+        <v>0.1119919111220771</v>
       </c>
       <c r="C41">
-        <v>27211.8298806204</v>
+        <v>28446.57598030748</v>
       </c>
       <c r="D41">
-        <v>44407.78107194501</v>
+        <v>45642.52717163209</v>
       </c>
       <c r="E41">
         <v>13811.91736741535</v>
@@ -4655,45 +4655,45 @@
         <v>3064</v>
       </c>
       <c r="M41">
-        <v>1280.061083040139</v>
+        <v>1180.080346606986</v>
       </c>
       <c r="N41">
-        <v>1783.938916959861</v>
+        <v>1883.919653393014</v>
       </c>
       <c r="O41">
-        <v>222.9923646199827</v>
+        <v>235.4899566741268</v>
       </c>
       <c r="P41">
-        <v>1560.946552339879</v>
+        <v>1648.429696718887</v>
       </c>
       <c r="Q41">
-        <v>2386.946552339879</v>
+        <v>2474.429696718887</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1479850832216085</v>
+        <v>0.1479373617803071</v>
       </c>
       <c r="T41">
         <v>1.990847289269694</v>
       </c>
       <c r="U41">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.393635773007813</v>
+        <v>2.596433377447338</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1139288073976395</v>
+        <v>0.1120097355708493</v>
       </c>
       <c r="C42">
-        <v>26694.69558983721</v>
+        <v>27959.54613056588</v>
       </c>
       <c r="D42">
-        <v>44365.38911940092</v>
+        <v>45630.23966012958</v>
       </c>
       <c r="E42">
         <v>14286.65970565445</v>
@@ -4737,45 +4737,45 @@
         <v>3064</v>
       </c>
       <c r="M42">
-        <v>1312.88316209245</v>
+        <v>1210.338817032806</v>
       </c>
       <c r="N42">
-        <v>1751.11683790755</v>
+        <v>1853.661182967194</v>
       </c>
       <c r="O42">
-        <v>218.8896047384438</v>
+        <v>231.7076478708993</v>
       </c>
       <c r="P42">
-        <v>1532.227233169106</v>
+        <v>1621.953535096295</v>
       </c>
       <c r="Q42">
-        <v>2358.227233169107</v>
+        <v>2447.953535096295</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1495516526095876</v>
+        <v>0.1495031995649372</v>
       </c>
       <c r="T42">
         <v>2.021368382184472</v>
       </c>
       <c r="U42">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.333794878682617</v>
+        <v>2.531522543011153</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1139938435940081</v>
+        <v>0.1132831850196215</v>
       </c>
       <c r="C43">
-        <v>26177.64215712579</v>
+        <v>26623.73294148236</v>
       </c>
       <c r="D43">
-        <v>44323.07802492859</v>
+        <v>44769.16880928515</v>
       </c>
       <c r="E43">
         <v>14761.40204389354</v>
@@ -4819,37 +4819,37 @@
         <v>3064</v>
       </c>
       <c r="M43">
-        <v>1345.705241144761</v>
+        <v>1308.722812995936</v>
       </c>
       <c r="N43">
-        <v>1718.294758855239</v>
+        <v>1755.277187004064</v>
       </c>
       <c r="O43">
-        <v>214.7868448569048</v>
+        <v>219.4096483755081</v>
       </c>
       <c r="P43">
-        <v>1503.507913998334</v>
+        <v>1535.867538628556</v>
       </c>
       <c r="Q43">
-        <v>2329.507913998334</v>
+        <v>2361.867538628556</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1511713260446169</v>
+        <v>0.1511221165965041</v>
       </c>
       <c r="T43">
         <v>2.052924088418396</v>
       </c>
       <c r="U43">
-        <v>0.06913661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971732</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.276873052373285</v>
+        <v>2.34121386864639</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1157861297903766</v>
+        <v>0.1133316344683937</v>
       </c>
       <c r="C44">
-        <v>24567.82289489355</v>
+        <v>26116.87170714554</v>
       </c>
       <c r="D44">
-        <v>43188.00110093544</v>
+        <v>44737.04991318742</v>
       </c>
       <c r="E44">
         <v>15236.14438213263</v>
@@ -4901,45 +4901,45 @@
         <v>3064</v>
       </c>
       <c r="M44">
-        <v>1472.241457765469</v>
+        <v>1340.642881605592</v>
       </c>
       <c r="N44">
-        <v>1591.758542234531</v>
+        <v>1723.357118394408</v>
       </c>
       <c r="O44">
-        <v>198.9698177793164</v>
+        <v>215.4196397993009</v>
       </c>
       <c r="P44">
-        <v>1392.788724455215</v>
+        <v>1507.937478595107</v>
       </c>
       <c r="Q44">
-        <v>2218.788724455215</v>
+        <v>2333.937478595107</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1528468502877506</v>
+        <v>0.1527968583532973</v>
       </c>
       <c r="T44">
         <v>2.085567922453489</v>
       </c>
       <c r="U44">
-        <v>0.07383661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971732</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.081180355191506</v>
+        <v>2.285470681297666</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1158922909867452</v>
+        <v>0.114433583917166</v>
       </c>
       <c r="C45">
-        <v>24027.66837221739</v>
+        <v>24923.85174623369</v>
       </c>
       <c r="D45">
-        <v>43122.58891649837</v>
+        <v>44018.77229051467</v>
       </c>
       <c r="E45">
         <v>15710.88672037172</v>
@@ -4983,37 +4983,37 @@
         <v>3064</v>
       </c>
       <c r="M45">
-        <v>1507.294825807504</v>
+        <v>1429.721927739236</v>
       </c>
       <c r="N45">
-        <v>1556.705174192496</v>
+        <v>1634.278072260764</v>
       </c>
       <c r="O45">
-        <v>194.588146774062</v>
+        <v>204.2847590325955</v>
       </c>
       <c r="P45">
-        <v>1362.117027418434</v>
+        <v>1429.993313228168</v>
       </c>
       <c r="Q45">
-        <v>2188.117027418434</v>
+        <v>2255.993313228169</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1545811648552048</v>
+        <v>0.15453036297875</v>
       </c>
       <c r="T45">
         <v>2.119357154174024</v>
       </c>
       <c r="U45">
-        <v>0.07383661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.032780812047518</v>
+        <v>2.143074076540873</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1195789521831137</v>
+        <v>0.1145065333659382</v>
       </c>
       <c r="C46">
-        <v>21398.13295897182</v>
+        <v>24402.37229265915</v>
       </c>
       <c r="D46">
-        <v>40967.79584149189</v>
+        <v>43972.03517517922</v>
       </c>
       <c r="E46">
         <v>16185.62905861081</v>
@@ -5065,45 +5065,45 @@
         <v>3064</v>
       </c>
       <c r="M46">
-        <v>1736.612758656975</v>
+        <v>1462.971274895963</v>
       </c>
       <c r="N46">
-        <v>1327.387241343025</v>
+        <v>1601.028725104037</v>
       </c>
       <c r="O46">
-        <v>165.9234051678781</v>
+        <v>200.1285906380047</v>
       </c>
       <c r="P46">
-        <v>1161.463836175147</v>
+        <v>1400.900134466033</v>
       </c>
       <c r="Q46">
-        <v>1987.463836175147</v>
+        <v>2226.900134466033</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1563774192286395</v>
+        <v>0.1563257784836831</v>
       </c>
       <c r="T46">
         <v>2.154353144170293</v>
       </c>
       <c r="U46">
-        <v>0.08313661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V46">
         <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.764354191644642</v>
+        <v>2.09436784752858</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1216171133794823</v>
+        <v>0.1145794828147104</v>
       </c>
       <c r="C47">
-        <v>19822.06971753578</v>
+        <v>23880.99198047566</v>
       </c>
       <c r="D47">
-        <v>39866.47493829494</v>
+        <v>43925.39720123482</v>
       </c>
       <c r="E47">
         <v>16660.37139684991</v>
@@ -5147,45 +5147,45 @@
         <v>3064</v>
       </c>
       <c r="M47">
-        <v>1876.489234982202</v>
+        <v>1496.220622052689</v>
       </c>
       <c r="N47">
-        <v>1187.510765017798</v>
+        <v>1567.779377947311</v>
       </c>
       <c r="O47">
-        <v>148.4388456272247</v>
+        <v>195.9724222434138</v>
       </c>
       <c r="P47">
-        <v>1039.071919390573</v>
+        <v>1371.806955703897</v>
       </c>
       <c r="Q47">
-        <v>1865.071919390573</v>
+        <v>2197.806955703897</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1582389919429263</v>
+        <v>0.1581864818251593</v>
       </c>
       <c r="T47">
         <v>2.190621715620971</v>
       </c>
       <c r="U47">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.632836438856022</v>
+        <v>2.047826339805722</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1218457745758508</v>
+        <v>0.1146524322634826</v>
       </c>
       <c r="C48">
-        <v>19227.45331784841</v>
+        <v>23359.71049456101</v>
       </c>
       <c r="D48">
-        <v>39746.60087684667</v>
+        <v>43878.85805355927</v>
       </c>
       <c r="E48">
         <v>17135.113735089</v>
@@ -5229,45 +5229,45 @@
         <v>3064</v>
       </c>
       <c r="M48">
-        <v>1918.188995759584</v>
+        <v>1529.469969209416</v>
       </c>
       <c r="N48">
-        <v>1145.811004240416</v>
+        <v>1534.530030790584</v>
       </c>
       <c r="O48">
-        <v>143.2263755300519</v>
+        <v>191.816253848823</v>
       </c>
       <c r="P48">
-        <v>1002.584628710364</v>
+        <v>1342.713776941761</v>
       </c>
       <c r="Q48">
-        <v>1828.584628710364</v>
+        <v>2168.713776941761</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1601695117947794</v>
+        <v>0.1601161001052086</v>
       </c>
       <c r="T48">
         <v>2.228233567495749</v>
       </c>
       <c r="U48">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V48">
         <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.597339994533065</v>
+        <v>2.003308375896903</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1220744357722194</v>
+        <v>0.1179331317122548</v>
       </c>
       <c r="C49">
-        <v>18633.55565297767</v>
+        <v>20889.30621829171</v>
       </c>
       <c r="D49">
-        <v>39627.44555021502</v>
+        <v>41883.19611552906</v>
       </c>
       <c r="E49">
         <v>17609.85607332809</v>
@@ -5311,45 +5311,45 @@
         <v>3064</v>
       </c>
       <c r="M49">
-        <v>1959.888756536967</v>
+        <v>1736.759857564593</v>
       </c>
       <c r="N49">
-        <v>1104.111243463033</v>
+        <v>1327.240142435407</v>
       </c>
       <c r="O49">
-        <v>138.0139054328791</v>
+        <v>165.9050178044258</v>
       </c>
       <c r="P49">
-        <v>966.0973380301538</v>
+        <v>1161.335124630981</v>
       </c>
       <c r="Q49">
-        <v>1792.097338030154</v>
+        <v>1987.335124630981</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1621728814523627</v>
+        <v>0.1621185341694107</v>
       </c>
       <c r="T49">
         <v>2.267264734535612</v>
       </c>
       <c r="U49">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971732</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.563354037202574</v>
+        <v>1.764204755570846</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1223030969685879</v>
+        <v>0.1197123311610271</v>
       </c>
       <c r="C50">
-        <v>18040.37027821338</v>
+        <v>19406.36188897728</v>
       </c>
       <c r="D50">
-        <v>39509.00251368982</v>
+        <v>40874.99412445372</v>
       </c>
       <c r="E50">
         <v>18084.59841156718</v>
@@ -5393,37 +5393,37 @@
         <v>3064</v>
       </c>
       <c r="M50">
-        <v>2001.588517314349</v>
+        <v>1862.583960677943</v>
       </c>
       <c r="N50">
-        <v>1062.411482685651</v>
+        <v>1201.416039322057</v>
       </c>
       <c r="O50">
-        <v>132.8014353357064</v>
+        <v>150.1770049152572</v>
       </c>
       <c r="P50">
-        <v>929.6100473499446</v>
+        <v>1051.2390344068</v>
       </c>
       <c r="Q50">
-        <v>1755.610047349945</v>
+        <v>1877.2390344068</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1642533037890839</v>
+        <v>0.1641979849283899</v>
       </c>
       <c r="T50">
         <v>2.307797100307778</v>
       </c>
       <c r="U50">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V50">
         <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.530784161427521</v>
+        <v>1.645026514071755</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1295203831649565</v>
+        <v>0.1198876556097993</v>
       </c>
       <c r="C51">
-        <v>14159.67388560129</v>
+        <v>18834.89107749318</v>
       </c>
       <c r="D51">
-        <v>36103.04845931683</v>
+        <v>40778.26565120872</v>
       </c>
       <c r="E51">
         <v>18559.34074980628</v>
@@ -5475,45 +5475,45 @@
         <v>3064</v>
       </c>
       <c r="M51">
-        <v>2422.464983643295</v>
+        <v>1901.387793192067</v>
       </c>
       <c r="N51">
-        <v>641.535016356705</v>
+        <v>1162.612206807933</v>
       </c>
       <c r="O51">
-        <v>80.19187704458813</v>
+        <v>145.3265258509917</v>
       </c>
       <c r="P51">
-        <v>561.3431393121168</v>
+        <v>1017.285680956942</v>
       </c>
       <c r="Q51">
-        <v>1387.343139312117</v>
+        <v>1843.285680956942</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1664153113154804</v>
+        <v>0.1663589827759565</v>
       </c>
       <c r="T51">
         <v>2.349918970620029</v>
       </c>
       <c r="U51">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V51">
         <v>0.125</v>
       </c>
       <c r="W51">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.264827364147019</v>
+        <v>1.611454544396822</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1449148096183836</v>
+        <v>0.1200629800585715</v>
       </c>
       <c r="C52">
-        <v>8077.437305165899</v>
+        <v>18263.87699064465</v>
       </c>
       <c r="D52">
-        <v>30495.55421712053</v>
+        <v>40681.99390259928</v>
       </c>
       <c r="E52">
         <v>19034.08308804537</v>
@@ -5557,45 +5557,45 @@
         <v>3064</v>
       </c>
       <c r="M52">
-        <v>3248.10676755489</v>
+        <v>1940.191625706191</v>
       </c>
       <c r="N52">
-        <v>-184.1067675548902</v>
+        <v>1123.808374293809</v>
       </c>
       <c r="O52">
-        <v>-23.01334594436128</v>
+        <v>140.4760467867262</v>
       </c>
       <c r="P52">
-        <v>-161.0934216105289</v>
+        <v>983.3323275070833</v>
       </c>
       <c r="Q52">
-        <v>664.9065783894711</v>
+        <v>1809.332327507083</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1691280707638796</v>
+        <v>0.1686064205374257</v>
       </c>
       <c r="T52">
-        <v>2.402771007571195</v>
+        <v>2.39372571574477</v>
       </c>
       <c r="U52">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V52">
-        <v>0.1179148431405519</v>
+        <v>0.125</v>
       </c>
       <c r="W52">
-        <v>0.1207015484728875</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.9433187451244153</v>
+        <v>1.579225453508885</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1458251757850089</v>
+        <v>0.1202383045073437</v>
       </c>
       <c r="C53">
-        <v>7325.143634735941</v>
+        <v>17693.31640126277</v>
       </c>
       <c r="D53">
-        <v>30218.00288492966</v>
+        <v>40586.17565145649</v>
       </c>
       <c r="E53">
         <v>19508.82542628446</v>
@@ -5639,45 +5639,45 @@
         <v>3064</v>
       </c>
       <c r="M53">
-        <v>3313.068902905988</v>
+        <v>1978.995458220314</v>
       </c>
       <c r="N53">
-        <v>-249.0689029059877</v>
+        <v>1085.004541779686</v>
       </c>
       <c r="O53">
-        <v>-31.13361286324846</v>
+        <v>135.6255677224607</v>
       </c>
       <c r="P53">
-        <v>-217.9352900427392</v>
+        <v>949.378974057225</v>
       </c>
       <c r="Q53">
-        <v>608.0647099572608</v>
+        <v>1775.378974057225</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1716449701672241</v>
+        <v>0.1709455904524243</v>
       </c>
       <c r="T53">
-        <v>2.451807150582852</v>
+        <v>2.439320491282766</v>
       </c>
       <c r="U53">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V53">
-        <v>0.115602787392698</v>
+        <v>0.125</v>
       </c>
       <c r="W53">
-        <v>0.121017922358959</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.9248222991415838</v>
+        <v>1.548260248538123</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1467355419516342</v>
+        <v>0.120413628956116</v>
       </c>
       <c r="C54">
-        <v>6577.856592049648</v>
+        <v>17123.20611251092</v>
       </c>
       <c r="D54">
-        <v>29945.45818048246</v>
+        <v>40490.80770094374</v>
       </c>
       <c r="E54">
         <v>19983.56776452356</v>
@@ -5721,45 +5721,45 @@
         <v>3064</v>
       </c>
       <c r="M54">
-        <v>3378.031038257086</v>
+        <v>2017.799290734438</v>
       </c>
       <c r="N54">
-        <v>-314.031038257086</v>
+        <v>1046.200709265562</v>
       </c>
       <c r="O54">
-        <v>-39.25387978213575</v>
+        <v>130.7750886581952</v>
       </c>
       <c r="P54">
-        <v>-274.7771584749503</v>
+        <v>915.4256206073665</v>
       </c>
       <c r="Q54">
-        <v>551.2228415250497</v>
+        <v>1741.425620607366</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1742667403790413</v>
+        <v>0.1733822257805478</v>
       </c>
       <c r="T54">
-        <v>2.502886466219994</v>
+        <v>2.486815049134844</v>
       </c>
       <c r="U54">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V54">
-        <v>0.1133796568659153</v>
+        <v>0.125</v>
       </c>
       <c r="W54">
-        <v>0.1213221280186432</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.9070372549273223</v>
+        <v>1.518486012989313</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1476459081182596</v>
+        <v>0.1271742034048882</v>
       </c>
       <c r="C55">
-        <v>5835.441919444882</v>
+        <v>13284.48466911102</v>
       </c>
       <c r="D55">
-        <v>29677.78584611679</v>
+        <v>37126.82859578293</v>
       </c>
       <c r="E55">
         <v>20458.31010276265</v>
@@ -5803,45 +5803,45 @@
         <v>3064</v>
       </c>
       <c r="M55">
-        <v>3442.993173608183</v>
+        <v>2413.894207007303</v>
       </c>
       <c r="N55">
-        <v>-378.9931736081835</v>
+        <v>650.1057929926969</v>
       </c>
       <c r="O55">
-        <v>-47.37414670102294</v>
+        <v>81.26322412408712</v>
       </c>
       <c r="P55">
-        <v>-331.6190269071606</v>
+        <v>568.8425688686098</v>
       </c>
       <c r="Q55">
-        <v>494.3809730928394</v>
+        <v>1394.84256886861</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.177000075280723</v>
+        <v>0.1759225477183787</v>
       </c>
       <c r="T55">
-        <v>2.55613936975659</v>
+        <v>2.536330652001905</v>
       </c>
       <c r="U55">
-        <v>0.1368366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V55">
-        <v>0.1112404180571245</v>
+        <v>0.125</v>
       </c>
       <c r="W55">
-        <v>0.1216148542194713</v>
+        <v>0.08394453957971733</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8899233444569956</v>
+        <v>1.26931826221112</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1485562742848849</v>
+        <v>0.1415040891807923</v>
       </c>
       <c r="C56">
-        <v>5097.770117066681</v>
+        <v>7250.6986415881</v>
       </c>
       <c r="D56">
-        <v>29414.85638197768</v>
+        <v>31567.78490649911</v>
       </c>
       <c r="E56">
         <v>20933.05244100174</v>
@@ -5885,37 +5885,37 @@
         <v>3064</v>
       </c>
       <c r="M56">
-        <v>3507.955308959282</v>
+        <v>3192.631447900877</v>
       </c>
       <c r="N56">
-        <v>-443.9553089592819</v>
+        <v>-128.631447900877</v>
       </c>
       <c r="O56">
-        <v>-55.49441361991023</v>
+        <v>-16.07893098760962</v>
       </c>
       <c r="P56">
-        <v>-388.4608953393716</v>
+        <v>-112.5525169132674</v>
       </c>
       <c r="Q56">
-        <v>437.5391046606284</v>
+        <v>713.4474830867326</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.179852250830304</v>
+        <v>0.1789605440822764</v>
       </c>
       <c r="T56">
-        <v>2.611707616925212</v>
+        <v>2.59554685575393</v>
       </c>
       <c r="U56">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V56">
-        <v>0.1091804103153258</v>
+        <v>0.1199637372023691</v>
       </c>
       <c r="W56">
-        <v>0.1218967387091577</v>
+        <v>0.1095967387091577</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8734432825226066</v>
+        <v>0.9597098976189529</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1494666404515103</v>
+        <v>0.1422914553474176</v>
       </c>
       <c r="C57">
-        <v>4364.716233959669</v>
+        <v>6518.364522800231</v>
       </c>
       <c r="D57">
-        <v>29156.54483710976</v>
+        <v>31310.19312595033</v>
       </c>
       <c r="E57">
         <v>21407.79477924083</v>
@@ -5967,37 +5967,37 @@
         <v>3064</v>
       </c>
       <c r="M57">
-        <v>3572.917444310379</v>
+        <v>3251.754252491634</v>
       </c>
       <c r="N57">
-        <v>-508.9174443103793</v>
+        <v>-187.7542524916339</v>
       </c>
       <c r="O57">
-        <v>-63.61468053879742</v>
+        <v>-23.46928156145424</v>
       </c>
       <c r="P57">
-        <v>-445.3027637715819</v>
+        <v>-164.2849709301797</v>
       </c>
       <c r="Q57">
-        <v>380.6972362284181</v>
+        <v>661.7150290698203</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.182831189737644</v>
+        <v>0.1819196672841048</v>
       </c>
       <c r="T57">
-        <v>2.669745563967994</v>
+        <v>2.653225674770684</v>
       </c>
       <c r="U57">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V57">
-        <v>0.1071953119459563</v>
+        <v>0.1177825783441442</v>
       </c>
       <c r="W57">
-        <v>0.1221683728537645</v>
+        <v>0.1098683728537645</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8575624955676503</v>
+        <v>0.9422606267531538</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1503770066181356</v>
+        <v>0.1430788215140429</v>
       </c>
       <c r="C58">
-        <v>3636.159670072273</v>
+        <v>5790.200254132855</v>
       </c>
       <c r="D58">
-        <v>28902.73061146146</v>
+        <v>31056.77119552204</v>
       </c>
       <c r="E58">
         <v>21882.53711747993</v>
@@ -6049,37 +6049,37 @@
         <v>3064</v>
       </c>
       <c r="M58">
-        <v>3637.879579661477</v>
+        <v>3310.877057082391</v>
       </c>
       <c r="N58">
-        <v>-573.8795796614772</v>
+        <v>-246.8770570823908</v>
       </c>
       <c r="O58">
-        <v>-71.73494745768465</v>
+        <v>-30.85963213529885</v>
       </c>
       <c r="P58">
-        <v>-502.1446322037926</v>
+        <v>-216.017424947092</v>
       </c>
       <c r="Q58">
-        <v>323.8553677962074</v>
+        <v>609.982575052908</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1859455349589541</v>
+        <v>0.1850132960860162</v>
       </c>
       <c r="T58">
-        <v>2.730421599512721</v>
+        <v>2.713526258288199</v>
       </c>
       <c r="U58">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V58">
-        <v>0.1052811099469213</v>
+        <v>0.1156793180165702</v>
       </c>
       <c r="W58">
-        <v>0.1224303057789211</v>
+        <v>0.1101303057789211</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8422488795753708</v>
+        <v>0.9254345441325618</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.151287372784761</v>
+        <v>0.1438661876806683</v>
       </c>
       <c r="C59">
-        <v>2911.983988513031</v>
+        <v>5066.105397331437</v>
       </c>
       <c r="D59">
-        <v>28653.29726814131</v>
+        <v>30807.41867695972</v>
       </c>
       <c r="E59">
         <v>22357.27945571902</v>
@@ -6131,37 +6131,37 @@
         <v>3064</v>
       </c>
       <c r="M59">
-        <v>3702.841715012575</v>
+        <v>3369.999861673148</v>
       </c>
       <c r="N59">
-        <v>-638.8417150125752</v>
+        <v>-305.9998616731482</v>
       </c>
       <c r="O59">
-        <v>-79.85521437657189</v>
+        <v>-38.24998270914352</v>
       </c>
       <c r="P59">
-        <v>-558.9865006360033</v>
+        <v>-267.7498789640047</v>
       </c>
       <c r="Q59">
-        <v>267.0134993639967</v>
+        <v>558.2501210359953</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1892047334463717</v>
+        <v>0.1882508145996446</v>
       </c>
       <c r="T59">
-        <v>2.793919776245576</v>
+        <v>2.776631520108856</v>
       </c>
       <c r="U59">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V59">
-        <v>0.1034340729303087</v>
+        <v>0.1136498562969813</v>
       </c>
       <c r="W59">
-        <v>0.1226830480751248</v>
+        <v>0.1103830480751249</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8274725834424695</v>
+        <v>0.90919885037585</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1521977389513863</v>
+        <v>0.1446535538472937</v>
       </c>
       <c r="C60">
-        <v>2192.076737445383</v>
+        <v>4345.982714094625</v>
       </c>
       <c r="D60">
-        <v>28408.13235531275</v>
+        <v>30562.03833196199</v>
       </c>
       <c r="E60">
         <v>22832.02179395811</v>
@@ -6213,37 +6213,37 @@
         <v>3064</v>
       </c>
       <c r="M60">
-        <v>3767.803850363673</v>
+        <v>3429.122666263905</v>
       </c>
       <c r="N60">
-        <v>-703.8038503636726</v>
+        <v>-365.1226662639046</v>
       </c>
       <c r="O60">
-        <v>-87.97548129545908</v>
+        <v>-45.64033328298808</v>
       </c>
       <c r="P60">
-        <v>-615.8283690682135</v>
+        <v>-319.4823329809166</v>
       </c>
       <c r="Q60">
-        <v>210.1716309317865</v>
+        <v>506.5176670190834</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1926191318617614</v>
+        <v>0.1916425006615408</v>
       </c>
       <c r="T60">
-        <v>2.860441675679993</v>
+        <v>2.842741794397161</v>
       </c>
       <c r="U60">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V60">
-        <v>0.1016507268453034</v>
+        <v>0.1116903760159988</v>
       </c>
       <c r="W60">
-        <v>0.1229270751197353</v>
+        <v>0.1106270751197354</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.813205814762427</v>
+        <v>0.8935230081279907</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2046783205322366</v>
+        <v>0.145440920013919</v>
       </c>
       <c r="C61">
-        <v>-7666.421059928765</v>
+        <v>3629.738039643344</v>
       </c>
       <c r="D61">
-        <v>19024.3768961777</v>
+        <v>30320.5359957498</v>
       </c>
       <c r="E61">
         <v>23306.7641321972</v>
@@ -6295,45 +6295,45 @@
         <v>3064</v>
       </c>
       <c r="M61">
-        <v>6210.797832188209</v>
+        <v>3488.245470854662</v>
       </c>
       <c r="N61">
-        <v>-3146.797832188209</v>
+        <v>-424.2454708546616</v>
       </c>
       <c r="O61">
-        <v>-393.3497290235262</v>
+        <v>-53.0306838568327</v>
       </c>
       <c r="P61">
-        <v>-2753.448103164683</v>
+        <v>-371.2147869978289</v>
       </c>
       <c r="Q61">
-        <v>-1927.448103164683</v>
+        <v>454.7852130021711</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1998079287711335</v>
+        <v>0.1951996348240174</v>
       </c>
       <c r="T61">
-        <v>3.000499269106773</v>
+        <v>2.912076960114165</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V61">
-        <v>0.06166679553068952</v>
+        <v>0.1097973187953887</v>
       </c>
       <c r="W61">
-        <v>0.2080628300611387</v>
+        <v>0.1108628300611387</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.4933343642455161</v>
+        <v>0.8783785503631095</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2064376866988619</v>
+        <v>0.1462282861805443</v>
       </c>
       <c r="C62">
-        <v>-8349.525742895901</v>
+        <v>2917.280162237523</v>
       </c>
       <c r="D62">
-        <v>18816.01455144965</v>
+        <v>30082.82045658307</v>
       </c>
       <c r="E62">
         <v>23781.50647043629</v>
@@ -6377,45 +6377,45 @@
         <v>3064</v>
       </c>
       <c r="M62">
-        <v>6316.065592055807</v>
+        <v>3547.368275445418</v>
       </c>
       <c r="N62">
-        <v>-3252.065592055807</v>
+        <v>-483.368275445418</v>
       </c>
       <c r="O62">
-        <v>-406.5081990069758</v>
+        <v>-60.42103443067725</v>
       </c>
       <c r="P62">
-        <v>-2845.557393048831</v>
+        <v>-422.9472410147408</v>
       </c>
       <c r="Q62">
-        <v>-2019.557393048831</v>
+        <v>403.0527589852592</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.2036581269904118</v>
+        <v>0.1989346256946178</v>
       </c>
       <c r="T62">
-        <v>3.075511750834442</v>
+        <v>2.984878884117018</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V62">
-        <v>0.06063901560517802</v>
+        <v>0.1079673634821322</v>
       </c>
       <c r="W62">
-        <v>0.2082907265044953</v>
+        <v>0.1110907265044953</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.4851121248414242</v>
+        <v>0.8637389078570579</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2081970528654873</v>
+        <v>0.1470156523471697</v>
       </c>
       <c r="C63">
-        <v>-9028.115742212754</v>
+        <v>2208.520708316213</v>
       </c>
       <c r="D63">
-        <v>18612.16689037189</v>
+        <v>29848.80334090086</v>
       </c>
       <c r="E63">
         <v>24256.24880867539</v>
@@ -6459,45 +6459,45 @@
         <v>3064</v>
       </c>
       <c r="M63">
-        <v>6421.333351923404</v>
+        <v>3606.491080036175</v>
       </c>
       <c r="N63">
-        <v>-3357.333351923404</v>
+        <v>-542.4910800361754</v>
       </c>
       <c r="O63">
-        <v>-419.6666689904255</v>
+        <v>-67.81138500452192</v>
       </c>
       <c r="P63">
-        <v>-2937.666682932978</v>
+        <v>-474.6796950316535</v>
       </c>
       <c r="Q63">
-        <v>-2111.666682932978</v>
+        <v>351.3203049683465</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2077057712722173</v>
+        <v>0.2028611545585824</v>
       </c>
       <c r="T63">
-        <v>3.154371026496864</v>
+        <v>3.06141424012002</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V63">
-        <v>0.05964493338214231</v>
+        <v>0.1061974067037366</v>
       </c>
       <c r="W63">
-        <v>0.2085111509333157</v>
+        <v>0.1113111509333156</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.4771594670571385</v>
+        <v>0.8495792536298928</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2099564190321126</v>
+        <v>0.147803018513795</v>
       </c>
       <c r="C64">
-        <v>-9702.336217874537</v>
+        <v>1503.374032957428</v>
       </c>
       <c r="D64">
-        <v>18412.6887529492</v>
+        <v>29618.39900378117</v>
       </c>
       <c r="E64">
         <v>24730.99114691448</v>
@@ -6541,45 +6541,45 @@
         <v>3064</v>
       </c>
       <c r="M64">
-        <v>6526.601111791</v>
+        <v>3665.613884626932</v>
       </c>
       <c r="N64">
-        <v>-3462.601111791</v>
+        <v>-601.6138846269323</v>
       </c>
       <c r="O64">
-        <v>-432.825138973875</v>
+        <v>-75.20173557836654</v>
       </c>
       <c r="P64">
-        <v>-3029.775972817125</v>
+        <v>-526.4121490485658</v>
       </c>
       <c r="Q64">
-        <v>-2203.775972817125</v>
+        <v>299.5878509514342</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2119664494635914</v>
+        <v>0.2069943428364399</v>
       </c>
       <c r="T64">
-        <v>3.237380790352045</v>
+        <v>3.141977772754757</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V64">
-        <v>0.05868291832759163</v>
+        <v>0.1044845453052892</v>
       </c>
       <c r="W64">
-        <v>0.2087244648966901</v>
+        <v>0.1115244648966901</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.4694633466207331</v>
+        <v>0.835876362442314</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.211715785198738</v>
+        <v>0.1485903846804204</v>
       </c>
       <c r="C65">
-        <v>-10372.32617278698</v>
+        <v>801.7571153723111</v>
       </c>
       <c r="D65">
-        <v>18217.44113627585</v>
+        <v>29391.52442443514</v>
       </c>
       <c r="E65">
         <v>25205.73348515357</v>
@@ -6623,45 +6623,45 @@
         <v>3064</v>
       </c>
       <c r="M65">
-        <v>6631.868871658597</v>
+        <v>3724.736689217689</v>
       </c>
       <c r="N65">
-        <v>-3567.868871658597</v>
+        <v>-660.7366892176892</v>
       </c>
       <c r="O65">
-        <v>-445.9836089573246</v>
+        <v>-82.59208615221115</v>
       </c>
       <c r="P65">
-        <v>-3121.885262701272</v>
+        <v>-578.1446030654781</v>
       </c>
       <c r="Q65">
-        <v>-2295.885262701272</v>
+        <v>247.8553969345219</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.216457434584229</v>
+        <v>0.2113509466968842</v>
       </c>
       <c r="T65">
-        <v>3.324877568469668</v>
+        <v>3.226896090937318</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V65">
-        <v>0.05775144343350288</v>
+        <v>0.1028260604591735</v>
       </c>
       <c r="W65">
-        <v>0.2089310069882115</v>
+        <v>0.1117310069882115</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.462011547468023</v>
+        <v>0.8226084836733883</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2134751513653633</v>
+        <v>0.1493777508470457</v>
       </c>
       <c r="C66">
-        <v>-11038.218775789</v>
+        <v>103.5894591658798</v>
       </c>
       <c r="D66">
-        <v>18026.29087151292</v>
+        <v>29168.09910646781</v>
       </c>
       <c r="E66">
         <v>25680.47582339267</v>
@@ -6705,45 +6705,45 @@
         <v>3064</v>
       </c>
       <c r="M66">
-        <v>6737.136631526194</v>
+        <v>3783.859493808447</v>
       </c>
       <c r="N66">
-        <v>-3673.136631526194</v>
+        <v>-719.8594938084466</v>
       </c>
       <c r="O66">
-        <v>-459.1420789407742</v>
+        <v>-89.98243672605582</v>
       </c>
       <c r="P66">
-        <v>-3213.99455258542</v>
+        <v>-629.8770570823908</v>
       </c>
       <c r="Q66">
-        <v>-2387.99455258542</v>
+        <v>196.1229429176092</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2211979188782354</v>
+        <v>0.215949584105131</v>
       </c>
       <c r="T66">
-        <v>3.417235278704936</v>
+        <v>3.316532093463354</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V66">
-        <v>0.05684907712985439</v>
+        <v>0.1012194032644989</v>
       </c>
       <c r="W66">
-        <v>0.2091310946393727</v>
+        <v>0.1119310946393727</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.4547926170388351</v>
+        <v>0.8097552261159915</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2152345175319887</v>
+        <v>0.1692784916206388</v>
       </c>
       <c r="C67">
-        <v>-11700.14166455021</v>
+        <v>-5072.107446607519</v>
       </c>
       <c r="D67">
-        <v>17839.11032099081</v>
+        <v>24467.1445389335</v>
       </c>
       <c r="E67">
         <v>26155.21816163176</v>
@@ -6787,45 +6787,45 @@
         <v>3064</v>
       </c>
       <c r="M67">
-        <v>6842.40439139379</v>
+        <v>4713.18500439146</v>
       </c>
       <c r="N67">
-        <v>-3778.40439139379</v>
+        <v>-1649.18500439146</v>
       </c>
       <c r="O67">
-        <v>-472.3005489242238</v>
+        <v>-206.1481255489325</v>
       </c>
       <c r="P67">
-        <v>-3306.103842469567</v>
+        <v>-1443.036878842528</v>
       </c>
       <c r="Q67">
-        <v>-2480.103842469567</v>
+        <v>-617.0368788425276</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2262092879890422</v>
+        <v>0.2230492139566139</v>
       </c>
       <c r="T67">
-        <v>3.514870572382221</v>
+        <v>3.454917093802851</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V67">
-        <v>0.05597447594324125</v>
+        <v>0.08126139747180385</v>
       </c>
       <c r="W67">
-        <v>0.2093250257474214</v>
+        <v>0.1403250257474214</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.44779580754593</v>
+        <v>0.6500911797744308</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.216993883698614</v>
+        <v>0.2068914943597964</v>
       </c>
       <c r="C68">
-        <v>-12358.21722979117</v>
+        <v>-11259.6453499981</v>
       </c>
       <c r="D68">
-        <v>17655.77709398894</v>
+        <v>18754.34897378201</v>
       </c>
       <c r="E68">
         <v>26629.96049987085</v>
@@ -6869,37 +6869,37 @@
         <v>3064</v>
       </c>
       <c r="M68">
-        <v>6947.672151261388</v>
+        <v>6477.677236404686</v>
       </c>
       <c r="N68">
-        <v>-3883.672151261388</v>
+        <v>-3413.677236404686</v>
       </c>
       <c r="O68">
-        <v>-485.4590189076735</v>
+        <v>-426.7096545505857</v>
       </c>
       <c r="P68">
-        <v>-3398.213132353714</v>
+        <v>-2986.9675818541</v>
       </c>
       <c r="Q68">
-        <v>-2572.213132353714</v>
+        <v>-2160.9675818541</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2315154435181316</v>
+        <v>0.2309201807569035</v>
       </c>
       <c r="T68">
-        <v>3.618249118628756</v>
+        <v>3.608336886963296</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.05512637782288911</v>
+        <v>0.05912613210295996</v>
       </c>
       <c r="W68">
-        <v>0.2095130801552261</v>
+        <v>0.1945130801552261</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4410110225831129</v>
+        <v>0.4730090568236797</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2187532498652393</v>
+        <v>0.2085008605264217</v>
       </c>
       <c r="C69">
-        <v>-13012.56288215617</v>
+        <v>-11919.8975535067</v>
       </c>
       <c r="D69">
-        <v>17476.17377986304</v>
+        <v>18568.8391085125</v>
       </c>
       <c r="E69">
         <v>27104.70283810994</v>
@@ -6951,37 +6951,37 @@
         <v>3064</v>
       </c>
       <c r="M69">
-        <v>7052.939911128985</v>
+        <v>6575.823861198696</v>
       </c>
       <c r="N69">
-        <v>-3988.939911128985</v>
+        <v>-3511.823861198696</v>
       </c>
       <c r="O69">
-        <v>-498.6174888911231</v>
+        <v>-438.977982649837</v>
       </c>
       <c r="P69">
-        <v>-3490.322422237862</v>
+        <v>-3072.845878548859</v>
       </c>
       <c r="Q69">
-        <v>-2664.322422237862</v>
+        <v>-2246.845878548859</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2371431842308023</v>
+        <v>0.2365298832040824</v>
       </c>
       <c r="T69">
-        <v>3.727893031314476</v>
+        <v>3.717680428992487</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.05430359606433852</v>
+        <v>0.05824365251933369</v>
       </c>
       <c r="W69">
-        <v>0.2096955209986188</v>
+        <v>0.1946955209986188</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4344287685147081</v>
+        <v>0.4659492201546694</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2205126160318647</v>
+        <v>0.2101102266930471</v>
       </c>
       <c r="C70">
-        <v>-13663.29130296154</v>
+        <v>-12576.51573731063</v>
       </c>
       <c r="D70">
-        <v>17300.18769729675</v>
+        <v>18386.96326294766</v>
       </c>
       <c r="E70">
         <v>27579.44517634904</v>
@@ -7033,37 +7033,37 @@
         <v>3064</v>
       </c>
       <c r="M70">
-        <v>7158.207670996581</v>
+        <v>6673.970485992706</v>
       </c>
       <c r="N70">
-        <v>-4094.207670996581</v>
+        <v>-3609.970485992706</v>
       </c>
       <c r="O70">
-        <v>-511.7759588745727</v>
+        <v>-451.2463107490883</v>
       </c>
       <c r="P70">
-        <v>-3582.431712122009</v>
+        <v>-3158.724175243618</v>
       </c>
       <c r="Q70">
-        <v>-2756.431712122009</v>
+        <v>-2332.724175243618</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2431226587380148</v>
+        <v>0.2424901920542099</v>
       </c>
       <c r="T70">
-        <v>3.844389688543054</v>
+        <v>3.833857942398502</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05350501376927472</v>
+        <v>0.05738712821757878</v>
       </c>
       <c r="W70">
-        <v>0.2098725959348528</v>
+        <v>0.1948725959348528</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4280401101541977</v>
+        <v>0.4590970257406303</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.22227198219849</v>
+        <v>0.2117195928596725</v>
       </c>
       <c r="C71">
-        <v>-14310.51067994471</v>
+        <v>-13229.60564784277</v>
       </c>
       <c r="D71">
-        <v>17127.71065855268</v>
+        <v>18208.61569065462</v>
       </c>
       <c r="E71">
         <v>28054.18751458813</v>
@@ -7115,37 +7115,37 @@
         <v>3064</v>
       </c>
       <c r="M71">
-        <v>7263.475430864179</v>
+        <v>6772.117110786718</v>
       </c>
       <c r="N71">
-        <v>-4199.475430864179</v>
+        <v>-3708.117110786718</v>
       </c>
       <c r="O71">
-        <v>-524.9344288580223</v>
+        <v>-463.5146388483397</v>
       </c>
       <c r="P71">
-        <v>-3674.541002006156</v>
+        <v>-3244.602471938378</v>
       </c>
       <c r="Q71">
-        <v>-2848.541002006156</v>
+        <v>-2418.602471938378</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2494879057940798</v>
+        <v>0.2488350369591845</v>
       </c>
       <c r="T71">
-        <v>3.968402259141217</v>
+        <v>3.957530779250066</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05272957878711131</v>
+        <v>0.05655543070717908</v>
       </c>
       <c r="W71">
-        <v>0.2100445382642395</v>
+        <v>0.1950445382642395</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4218366302968906</v>
+        <v>0.4524434456574327</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2240313483651153</v>
+        <v>0.2133289590262978</v>
       </c>
       <c r="C72">
-        <v>-14954.32492905032</v>
+        <v>-13879.26896812547</v>
       </c>
       <c r="D72">
-        <v>16958.63874768616</v>
+        <v>18033.69470861102</v>
       </c>
       <c r="E72">
         <v>28528.92985282723</v>
@@ -7197,37 +7197,37 @@
         <v>3064</v>
       </c>
       <c r="M72">
-        <v>7368.743190731776</v>
+        <v>6870.263735580728</v>
       </c>
       <c r="N72">
-        <v>-4304.743190731776</v>
+        <v>-3806.263735580728</v>
       </c>
       <c r="O72">
-        <v>-538.092898841472</v>
+        <v>-475.782966947591</v>
       </c>
       <c r="P72">
-        <v>-3766.650291890304</v>
+        <v>-3330.480768633137</v>
       </c>
       <c r="Q72">
-        <v>-2940.650291890304</v>
+        <v>-2504.480768633137</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2562775026538825</v>
+        <v>0.2556028715244906</v>
       </c>
       <c r="T72">
-        <v>4.100682334445924</v>
+        <v>4.089448471891735</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.05197629909015258</v>
+        <v>0.05574749598279081</v>
       </c>
       <c r="W72">
-        <v>0.2102115679556437</v>
+        <v>0.1952115679556437</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4158103927212207</v>
+        <v>0.4459799678623264</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2257907145317407</v>
+        <v>0.2149383251929231</v>
       </c>
       <c r="C73">
-        <v>-15594.83390320906</v>
+        <v>-14525.6035110892</v>
       </c>
       <c r="D73">
-        <v>16792.87211176652</v>
+        <v>17862.10250388637</v>
       </c>
       <c r="E73">
         <v>29003.67219106631</v>
@@ -7279,37 +7279,37 @@
         <v>3064</v>
       </c>
       <c r="M73">
-        <v>7474.010950599371</v>
+        <v>6968.410360374737</v>
       </c>
       <c r="N73">
-        <v>-4410.010950599371</v>
+        <v>-3904.410360374737</v>
       </c>
       <c r="O73">
-        <v>-551.2513688249213</v>
+        <v>-488.0512950468421</v>
       </c>
       <c r="P73">
-        <v>-3858.759581774449</v>
+        <v>-3416.359065327895</v>
       </c>
       <c r="Q73">
-        <v>-3032.759581774449</v>
+        <v>-2590.359065327895</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2635353475729819</v>
+        <v>0.2628374533011971</v>
       </c>
       <c r="T73">
-        <v>4.242085173564749</v>
+        <v>4.230463936439724</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.05124423853958706</v>
+        <v>0.0549623199830332</v>
       </c>
       <c r="W73">
-        <v>0.2103738925853182</v>
+        <v>0.1953738925853182</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4099539083166965</v>
+        <v>0.4396985598642656</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.227550080698366</v>
+        <v>0.2165476913595484</v>
       </c>
       <c r="C74">
-        <v>-16232.13358899035</v>
+        <v>-15168.70340195848</v>
       </c>
       <c r="D74">
-        <v>16630.31476422431</v>
+        <v>17693.74495125618</v>
       </c>
       <c r="E74">
         <v>29478.4145293054</v>
@@ -7361,37 +7361,37 @@
         <v>3064</v>
       </c>
       <c r="M74">
-        <v>7579.278710466967</v>
+        <v>7066.556985168747</v>
       </c>
       <c r="N74">
-        <v>-4515.278710466967</v>
+        <v>-4002.556985168747</v>
       </c>
       <c r="O74">
-        <v>-564.4098388083709</v>
+        <v>-500.3196231460934</v>
       </c>
       <c r="P74">
-        <v>-3950.868871658596</v>
+        <v>-3502.237362022654</v>
       </c>
       <c r="Q74">
-        <v>-3124.868871658596</v>
+        <v>-2676.237362022654</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2713116099863026</v>
+        <v>0.270588790919097</v>
       </c>
       <c r="T74">
-        <v>4.393588215477775</v>
+        <v>4.381551934169715</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.05053251300431502</v>
+        <v>0.0541989544277133</v>
       </c>
       <c r="W74">
-        <v>0.2105317081975018</v>
+        <v>0.1955317081975018</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4042601040345202</v>
+        <v>0.4335916354217064</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2293094468649914</v>
+        <v>0.2181570575261738</v>
       </c>
       <c r="C75">
-        <v>-16866.31629194283</v>
+        <v>-15808.65925041966</v>
       </c>
       <c r="D75">
-        <v>16470.87439951093</v>
+        <v>17528.53144103409</v>
       </c>
       <c r="E75">
         <v>29953.15686754449</v>
@@ -7443,37 +7443,37 @@
         <v>3064</v>
       </c>
       <c r="M75">
-        <v>7684.546470334564</v>
+        <v>7164.703609962758</v>
       </c>
       <c r="N75">
-        <v>-4620.546470334564</v>
+        <v>-4100.703609962758</v>
       </c>
       <c r="O75">
-        <v>-577.5683087918205</v>
+        <v>-512.5879512453447</v>
       </c>
       <c r="P75">
-        <v>-4042.978161542744</v>
+        <v>-3588.115658717413</v>
       </c>
       <c r="Q75">
-        <v>-3216.978161542744</v>
+        <v>-2762.115658717413</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2796638918376472</v>
+        <v>0.2789143016938784</v>
       </c>
       <c r="T75">
-        <v>4.556313704939915</v>
+        <v>4.54383163543526</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.04984028679877646</v>
+        <v>0.05345650299719668</v>
       </c>
       <c r="W75">
-        <v>0.210685200094283</v>
+        <v>0.195685200094283</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3987222943902117</v>
+        <v>0.4276520239775734</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2310688130316167</v>
+        <v>0.2197664236927991</v>
       </c>
       <c r="C76">
-        <v>-17497.47081137451</v>
+        <v>-16445.55831323249</v>
       </c>
       <c r="D76">
-        <v>16314.46221831835</v>
+        <v>17366.37471646037</v>
       </c>
       <c r="E76">
         <v>30427.89920578359</v>
@@ -7525,37 +7525,37 @@
         <v>3064</v>
       </c>
       <c r="M76">
-        <v>7789.814230202162</v>
+        <v>7262.850234756769</v>
       </c>
       <c r="N76">
-        <v>-4725.814230202162</v>
+        <v>-4198.850234756769</v>
       </c>
       <c r="O76">
-        <v>-590.7267787752703</v>
+        <v>-524.8562793445961</v>
       </c>
       <c r="P76">
-        <v>-4135.087451426893</v>
+        <v>-3673.993955412173</v>
       </c>
       <c r="Q76">
-        <v>-3309.087451426893</v>
+        <v>-2847.993955412173</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2886586569083259</v>
+        <v>0.2878802363744122</v>
       </c>
       <c r="T76">
-        <v>4.731556539745296</v>
+        <v>4.718594390644308</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.04916676940960379</v>
+        <v>0.05273411782155887</v>
       </c>
       <c r="W76">
-        <v>0.2108345435614216</v>
+        <v>0.1958345435614216</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3933341552768304</v>
+        <v>0.421872942572471</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2328281791982421</v>
+        <v>0.2213757898594245</v>
       </c>
       <c r="C77">
-        <v>-18125.68260526805</v>
+        <v>-17079.48464789834</v>
       </c>
       <c r="D77">
-        <v>16160.9927626639</v>
+        <v>17207.1907200336</v>
       </c>
       <c r="E77">
         <v>30902.64154402268</v>
@@ -7607,37 +7607,37 @@
         <v>3064</v>
       </c>
       <c r="M77">
-        <v>7895.081990069759</v>
+        <v>7360.996859550779</v>
       </c>
       <c r="N77">
-        <v>-4831.081990069759</v>
+        <v>-4296.996859550779</v>
       </c>
       <c r="O77">
-        <v>-603.8852487587199</v>
+        <v>-537.1246074438474</v>
       </c>
       <c r="P77">
-        <v>-4227.196741311039</v>
+        <v>-3759.872252106932</v>
       </c>
       <c r="Q77">
-        <v>-3401.196741311039</v>
+        <v>-2933.872252106932</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.298373003184659</v>
+        <v>0.2975634458293887</v>
       </c>
       <c r="T77">
-        <v>4.920818801335108</v>
+        <v>4.907338166270081</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.04851121248414241</v>
+        <v>0.05203099625060476</v>
       </c>
       <c r="W77">
-        <v>0.2109799045361031</v>
+        <v>0.1959799045361031</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3880896998731392</v>
+        <v>0.416247970004838</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2345875453648674</v>
+        <v>0.2229851560260498</v>
       </c>
       <c r="C78">
-        <v>-18751.03394597473</v>
+        <v>-17710.51925795405</v>
       </c>
       <c r="D78">
-        <v>16010.38376019631</v>
+        <v>17050.89844821699</v>
       </c>
       <c r="E78">
         <v>31377.38388226178</v>
@@ -7689,37 +7689,37 @@
         <v>3064</v>
       </c>
       <c r="M78">
-        <v>8000.349749937355</v>
+        <v>7459.14348434479</v>
       </c>
       <c r="N78">
-        <v>-4936.349749937355</v>
+        <v>-4395.14348434479</v>
       </c>
       <c r="O78">
-        <v>-617.0437187421694</v>
+        <v>-549.3929355430987</v>
       </c>
       <c r="P78">
-        <v>-4319.306031195186</v>
+        <v>-3845.750548801691</v>
       </c>
       <c r="Q78">
-        <v>-3493.306031195186</v>
+        <v>-3019.750548801691</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3088968783173531</v>
+        <v>0.3080535894056132</v>
       </c>
       <c r="T78">
-        <v>5.125852918057404</v>
+        <v>5.111810589864668</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.04787290705671949</v>
+        <v>0.05134637787888627</v>
       </c>
       <c r="W78">
-        <v>0.2111214402219772</v>
+        <v>0.1961214402219772</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3829832564537559</v>
+        <v>0.4107710230310903</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2363469115314927</v>
+        <v>0.2245945221926751</v>
       </c>
       <c r="C79">
-        <v>-19373.60406728299</v>
+        <v>-18338.74023041859</v>
       </c>
       <c r="D79">
-        <v>15862.55597712714</v>
+        <v>16897.41981399154</v>
       </c>
       <c r="E79">
         <v>31852.12622050087</v>
@@ -7771,37 +7771,37 @@
         <v>3064</v>
       </c>
       <c r="M79">
-        <v>8105.617509804952</v>
+        <v>7557.290109138799</v>
       </c>
       <c r="N79">
-        <v>-5041.617509804952</v>
+        <v>-4493.290109138799</v>
       </c>
       <c r="O79">
-        <v>-630.202188725619</v>
+        <v>-561.6612636423499</v>
       </c>
       <c r="P79">
-        <v>-4411.415321079333</v>
+        <v>-3931.62884549645</v>
       </c>
       <c r="Q79">
-        <v>-3585.415321079333</v>
+        <v>-3105.62884549645</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3203358730268033</v>
+        <v>0.3194559193797703</v>
       </c>
       <c r="T79">
-        <v>5.348716088407727</v>
+        <v>5.33406322420661</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.04725118099104781</v>
+        <v>0.05067954180253711</v>
       </c>
       <c r="W79">
-        <v>0.2112592996562701</v>
+        <v>0.1962592996562701</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3780094479283824</v>
+        <v>0.4054363344202968</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.238106277698118</v>
+        <v>0.2262038883593005</v>
       </c>
       <c r="C80">
-        <v>-19993.46930341399</v>
+        <v>-18964.22286588311</v>
       </c>
       <c r="D80">
-        <v>15717.43307923523</v>
+        <v>16746.67951676611</v>
       </c>
       <c r="E80">
         <v>32326.86855873996</v>
@@ -7853,37 +7853,37 @@
         <v>3064</v>
       </c>
       <c r="M80">
-        <v>8210.885269672548</v>
+        <v>7655.436733932809</v>
       </c>
       <c r="N80">
-        <v>-5146.885269672548</v>
+        <v>-4591.436733932809</v>
       </c>
       <c r="O80">
-        <v>-643.3606587090685</v>
+        <v>-573.9295917416011</v>
       </c>
       <c r="P80">
-        <v>-4503.524610963479</v>
+        <v>-4017.507142191208</v>
       </c>
       <c r="Q80">
-        <v>-3677.524610963479</v>
+        <v>-3191.507142191208</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3328147763462033</v>
+        <v>0.3318948248061235</v>
       </c>
       <c r="T80">
-        <v>5.591839546971713</v>
+        <v>5.576520643488729</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.04664539661936771</v>
+        <v>0.05002980408711997</v>
       </c>
       <c r="W80">
-        <v>0.2113936242332735</v>
+        <v>0.1963936242332735</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3731631729549417</v>
+        <v>0.4002384326969598</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2398656438647434</v>
+        <v>0.2278132545259259</v>
       </c>
       <c r="C81">
-        <v>-20610.70322045659</v>
+        <v>-19587.03980169917</v>
       </c>
       <c r="D81">
-        <v>15574.94150043173</v>
+        <v>16598.60491918914</v>
       </c>
       <c r="E81">
         <v>32801.61089697906</v>
@@ -7935,37 +7935,37 @@
         <v>3064</v>
       </c>
       <c r="M81">
-        <v>8316.153029540146</v>
+        <v>7753.583358726822</v>
       </c>
       <c r="N81">
-        <v>-5252.153029540146</v>
+        <v>-4689.583358726822</v>
       </c>
       <c r="O81">
-        <v>-656.5191286925183</v>
+        <v>-586.1979198408527</v>
       </c>
       <c r="P81">
-        <v>-4595.633900847628</v>
+        <v>-4103.385438885969</v>
       </c>
       <c r="Q81">
-        <v>-3769.633900847628</v>
+        <v>-3277.385438885969</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3464821466484036</v>
+        <v>0.3455183878921294</v>
       </c>
       <c r="T81">
-        <v>5.858117620637035</v>
+        <v>5.842069245559621</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04605494856089469</v>
+        <v>0.04939651542778932</v>
       </c>
       <c r="W81">
-        <v>0.2115245481880743</v>
+        <v>0.1965245481880743</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3684395884871575</v>
+        <v>0.3951721234223146</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2416250100313688</v>
+        <v>0.2294226206925512</v>
       </c>
       <c r="C82">
-        <v>-21225.37674071701</v>
+        <v>-20207.26112868907</v>
       </c>
       <c r="D82">
-        <v>15435.0103184104</v>
+        <v>16453.12593043834</v>
       </c>
       <c r="E82">
         <v>33276.35323521815</v>
@@ -8017,37 +8017,37 @@
         <v>3064</v>
       </c>
       <c r="M82">
-        <v>8421.420789407743</v>
+        <v>7851.729983520831</v>
       </c>
       <c r="N82">
-        <v>-5357.420789407743</v>
+        <v>-4787.729983520831</v>
       </c>
       <c r="O82">
-        <v>-669.6775986759678</v>
+        <v>-598.4662479401039</v>
       </c>
       <c r="P82">
-        <v>-4687.743190731775</v>
+        <v>-4189.263735580727</v>
       </c>
       <c r="Q82">
-        <v>-3861.743190731775</v>
+        <v>-3363.263735580727</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3615162539808238</v>
+        <v>0.3605043072867359</v>
       </c>
       <c r="T82">
-        <v>6.151023501668886</v>
+        <v>6.134172707837603</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04547926170388351</v>
+        <v>0.04877905898494196</v>
       </c>
       <c r="W82">
-        <v>0.211652199044005</v>
+        <v>0.196652199044005</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3638340936310681</v>
+        <v>0.3902324718795357</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2433843761979941</v>
+        <v>0.2310319868591765</v>
       </c>
       <c r="C83">
-        <v>-21837.55826042515</v>
+        <v>-20824.95450177186</v>
       </c>
       <c r="D83">
-        <v>15297.57113694135</v>
+        <v>16310.17489559465</v>
       </c>
       <c r="E83">
         <v>33751.09557345724</v>
@@ -8099,37 +8099,37 @@
         <v>3064</v>
       </c>
       <c r="M83">
-        <v>8526.688549275339</v>
+        <v>7949.876608314842</v>
       </c>
       <c r="N83">
-        <v>-5462.688549275339</v>
+        <v>-4885.876608314842</v>
       </c>
       <c r="O83">
-        <v>-682.8360686594174</v>
+        <v>-610.7345760393553</v>
       </c>
       <c r="P83">
-        <v>-4779.852480615922</v>
+        <v>-4275.142032275487</v>
       </c>
       <c r="Q83">
-        <v>-3953.852480615922</v>
+        <v>-3449.142032275487</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3781328989271829</v>
+        <v>0.3770676918807747</v>
       </c>
       <c r="T83">
-        <v>6.474761580704091</v>
+        <v>6.457023902986951</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.0449177893371689</v>
+        <v>0.04817684838018959</v>
       </c>
       <c r="W83">
-        <v>0.2117766980269498</v>
+        <v>0.1967766980269498</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3593423146973512</v>
+        <v>0.3854147870415167</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2451437423646194</v>
+        <v>0.2326413530258019</v>
       </c>
       <c r="C84">
-        <v>-22447.31376120762</v>
+        <v>-21440.18524487219</v>
       </c>
       <c r="D84">
-        <v>15162.55797439798</v>
+        <v>16169.6864907334</v>
       </c>
       <c r="E84">
         <v>34225.83791169633</v>
@@ -8181,37 +8181,37 @@
         <v>3064</v>
       </c>
       <c r="M84">
-        <v>8631.956309142935</v>
+        <v>8048.023233108852</v>
       </c>
       <c r="N84">
-        <v>-5567.956309142935</v>
+        <v>-4984.023233108852</v>
       </c>
       <c r="O84">
-        <v>-695.9945386428669</v>
+        <v>-623.0029041386065</v>
       </c>
       <c r="P84">
-        <v>-4871.961770500068</v>
+        <v>-4361.020328970246</v>
       </c>
       <c r="Q84">
-        <v>-4045.961770500068</v>
+        <v>-3535.020328970246</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3965958377564709</v>
+        <v>0.3954714525408177</v>
       </c>
       <c r="T84">
-        <v>6.834470557409874</v>
+        <v>6.815747453152893</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04437001141842294</v>
+        <v>0.04758932583896777</v>
       </c>
       <c r="W84">
-        <v>0.211898160449335</v>
+        <v>0.196898160449335</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3549600913473835</v>
+        <v>0.3807146067117422</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2469031085312448</v>
+        <v>0.2342507191924272</v>
       </c>
       <c r="C85">
-        <v>-23054.70691570948</v>
+        <v>-22053.01645045359</v>
       </c>
       <c r="D85">
-        <v>15029.9071581352</v>
+        <v>16031.59762339109</v>
       </c>
       <c r="E85">
         <v>34700.58024993542</v>
@@ -8263,37 +8263,37 @@
         <v>3064</v>
       </c>
       <c r="M85">
-        <v>8737.224069010534</v>
+        <v>8146.169857902862</v>
       </c>
       <c r="N85">
-        <v>-5673.224069010534</v>
+        <v>-5082.169857902862</v>
       </c>
       <c r="O85">
-        <v>-709.1530086263167</v>
+        <v>-635.2712322378577</v>
       </c>
       <c r="P85">
-        <v>-4964.071060384217</v>
+        <v>-4446.898625665004</v>
       </c>
       <c r="Q85">
-        <v>-4138.071060384217</v>
+        <v>-3620.898625665004</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.4172308870362633</v>
+        <v>0.416040361513807</v>
       </c>
       <c r="T85">
-        <v>7.236498237257515</v>
+        <v>7.216673773926592</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04383543296759856</v>
+        <v>0.04701596046741394</v>
       </c>
       <c r="W85">
-        <v>0.2120166960663615</v>
+        <v>0.1970166960663615</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3506834637407885</v>
+        <v>0.3761276837393115</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2486624746978701</v>
+        <v>0.2358600853590526</v>
       </c>
       <c r="C86">
-        <v>-23659.79918771984</v>
+        <v>-22663.5090739948</v>
       </c>
       <c r="D86">
-        <v>14899.55722436393</v>
+        <v>15895.84733808897</v>
       </c>
       <c r="E86">
         <v>35175.32258817452</v>
@@ -8345,37 +8345,37 @@
         <v>3064</v>
       </c>
       <c r="M86">
-        <v>8842.49182887813</v>
+        <v>8244.316482696871</v>
       </c>
       <c r="N86">
-        <v>-5778.49182887813</v>
+        <v>-5180.316482696871</v>
       </c>
       <c r="O86">
-        <v>-722.3114786097663</v>
+        <v>-647.5395603371089</v>
       </c>
       <c r="P86">
-        <v>-5056.180350268363</v>
+        <v>-4532.776922359762</v>
       </c>
       <c r="Q86">
-        <v>-4230.180350268363</v>
+        <v>-3706.776922359762</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4404453174760296</v>
+        <v>0.4391803841084198</v>
       </c>
       <c r="T86">
-        <v>7.688779377086106</v>
+        <v>7.667715884797001</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04331358257512715</v>
+        <v>0.04645624665232569</v>
       </c>
       <c r="W86">
-        <v>0.2121324094067921</v>
+        <v>0.1971324094067921</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3465086606010173</v>
+        <v>0.3716499732186055</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2504218408644955</v>
+        <v>0.2374694515256779</v>
       </c>
       <c r="C87">
-        <v>-24262.64992713202</v>
+        <v>-23271.72202370656</v>
       </c>
       <c r="D87">
-        <v>14771.44882319084</v>
+        <v>15762.37672661631</v>
       </c>
       <c r="E87">
         <v>35650.06492641361</v>
@@ -8427,37 +8427,37 @@
         <v>3064</v>
       </c>
       <c r="M87">
-        <v>8947.759588745726</v>
+        <v>8342.463107490883</v>
       </c>
       <c r="N87">
-        <v>-5883.759588745726</v>
+        <v>-5278.463107490883</v>
       </c>
       <c r="O87">
-        <v>-735.4699485932158</v>
+        <v>-659.8078884363604</v>
       </c>
       <c r="P87">
-        <v>-5148.28964015251</v>
+        <v>-4618.655219054523</v>
       </c>
       <c r="Q87">
-        <v>-4322.28964015251</v>
+        <v>-3792.655219054523</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4667550053077649</v>
+        <v>0.4654057430489812</v>
       </c>
       <c r="T87">
-        <v>8.201364668891847</v>
+        <v>8.178896943783469</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04280401101541978</v>
+        <v>0.04590970257406302</v>
       </c>
       <c r="W87">
-        <v>0.2122454000803891</v>
+        <v>0.1972454000803891</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3424320881233582</v>
+        <v>0.3672776205925042</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2521812070311208</v>
+        <v>0.2390788176923033</v>
       </c>
       <c r="C88">
-        <v>-24863.31646004665</v>
+        <v>-23877.71224576603</v>
       </c>
       <c r="D88">
-        <v>14645.52462851531</v>
+        <v>15631.12884279593</v>
       </c>
       <c r="E88">
         <v>36124.8072646527</v>
@@ -8509,37 +8509,37 @@
         <v>3064</v>
       </c>
       <c r="M88">
-        <v>9053.027348613323</v>
+        <v>8440.609732284893</v>
       </c>
       <c r="N88">
-        <v>-5989.027348613323</v>
+        <v>-5376.609732284893</v>
       </c>
       <c r="O88">
-        <v>-748.6284185766654</v>
+        <v>-672.0762165356116</v>
       </c>
       <c r="P88">
-        <v>-5240.398930036657</v>
+        <v>-4704.533515749281</v>
       </c>
       <c r="Q88">
-        <v>-4414.398930036657</v>
+        <v>-3878.533515749281</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4968232199726052</v>
+        <v>0.4953775818381941</v>
       </c>
       <c r="T88">
-        <v>8.787176430955549</v>
+        <v>8.763103868339432</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04230628995710094</v>
+        <v>0.04537586882320183</v>
       </c>
       <c r="W88">
-        <v>0.2123557630639024</v>
+        <v>0.1973557630639024</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3384503196568075</v>
+        <v>0.3630069505856146</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2539405731977462</v>
+        <v>0.2406881838589285</v>
       </c>
       <c r="C89">
-        <v>-25461.85417430505</v>
+        <v>-24481.53480532816</v>
       </c>
       <c r="D89">
-        <v>14521.729252496</v>
+        <v>15502.04862147289</v>
       </c>
       <c r="E89">
         <v>36599.54960289179</v>
@@ -8591,37 +8591,37 @@
         <v>3064</v>
       </c>
       <c r="M89">
-        <v>9158.295108480919</v>
+        <v>8538.756357078903</v>
       </c>
       <c r="N89">
-        <v>-6094.295108480919</v>
+        <v>-5474.756357078903</v>
       </c>
       <c r="O89">
-        <v>-761.7868885601149</v>
+        <v>-684.3445446348628</v>
       </c>
       <c r="P89">
-        <v>-5332.508219920805</v>
+        <v>-4790.411812444039</v>
       </c>
       <c r="Q89">
-        <v>-4506.508219920805</v>
+        <v>-3964.411812444039</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5315173138166518</v>
+        <v>0.5299604727488243</v>
       </c>
       <c r="T89">
-        <v>9.463113079490592</v>
+        <v>9.437188781288617</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04182001076219174</v>
+        <v>0.04485430711259032</v>
       </c>
       <c r="W89">
-        <v>0.2124635889673349</v>
+        <v>0.1974635889673349</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.334560086097534</v>
+        <v>0.3588344569007226</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2556999393643715</v>
+        <v>0.2422975500255539</v>
       </c>
       <c r="C90">
-        <v>-26058.31660072093</v>
+        <v>-25083.24296355603</v>
       </c>
       <c r="D90">
-        <v>14400.00916431921</v>
+        <v>15375.08280148412</v>
       </c>
       <c r="E90">
         <v>37074.29194113088</v>
@@ -8673,37 +8673,37 @@
         <v>3064</v>
       </c>
       <c r="M90">
-        <v>9263.562868348516</v>
+        <v>8636.902981872912</v>
       </c>
       <c r="N90">
-        <v>-6199.562868348516</v>
+        <v>-5572.902981872912</v>
       </c>
       <c r="O90">
-        <v>-774.9453585435645</v>
+        <v>-696.612872734114</v>
       </c>
       <c r="P90">
-        <v>-5424.617509804952</v>
+        <v>-4876.290109138798</v>
       </c>
       <c r="Q90">
-        <v>-4598.617509804952</v>
+        <v>-4050.290109138798</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5719937566347061</v>
+        <v>0.5703071788112264</v>
       </c>
       <c r="T90">
-        <v>10.25170583611481</v>
+        <v>10.22362117972934</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04134478336716683</v>
+        <v>0.04434459907721998</v>
       </c>
       <c r="W90">
-        <v>0.2125689642820531</v>
+        <v>0.1975689642820531</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3307582669373347</v>
+        <v>0.3547567926177598</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2574593055309968</v>
+        <v>0.2439069161921792</v>
       </c>
       <c r="C91">
-        <v>-26652.7554902609</v>
+        <v>-25682.88825089645</v>
       </c>
       <c r="D91">
-        <v>14280.31261301834</v>
+        <v>15250.17985238279</v>
       </c>
       <c r="E91">
         <v>37549.03427936998</v>
@@ -8755,37 +8755,37 @@
         <v>3064</v>
       </c>
       <c r="M91">
-        <v>9368.830628216114</v>
+        <v>8735.049606666924</v>
       </c>
       <c r="N91">
-        <v>-6304.830628216114</v>
+        <v>-5671.049606666924</v>
       </c>
       <c r="O91">
-        <v>-788.1038285270142</v>
+        <v>-708.8812008333655</v>
       </c>
       <c r="P91">
-        <v>-5516.7267996891</v>
+        <v>-4962.168405833559</v>
       </c>
       <c r="Q91">
-        <v>-4690.7267996891</v>
+        <v>-4136.168405833559</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.6198295526924066</v>
+        <v>0.6179896496122471</v>
       </c>
       <c r="T91">
-        <v>11.18367909394343</v>
+        <v>11.15304128697746</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04088023523944585</v>
+        <v>0.04384634515500401</v>
       </c>
       <c r="W91">
-        <v>0.2126719716121709</v>
+        <v>0.1976719716121709</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3270418819155668</v>
+        <v>0.3507707612400321</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2592186716976221</v>
+        <v>0.2455162823588046</v>
       </c>
       <c r="C92">
-        <v>-27245.2208874073</v>
+        <v>-26280.52053681283</v>
       </c>
       <c r="D92">
-        <v>14162.58955411104</v>
+        <v>15127.2899047055</v>
       </c>
       <c r="E92">
         <v>38023.77661760907</v>
@@ -8837,37 +8837,37 @@
         <v>3064</v>
       </c>
       <c r="M92">
-        <v>9474.09838808371</v>
+        <v>8833.196231460935</v>
       </c>
       <c r="N92">
-        <v>-6410.09838808371</v>
+        <v>-5769.196231460935</v>
       </c>
       <c r="O92">
-        <v>-801.2622985104638</v>
+        <v>-721.1495289326169</v>
       </c>
       <c r="P92">
-        <v>-5608.836089573247</v>
+        <v>-5048.046702528319</v>
       </c>
       <c r="Q92">
-        <v>-4782.836089573247</v>
+        <v>-4222.046702528319</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6772325079616475</v>
+        <v>0.6752086145734718</v>
       </c>
       <c r="T92">
-        <v>12.30204700333777</v>
+        <v>12.26834541567521</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04042601040345201</v>
+        <v>0.04335916354217063</v>
       </c>
       <c r="W92">
-        <v>0.2127726898905082</v>
+        <v>0.1977726898905083</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.323408083227616</v>
+        <v>0.3468733083373651</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2609780378642475</v>
+        <v>0.24712564852543</v>
       </c>
       <c r="C93">
-        <v>-27835.76119992211</v>
+        <v>-26876.18809617342</v>
       </c>
       <c r="D93">
-        <v>14046.79157983531</v>
+        <v>15006.364683584</v>
       </c>
       <c r="E93">
         <v>38498.51895584817</v>
@@ -8919,37 +8919,37 @@
         <v>3064</v>
       </c>
       <c r="M93">
-        <v>9579.366147951307</v>
+        <v>8931.342856254945</v>
       </c>
       <c r="N93">
-        <v>-6515.366147951307</v>
+        <v>-5867.342856254945</v>
       </c>
       <c r="O93">
-        <v>-814.4207684939133</v>
+        <v>-733.4178570318682</v>
       </c>
       <c r="P93">
-        <v>-5700.945379457393</v>
+        <v>-5133.924999223077</v>
       </c>
       <c r="Q93">
-        <v>-4874.945379457393</v>
+        <v>-4307.924999223077</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7473916755129417</v>
+        <v>0.7451429050816354</v>
       </c>
       <c r="T93">
-        <v>13.66894111481975</v>
+        <v>13.63149490630579</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.03998176853088661</v>
+        <v>0.0428826892175314</v>
       </c>
       <c r="W93">
-        <v>0.2128711945803107</v>
+        <v>0.1978711945803107</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3198541482470928</v>
+        <v>0.3430615137402512</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2627374040308729</v>
+        <v>0.2487350146920553</v>
       </c>
       <c r="C94">
-        <v>-28424.42326521612</v>
+        <v>-27469.93767248057</v>
       </c>
       <c r="D94">
-        <v>13932.87185278039</v>
+        <v>14887.35744551595</v>
       </c>
       <c r="E94">
         <v>38973.26129408726</v>
@@ -9001,37 +9001,37 @@
         <v>3064</v>
       </c>
       <c r="M94">
-        <v>9684.633907818903</v>
+        <v>9029.489481048955</v>
       </c>
       <c r="N94">
-        <v>-6620.633907818903</v>
+        <v>-5965.489481048955</v>
       </c>
       <c r="O94">
-        <v>-827.5792384773629</v>
+        <v>-745.6861851311194</v>
       </c>
       <c r="P94">
-        <v>-5793.05466934154</v>
+        <v>-5219.803295917835</v>
       </c>
       <c r="Q94">
-        <v>-4967.05466934154</v>
+        <v>-4393.803295917835</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.8350906349520596</v>
+        <v>0.8325607682168401</v>
       </c>
       <c r="T94">
-        <v>15.37755875417222</v>
+        <v>15.33543176959401</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03954718409033349</v>
+        <v>0.04241657303038432</v>
       </c>
       <c r="W94">
-        <v>0.2129675578638132</v>
+        <v>0.1979675578638131</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3163774727226679</v>
+        <v>0.3393325842430746</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2644967701974982</v>
+        <v>0.2503443808586806</v>
       </c>
       <c r="C95">
-        <v>-29011.25241351451</v>
+        <v>-28061.81453811508</v>
       </c>
       <c r="D95">
-        <v>13820.7850427211</v>
+        <v>14770.22291812052</v>
       </c>
       <c r="E95">
         <v>39448.00363232635</v>
@@ -9083,37 +9083,37 @@
         <v>3064</v>
       </c>
       <c r="M95">
-        <v>9789.901667686499</v>
+        <v>9127.636105842965</v>
       </c>
       <c r="N95">
-        <v>-6725.901667686499</v>
+        <v>-6063.636105842965</v>
       </c>
       <c r="O95">
-        <v>-840.7377084608124</v>
+        <v>-757.9545132303706</v>
       </c>
       <c r="P95">
-        <v>-5885.163959225687</v>
+        <v>-5305.681592612595</v>
       </c>
       <c r="Q95">
-        <v>-5059.163959225687</v>
+        <v>-4479.681592612595</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.9478464399452111</v>
+        <v>0.9449551636763888</v>
       </c>
       <c r="T95">
-        <v>17.57435286191111</v>
+        <v>17.52620773667887</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03912194555172776</v>
+        <v>0.04196048084726191</v>
       </c>
       <c r="W95">
-        <v>0.2130618488186381</v>
+        <v>0.1980618488186381</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.312975564413822</v>
+        <v>0.3356838467780953</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2662561363641235</v>
+        <v>0.2519537470253059</v>
       </c>
       <c r="C96">
-        <v>-29596.29252799787</v>
+        <v>-28651.86255175876</v>
       </c>
       <c r="D96">
-        <v>13710.48726647684</v>
+        <v>14654.91724271595</v>
       </c>
       <c r="E96">
         <v>39922.74597056545</v>
@@ -9165,37 +9165,37 @@
         <v>3064</v>
       </c>
       <c r="M96">
-        <v>9895.169427554098</v>
+        <v>9225.782730636976</v>
       </c>
       <c r="N96">
-        <v>-6831.169427554098</v>
+        <v>-6161.782730636976</v>
       </c>
       <c r="O96">
-        <v>-853.8961784442622</v>
+        <v>-770.222841329622</v>
       </c>
       <c r="P96">
-        <v>-5977.273249109836</v>
+        <v>-5391.559889307355</v>
       </c>
       <c r="Q96">
-        <v>-5151.273249109836</v>
+        <v>-4565.559889307355</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.098187513269413</v>
+        <v>1.094814357622454</v>
       </c>
       <c r="T96">
-        <v>20.50341167222964</v>
+        <v>20.44724235945869</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03870575464160299</v>
+        <v>0.0415140927531421</v>
       </c>
       <c r="W96">
-        <v>0.2131541335829349</v>
+        <v>0.1981541335829349</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3096460371328239</v>
+        <v>0.3321127420251367</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2680155025307489</v>
+        <v>0.2535631131919314</v>
       </c>
       <c r="C97">
-        <v>-30179.58610208627</v>
+        <v>-29240.12421314803</v>
       </c>
       <c r="D97">
-        <v>13601.93603062753</v>
+        <v>14541.39791956577</v>
       </c>
       <c r="E97">
         <v>40397.48830880454</v>
@@ -9247,37 +9247,37 @@
         <v>3064</v>
       </c>
       <c r="M97">
-        <v>10000.43718742169</v>
+        <v>9323.929355430988</v>
       </c>
       <c r="N97">
-        <v>-6936.437187421694</v>
+        <v>-6259.929355430988</v>
       </c>
       <c r="O97">
-        <v>-867.0546484277118</v>
+        <v>-782.4911694288735</v>
       </c>
       <c r="P97">
-        <v>-6069.382538993982</v>
+        <v>-5477.438186002115</v>
       </c>
       <c r="Q97">
-        <v>-5243.382538993982</v>
+        <v>-4651.438186002115</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.308665015923297</v>
+        <v>1.304617229146946</v>
       </c>
       <c r="T97">
-        <v>24.60409400667558</v>
+        <v>24.53669083135044</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03829832564537559</v>
+        <v>0.04107710230310901</v>
       </c>
       <c r="W97">
-        <v>0.2132444755100886</v>
+        <v>0.1982444755100886</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3063866051630048</v>
+        <v>0.3286168184248721</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2697748686973742</v>
+        <v>0.2551724793585566</v>
       </c>
       <c r="C98">
-        <v>-30761.17429402344</v>
+        <v>-29826.64071530246</v>
       </c>
       <c r="D98">
-        <v>13495.09017692944</v>
+        <v>14429.62375565043</v>
       </c>
       <c r="E98">
         <v>40872.23064704362</v>
@@ -9329,37 +9329,37 @@
         <v>3064</v>
       </c>
       <c r="M98">
-        <v>10105.70494728929</v>
+        <v>9422.075980224996</v>
       </c>
       <c r="N98">
-        <v>-7041.70494728929</v>
+        <v>-6358.075980224996</v>
       </c>
       <c r="O98">
-        <v>-880.2131184111613</v>
+        <v>-794.7594975281245</v>
       </c>
       <c r="P98">
-        <v>-6161.491828878129</v>
+        <v>-5563.316482696871</v>
       </c>
       <c r="Q98">
-        <v>-5335.491828878129</v>
+        <v>-4737.316482696871</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.624381269904117</v>
+        <v>1.619321536433678</v>
       </c>
       <c r="T98">
-        <v>30.7551175083444</v>
+        <v>30.67086353918798</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03789938475323626</v>
+        <v>0.04064921582078498</v>
       </c>
       <c r="W98">
-        <v>0.2133329353137599</v>
+        <v>0.1983329353137599</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3031950780258901</v>
+        <v>0.3251937265662798</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2715342348639995</v>
+        <v>0.256781845525182</v>
       </c>
       <c r="C99">
-        <v>-31341.09697890846</v>
+        <v>-30411.45199436283</v>
       </c>
       <c r="D99">
-        <v>13389.90983028352</v>
+        <v>14319.55481482914</v>
       </c>
       <c r="E99">
         <v>41346.97298528271</v>
@@ -9411,37 +9411,37 @@
         <v>3064</v>
       </c>
       <c r="M99">
-        <v>10210.97270715689</v>
+        <v>9520.222605019006</v>
       </c>
       <c r="N99">
-        <v>-7146.972707156887</v>
+        <v>-6456.222605019006</v>
       </c>
       <c r="O99">
-        <v>-893.3715883946109</v>
+        <v>-807.0278256273757</v>
       </c>
       <c r="P99">
-        <v>-6253.601118762276</v>
+        <v>-5649.19477939163</v>
       </c>
       <c r="Q99">
-        <v>-5427.601118762276</v>
+        <v>-4823.19477939163</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.150575026538823</v>
+        <v>2.143828715244904</v>
       </c>
       <c r="T99">
-        <v>41.0068233444592</v>
+        <v>40.89448471891731</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03750866944650187</v>
+        <v>0.04023015174015833</v>
       </c>
       <c r="W99">
-        <v>0.2134195712039534</v>
+        <v>0.1984195712039534</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.300069355572015</v>
+        <v>0.3218412139212666</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2732936010306249</v>
+        <v>0.2583912116918073</v>
       </c>
       <c r="C100">
-        <v>-31919.39279831291</v>
+        <v>-30994.5967771655</v>
       </c>
       <c r="D100">
-        <v>13286.35634911816</v>
+        <v>14211.15237026558</v>
       </c>
       <c r="E100">
         <v>41821.71532352181</v>
@@ -9493,37 +9493,37 @@
         <v>3064</v>
       </c>
       <c r="M100">
-        <v>10316.24046702449</v>
+        <v>9618.369229813017</v>
       </c>
       <c r="N100">
-        <v>-7252.240467024485</v>
+        <v>-6554.369229813017</v>
       </c>
       <c r="O100">
-        <v>-906.5300583780606</v>
+        <v>-819.2961537266272</v>
       </c>
       <c r="P100">
-        <v>-6345.710408646424</v>
+        <v>-5735.07307608639</v>
       </c>
       <c r="Q100">
-        <v>-5519.710408646424</v>
+        <v>-4909.07307608639</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.202962539808234</v>
+        <v>3.192843072867356</v>
       </c>
       <c r="T100">
-        <v>61.5102350166888</v>
+        <v>61.34172707837596</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03712592792153756</v>
+        <v>0.03981963998770773</v>
       </c>
       <c r="W100">
-        <v>0.2135044390147553</v>
+        <v>0.1985044390147552</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2970074233723005</v>
+        <v>0.3185571199016618</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2750529671972503</v>
+        <v>0.2600005778584327</v>
       </c>
       <c r="C101">
-        <v>-32496.09920761353</v>
+        <v>-31576.11262667205</v>
       </c>
       <c r="D101">
-        <v>13184.39227805663</v>
+        <v>14104.37885899812</v>
       </c>
       <c r="E101">
         <v>42296.45766176091</v>
@@ -9575,37 +9575,37 @@
         <v>3064</v>
       </c>
       <c r="M101">
-        <v>10421.50822689208</v>
+        <v>9716.515854607029</v>
       </c>
       <c r="N101">
-        <v>-7357.508226892081</v>
+        <v>-6652.515854607029</v>
       </c>
       <c r="O101">
-        <v>-919.6885283615102</v>
+        <v>-831.5644818258786</v>
       </c>
       <c r="P101">
-        <v>-6437.819698530571</v>
+        <v>-5820.95137278115</v>
       </c>
       <c r="Q101">
-        <v>-5611.819698530571</v>
+        <v>-4994.95137278115</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>6.360125079616469</v>
+        <v>6.339886145734711</v>
       </c>
       <c r="T101">
-        <v>123.0204700333776</v>
+        <v>122.6834541567519</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.03675091854859273</v>
+        <v>0.0394174214019733</v>
       </c>
       <c r="W101">
-        <v>0.2135875923243288</v>
+        <v>0.1985875923243288</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2940073483887419</v>
+        <v>0.3153393712157864</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_electronics_general.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1112967576199604</v>
+        <v>0.1112489570687326</v>
       </c>
       <c r="C2">
-        <v>47445.95668786737</v>
+        <v>47004.90310579629</v>
       </c>
       <c r="D2">
-        <v>46126.95668786737</v>
+        <v>46160.64544403538</v>
       </c>
       <c r="E2">
-        <v>-4703.033823909261</v>
+        <v>-4228.291485670168</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>474.7423382390926</v>
       </c>
       <c r="G2">
         <v>1319</v>
@@ -1457,28 +1457,28 @@
         <v>3064</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>26.69790288902695</v>
       </c>
       <c r="N2">
-        <v>3064</v>
+        <v>3037.302097110973</v>
       </c>
       <c r="O2">
-        <v>383</v>
+        <v>379.6627621388716</v>
       </c>
       <c r="P2">
-        <v>2681</v>
+        <v>2657.639334972102</v>
       </c>
       <c r="Q2">
-        <v>3507</v>
+        <v>3483.639334972102</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1112967576199604</v>
+        <v>0.1118756431039752</v>
       </c>
       <c r="T2">
-        <v>1.276653715063877</v>
+        <v>1.287937270626311</v>
       </c>
       <c r="U2">
         <v>0.05623661666253409</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>114.7655683944872</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1112489570687326</v>
+        <v>0.1112011565175048</v>
       </c>
       <c r="C3">
-        <v>47004.90310579629</v>
+        <v>46563.89876876006</v>
       </c>
       <c r="D3">
-        <v>46160.64544403538</v>
+        <v>46194.38344523824</v>
       </c>
       <c r="E3">
-        <v>-4228.291485670168</v>
+        <v>-3753.549147431076</v>
       </c>
       <c r="F3">
-        <v>474.7423382390926</v>
+        <v>949.4846764781852</v>
       </c>
       <c r="G3">
         <v>1319</v>
@@ -1539,28 +1539,28 @@
         <v>3064</v>
       </c>
       <c r="M3">
-        <v>26.69790288902695</v>
+        <v>53.3958057780539</v>
       </c>
       <c r="N3">
-        <v>3037.302097110973</v>
+        <v>3010.604194221946</v>
       </c>
       <c r="O3">
-        <v>379.6627621388716</v>
+        <v>376.3255242777433</v>
       </c>
       <c r="P3">
-        <v>2657.639334972102</v>
+        <v>2634.278669944203</v>
       </c>
       <c r="Q3">
-        <v>3483.639334972102</v>
+        <v>3460.278669944203</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1118756431039752</v>
+        <v>0.1124663425774597</v>
       </c>
       <c r="T3">
-        <v>1.287937270626311</v>
+        <v>1.299451102832875</v>
       </c>
       <c r="U3">
         <v>0.05623661666253409</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>114.7655683944872</v>
+        <v>57.38278419724361</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1112011565175048</v>
+        <v>0.111153355966277</v>
       </c>
       <c r="C4">
-        <v>46563.89876876006</v>
+        <v>46122.94378481458</v>
       </c>
       <c r="D4">
-        <v>46194.38344523824</v>
+        <v>46228.17079953186</v>
       </c>
       <c r="E4">
-        <v>-3753.549147431076</v>
+        <v>-3278.806809191983</v>
       </c>
       <c r="F4">
-        <v>949.4846764781852</v>
+        <v>1424.227014717278</v>
       </c>
       <c r="G4">
         <v>1319</v>
@@ -1621,28 +1621,28 @@
         <v>3064</v>
       </c>
       <c r="M4">
-        <v>53.3958057780539</v>
+        <v>80.09370866708083</v>
       </c>
       <c r="N4">
-        <v>3010.604194221946</v>
+        <v>2983.906291332919</v>
       </c>
       <c r="O4">
-        <v>376.3255242777433</v>
+        <v>372.9882864166149</v>
       </c>
       <c r="P4">
-        <v>2634.278669944203</v>
+        <v>2610.918004916304</v>
       </c>
       <c r="Q4">
-        <v>3460.278669944203</v>
+        <v>3436.918004916304</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1124663425774597</v>
+        <v>0.1130692214215314</v>
       </c>
       <c r="T4">
-        <v>1.299451102832875</v>
+        <v>1.311202333641637</v>
       </c>
       <c r="U4">
         <v>0.05623661666253409</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>57.38278419724361</v>
+        <v>38.25518946482907</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.111153355966277</v>
+        <v>0.1111055554150492</v>
       </c>
       <c r="C5">
-        <v>46122.94378481458</v>
+        <v>45682.03826233221</v>
       </c>
       <c r="D5">
-        <v>46228.17079953186</v>
+        <v>46262.00761528858</v>
       </c>
       <c r="E5">
-        <v>-3278.806809191983</v>
+        <v>-2804.064470952891</v>
       </c>
       <c r="F5">
-        <v>1424.227014717278</v>
+        <v>1898.96935295637</v>
       </c>
       <c r="G5">
         <v>1319</v>
@@ -1703,28 +1703,28 @@
         <v>3064</v>
       </c>
       <c r="M5">
-        <v>80.09370866708083</v>
+        <v>106.7916115561078</v>
       </c>
       <c r="N5">
-        <v>2983.906291332919</v>
+        <v>2957.208388443892</v>
       </c>
       <c r="O5">
-        <v>372.9882864166149</v>
+        <v>369.6510485554865</v>
       </c>
       <c r="P5">
-        <v>2610.918004916304</v>
+        <v>2587.557339888406</v>
       </c>
       <c r="Q5">
-        <v>3436.918004916304</v>
+        <v>3413.557339888406</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1130692214215314</v>
+        <v>0.1136846602415214</v>
       </c>
       <c r="T5">
-        <v>1.311202333641637</v>
+        <v>1.323198381758914</v>
       </c>
       <c r="U5">
         <v>0.05623661666253409</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.25518946482907</v>
+        <v>28.6913920986218</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1111055554150492</v>
+        <v>0.1110577548638215</v>
       </c>
       <c r="C6">
-        <v>45682.03826233221</v>
+        <v>45241.18231000279</v>
       </c>
       <c r="D6">
-        <v>46262.00761528858</v>
+        <v>46295.89400119826</v>
       </c>
       <c r="E6">
-        <v>-2804.064470952891</v>
+        <v>-2329.322132713798</v>
       </c>
       <c r="F6">
-        <v>1898.96935295637</v>
+        <v>2373.711691195463</v>
       </c>
       <c r="G6">
         <v>1319</v>
@@ -1785,28 +1785,28 @@
         <v>3064</v>
       </c>
       <c r="M6">
-        <v>106.7916115561078</v>
+        <v>133.4895144451347</v>
       </c>
       <c r="N6">
-        <v>2957.208388443892</v>
+        <v>2930.510485554865</v>
       </c>
       <c r="O6">
-        <v>369.6510485554865</v>
+        <v>366.3138106943582</v>
       </c>
       <c r="P6">
-        <v>2587.557339888406</v>
+        <v>2564.196674860507</v>
       </c>
       <c r="Q6">
-        <v>3413.557339888406</v>
+        <v>3390.196674860507</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1136846602415214</v>
+        <v>0.114313055668248</v>
       </c>
       <c r="T6">
-        <v>1.323198381758914</v>
+        <v>1.335446978257608</v>
       </c>
       <c r="U6">
         <v>0.05623661666253409</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.6913920986218</v>
+        <v>22.95311367889744</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1110577548638215</v>
+        <v>0.1110099543125937</v>
       </c>
       <c r="C7">
-        <v>45241.18231000279</v>
+        <v>44800.37603683486</v>
       </c>
       <c r="D7">
-        <v>46295.89400119826</v>
+        <v>46329.83006626942</v>
       </c>
       <c r="E7">
-        <v>-2329.322132713798</v>
+        <v>-1854.579794474705</v>
       </c>
       <c r="F7">
-        <v>2373.711691195463</v>
+        <v>2848.454029434556</v>
       </c>
       <c r="G7">
         <v>1319</v>
@@ -1867,28 +1867,28 @@
         <v>3064</v>
       </c>
       <c r="M7">
-        <v>133.4895144451347</v>
+        <v>160.1874173341617</v>
       </c>
       <c r="N7">
-        <v>2930.510485554865</v>
+        <v>2903.812582665838</v>
       </c>
       <c r="O7">
-        <v>366.3138106943582</v>
+        <v>362.9765728332298</v>
       </c>
       <c r="P7">
-        <v>2564.196674860507</v>
+        <v>2540.836009832608</v>
       </c>
       <c r="Q7">
-        <v>3390.196674860507</v>
+        <v>3366.836009832608</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.114313055668248</v>
+        <v>0.1149548212104369</v>
       </c>
       <c r="T7">
-        <v>1.335446978257608</v>
+        <v>1.347956183192445</v>
       </c>
       <c r="U7">
         <v>0.05623661666253409</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.95311367889744</v>
+        <v>19.12759473241454</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1110099543125937</v>
+        <v>0.1109621537613659</v>
       </c>
       <c r="C8">
-        <v>44800.37603683486</v>
+        <v>44359.61955215682</v>
       </c>
       <c r="D8">
-        <v>46329.83006626942</v>
+        <v>46363.81591983046</v>
       </c>
       <c r="E8">
-        <v>-1854.579794474706</v>
+        <v>-1379.837456235613</v>
       </c>
       <c r="F8">
-        <v>2848.454029434555</v>
+        <v>3323.196367673648</v>
       </c>
       <c r="G8">
         <v>1319</v>
@@ -1949,28 +1949,28 @@
         <v>3064</v>
       </c>
       <c r="M8">
-        <v>160.1874173341617</v>
+        <v>186.8853202231886</v>
       </c>
       <c r="N8">
-        <v>2903.812582665838</v>
+        <v>2877.114679776811</v>
       </c>
       <c r="O8">
-        <v>362.9765728332298</v>
+        <v>359.6393349721014</v>
       </c>
       <c r="P8">
-        <v>2540.836009832608</v>
+        <v>2517.47534480471</v>
       </c>
       <c r="Q8">
-        <v>3366.836009832608</v>
+        <v>3343.47534480471</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1149548212104369</v>
+        <v>0.1156103881621352</v>
       </c>
       <c r="T8">
-        <v>1.347956183192445</v>
+        <v>1.36073440328717</v>
       </c>
       <c r="U8">
         <v>0.05623661666253409</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.12759473241454</v>
+        <v>16.39508119921246</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1109621537613659</v>
+        <v>0.1109143532101382</v>
       </c>
       <c r="C9">
-        <v>44359.61955215682</v>
+        <v>43918.9129656181</v>
       </c>
       <c r="D9">
-        <v>46363.81591983047</v>
+        <v>46397.85167153084</v>
       </c>
       <c r="E9">
-        <v>-1379.837456235613</v>
+        <v>-905.09511799652</v>
       </c>
       <c r="F9">
-        <v>3323.196367673648</v>
+        <v>3797.938705912741</v>
       </c>
       <c r="G9">
         <v>1319</v>
@@ -2031,28 +2031,28 @@
         <v>3064</v>
       </c>
       <c r="M9">
-        <v>186.8853202231886</v>
+        <v>213.5832231122156</v>
       </c>
       <c r="N9">
-        <v>2877.114679776811</v>
+        <v>2850.416776887784</v>
       </c>
       <c r="O9">
-        <v>359.6393349721014</v>
+        <v>356.302097110973</v>
       </c>
       <c r="P9">
-        <v>2517.47534480471</v>
+        <v>2494.114679776811</v>
       </c>
       <c r="Q9">
-        <v>3343.47534480471</v>
+        <v>3320.114679776811</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1156103881621352</v>
+        <v>0.1162802065693052</v>
       </c>
       <c r="T9">
-        <v>1.36073440328717</v>
+        <v>1.373790410775259</v>
       </c>
       <c r="U9">
         <v>0.05623661666253409</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.39508119921246</v>
+        <v>14.3456960493109</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1109143532101382</v>
+        <v>0.1108665526589104</v>
       </c>
       <c r="C10">
-        <v>43918.9129656181</v>
+        <v>43478.25638719035</v>
       </c>
       <c r="D10">
-        <v>46397.85167153084</v>
+        <v>46431.93743134219</v>
       </c>
       <c r="E10">
-        <v>-905.09511799652</v>
+        <v>-430.3527797574279</v>
       </c>
       <c r="F10">
-        <v>3797.938705912741</v>
+        <v>4272.681044151833</v>
       </c>
       <c r="G10">
         <v>1319</v>
@@ -2113,28 +2113,28 @@
         <v>3064</v>
       </c>
       <c r="M10">
-        <v>213.5832231122156</v>
+        <v>240.2811260012425</v>
       </c>
       <c r="N10">
-        <v>2850.416776887784</v>
+        <v>2823.718873998757</v>
       </c>
       <c r="O10">
-        <v>356.302097110973</v>
+        <v>352.9648592498447</v>
       </c>
       <c r="P10">
-        <v>2494.114679776811</v>
+        <v>2470.754014748913</v>
       </c>
       <c r="Q10">
-        <v>3320.114679776811</v>
+        <v>3296.754014748913</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1162802065693052</v>
+        <v>0.1169647462601492</v>
       </c>
       <c r="T10">
-        <v>1.373790410775259</v>
+        <v>1.387133363482866</v>
       </c>
       <c r="U10">
         <v>0.05623661666253409</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.3456960493109</v>
+        <v>12.75172982160969</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1108665526589104</v>
+        <v>0.1108187521076826</v>
       </c>
       <c r="C11">
-        <v>43478.25638719035</v>
+        <v>43037.64992716863</v>
       </c>
       <c r="D11">
-        <v>46431.93743134219</v>
+        <v>46466.07330955955</v>
       </c>
       <c r="E11">
-        <v>-430.3527797574279</v>
+        <v>44.38955848166461</v>
       </c>
       <c r="F11">
-        <v>4272.681044151833</v>
+        <v>4747.423382390925</v>
       </c>
       <c r="G11">
         <v>1319</v>
@@ -2195,28 +2195,28 @@
         <v>3064</v>
       </c>
       <c r="M11">
-        <v>240.2811260012425</v>
+        <v>266.9790288902694</v>
       </c>
       <c r="N11">
-        <v>2823.718873998757</v>
+        <v>2797.02097110973</v>
       </c>
       <c r="O11">
-        <v>352.9648592498447</v>
+        <v>349.6276213887163</v>
       </c>
       <c r="P11">
-        <v>2470.754014748913</v>
+        <v>2447.393349721014</v>
       </c>
       <c r="Q11">
-        <v>3296.754014748913</v>
+        <v>3273.393349721014</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1169647462601492</v>
+        <v>0.1176644979441232</v>
       </c>
       <c r="T11">
-        <v>1.387133363482866</v>
+        <v>1.400772826250643</v>
       </c>
       <c r="U11">
         <v>0.05623661666253409</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.75172982160969</v>
+        <v>11.47655683944872</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1108187521076826</v>
+        <v>0.1107709515564548</v>
       </c>
       <c r="C12">
-        <v>43037.64992716863</v>
+        <v>42597.09369617249</v>
       </c>
       <c r="D12">
-        <v>46466.07330955955</v>
+        <v>46500.25941680251</v>
       </c>
       <c r="E12">
-        <v>44.38955848166552</v>
+        <v>519.1318967207571</v>
       </c>
       <c r="F12">
-        <v>4747.423382390926</v>
+        <v>5222.165720630018</v>
       </c>
       <c r="G12">
         <v>1319</v>
@@ -2277,28 +2277,28 @@
         <v>3064</v>
       </c>
       <c r="M12">
-        <v>266.9790288902695</v>
+        <v>293.6769317792964</v>
       </c>
       <c r="N12">
-        <v>2797.02097110973</v>
+        <v>2770.323068220704</v>
       </c>
       <c r="O12">
-        <v>349.6276213887163</v>
+        <v>346.2903835275879</v>
       </c>
       <c r="P12">
-        <v>2447.393349721014</v>
+        <v>2424.032684693116</v>
       </c>
       <c r="Q12">
-        <v>3273.393349721014</v>
+        <v>3250.032684693116</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1176644979441232</v>
+        <v>0.1183799743850404</v>
       </c>
       <c r="T12">
-        <v>1.400772826250643</v>
+        <v>1.414718793799718</v>
       </c>
       <c r="U12">
         <v>0.05623661666253409</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.47655683944872</v>
+        <v>10.43323349040793</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1107709515564548</v>
+        <v>0.110723151005227</v>
       </c>
       <c r="C13">
-        <v>42597.09369617249</v>
+        <v>42156.58780514741</v>
       </c>
       <c r="D13">
-        <v>46500.25941680251</v>
+        <v>46534.49586401653</v>
       </c>
       <c r="E13">
-        <v>519.1318967207571</v>
+        <v>993.8742349598497</v>
       </c>
       <c r="F13">
-        <v>5222.165720630018</v>
+        <v>5696.90805886911</v>
       </c>
       <c r="G13">
         <v>1319</v>
@@ -2359,28 +2359,28 @@
         <v>3064</v>
       </c>
       <c r="M13">
-        <v>293.6769317792964</v>
+        <v>320.3748346683233</v>
       </c>
       <c r="N13">
-        <v>2770.323068220704</v>
+        <v>2743.625165331677</v>
       </c>
       <c r="O13">
-        <v>346.2903835275879</v>
+        <v>342.9531456664596</v>
       </c>
       <c r="P13">
-        <v>2424.032684693116</v>
+        <v>2400.672019665217</v>
       </c>
       <c r="Q13">
-        <v>3250.032684693116</v>
+        <v>3226.672019665217</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1183799743850404</v>
+        <v>0.1191117116541602</v>
       </c>
       <c r="T13">
-        <v>1.414718793799718</v>
+        <v>1.428981715156726</v>
       </c>
       <c r="U13">
         <v>0.05623661666253409</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.43323349040793</v>
+        <v>9.56379736620727</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.110723151005227</v>
+        <v>0.1106753504539993</v>
       </c>
       <c r="C14">
-        <v>42156.58780514741</v>
+        <v>41716.13236536575</v>
       </c>
       <c r="D14">
-        <v>46534.49586401653</v>
+        <v>46568.78276247396</v>
       </c>
       <c r="E14">
-        <v>993.8742349598497</v>
+        <v>1468.616573198943</v>
       </c>
       <c r="F14">
-        <v>5696.90805886911</v>
+        <v>6171.650397108204</v>
       </c>
       <c r="G14">
         <v>1319</v>
@@ -2441,28 +2441,28 @@
         <v>3064</v>
       </c>
       <c r="M14">
-        <v>320.3748346683233</v>
+        <v>347.0727375573503</v>
       </c>
       <c r="N14">
-        <v>2743.625165331677</v>
+        <v>2716.92726244265</v>
       </c>
       <c r="O14">
-        <v>342.9531456664596</v>
+        <v>339.6159078053312</v>
       </c>
       <c r="P14">
-        <v>2400.672019665217</v>
+        <v>2377.311354637319</v>
       </c>
       <c r="Q14">
-        <v>3226.672019665217</v>
+        <v>3203.311354637319</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1191117116541602</v>
+        <v>0.1198602704696966</v>
       </c>
       <c r="T14">
-        <v>1.428981715156726</v>
+        <v>1.443572519763321</v>
       </c>
       <c r="U14">
         <v>0.05623661666253409</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.56379736620727</v>
+        <v>8.828120645729786</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1106753504539993</v>
+        <v>0.1108112999027715</v>
       </c>
       <c r="C15">
-        <v>41716.13236536575</v>
+        <v>41144.00695132261</v>
       </c>
       <c r="D15">
-        <v>46568.78276247396</v>
+        <v>46471.39968666991</v>
       </c>
       <c r="E15">
-        <v>1468.616573198943</v>
+        <v>1943.358911438036</v>
       </c>
       <c r="F15">
-        <v>6171.650397108204</v>
+        <v>6646.392735347296</v>
       </c>
       <c r="G15">
         <v>1319</v>
@@ -2523,45 +2523,45 @@
         <v>3064</v>
       </c>
       <c r="M15">
-        <v>347.0727375573503</v>
+        <v>383.7402295493982</v>
       </c>
       <c r="N15">
-        <v>2716.92726244265</v>
+        <v>2680.259770450602</v>
       </c>
       <c r="O15">
-        <v>339.6159078053312</v>
+        <v>335.0324713063252</v>
       </c>
       <c r="P15">
-        <v>2377.311354637319</v>
+        <v>2345.227299144276</v>
       </c>
       <c r="Q15">
-        <v>3203.311354637319</v>
+        <v>3171.227299144276</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1198602704696966</v>
+        <v>0.1206262376297803</v>
       </c>
       <c r="T15">
-        <v>1.443572519763321</v>
+        <v>1.458502645407278</v>
       </c>
       <c r="U15">
-        <v>0.05623661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.04920703957971732</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.828120645729786</v>
+        <v>7.984568111604718</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1108112999027715</v>
+        <v>0.1107766243515437</v>
       </c>
       <c r="C16">
-        <v>41144.00695132261</v>
+        <v>40694.06463026728</v>
       </c>
       <c r="D16">
-        <v>46471.39968666991</v>
+        <v>46496.19970385366</v>
       </c>
       <c r="E16">
-        <v>1943.358911438036</v>
+        <v>2418.101249677129</v>
       </c>
       <c r="F16">
-        <v>6646.392735347296</v>
+        <v>7121.13507358639</v>
       </c>
       <c r="G16">
         <v>1319</v>
@@ -2605,28 +2605,28 @@
         <v>3064</v>
       </c>
       <c r="M16">
-        <v>383.7402295493982</v>
+        <v>411.1502459457839</v>
       </c>
       <c r="N16">
-        <v>2680.259770450602</v>
+        <v>2652.849754054216</v>
       </c>
       <c r="O16">
-        <v>335.0324713063252</v>
+        <v>331.606219256777</v>
       </c>
       <c r="P16">
-        <v>2345.227299144276</v>
+        <v>2321.243534797439</v>
       </c>
       <c r="Q16">
-        <v>3171.227299144276</v>
+        <v>3147.243534797439</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1206262376297803</v>
+        <v>0.1214102275465719</v>
       </c>
       <c r="T16">
-        <v>1.458502645407278</v>
+        <v>1.473784068125211</v>
       </c>
       <c r="U16">
         <v>0.05773661666253409</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.984568111604718</v>
+        <v>7.452263570831071</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1107766243515437</v>
+        <v>0.1107419488003159</v>
       </c>
       <c r="C17">
-        <v>40694.0646302673</v>
+        <v>40244.14879299577</v>
       </c>
       <c r="D17">
-        <v>46496.19970385369</v>
+        <v>46521.02620482125</v>
       </c>
       <c r="E17">
-        <v>2418.101249677127</v>
+        <v>2892.843587916221</v>
       </c>
       <c r="F17">
-        <v>7121.135073586388</v>
+        <v>7595.877411825481</v>
       </c>
       <c r="G17">
         <v>1319</v>
@@ -2687,28 +2687,28 @@
         <v>3064</v>
       </c>
       <c r="M17">
-        <v>411.1502459457838</v>
+        <v>438.5602623421694</v>
       </c>
       <c r="N17">
-        <v>2652.849754054216</v>
+        <v>2625.439737657831</v>
       </c>
       <c r="O17">
-        <v>331.606219256777</v>
+        <v>328.1799672072289</v>
       </c>
       <c r="P17">
-        <v>2321.243534797439</v>
+        <v>2297.259770450602</v>
       </c>
       <c r="Q17">
-        <v>3147.243534797439</v>
+        <v>3123.259770450602</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1214102275465719</v>
+        <v>0.1222128838899538</v>
       </c>
       <c r="T17">
-        <v>1.473784068125211</v>
+        <v>1.48942933424119</v>
       </c>
       <c r="U17">
         <v>0.05773661666253409</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.452263570831072</v>
+        <v>6.98649709765413</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1107419488003159</v>
+        <v>0.1109601482490881</v>
       </c>
       <c r="C18">
-        <v>40244.14879299577</v>
+        <v>39613.62316470944</v>
       </c>
       <c r="D18">
-        <v>46521.02620482125</v>
+        <v>46365.24291477401</v>
       </c>
       <c r="E18">
-        <v>2892.843587916221</v>
+        <v>3367.585926155313</v>
       </c>
       <c r="F18">
-        <v>7595.877411825481</v>
+        <v>8070.619750064574</v>
       </c>
       <c r="G18">
         <v>1319</v>
@@ -2769,45 +2769,45 @@
         <v>3064</v>
       </c>
       <c r="M18">
-        <v>438.5602623421694</v>
+        <v>479.6903323136647</v>
       </c>
       <c r="N18">
-        <v>2625.439737657831</v>
+        <v>2584.309667686335</v>
       </c>
       <c r="O18">
-        <v>328.1799672072289</v>
+        <v>323.0387084607919</v>
       </c>
       <c r="P18">
-        <v>2297.259770450602</v>
+        <v>2261.270959225543</v>
       </c>
       <c r="Q18">
-        <v>3123.259770450602</v>
+        <v>3087.270959225543</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1222128838899538</v>
+        <v>0.1230348813500436</v>
       </c>
       <c r="T18">
-        <v>1.48942933424119</v>
+        <v>1.50545159472141</v>
       </c>
       <c r="U18">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05051953957971732</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.98649709765413</v>
+        <v>6.387454141970243</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1109601482490881</v>
+        <v>0.1109403476978604</v>
       </c>
       <c r="C19">
-        <v>39613.62316470944</v>
+        <v>39152.97435528878</v>
       </c>
       <c r="D19">
-        <v>46365.24291477401</v>
+        <v>46379.33644359244</v>
       </c>
       <c r="E19">
-        <v>3367.585926155313</v>
+        <v>3842.328264394407</v>
       </c>
       <c r="F19">
-        <v>8070.619750064574</v>
+        <v>8545.362088303667</v>
       </c>
       <c r="G19">
         <v>1319</v>
@@ -2851,28 +2851,28 @@
         <v>3064</v>
       </c>
       <c r="M19">
-        <v>479.6903323136647</v>
+        <v>507.9074106850568</v>
       </c>
       <c r="N19">
-        <v>2584.309667686335</v>
+        <v>2556.092589314943</v>
       </c>
       <c r="O19">
-        <v>323.0387084607919</v>
+        <v>319.5115736643679</v>
       </c>
       <c r="P19">
-        <v>2261.270959225543</v>
+        <v>2236.581015650575</v>
       </c>
       <c r="Q19">
-        <v>3087.270959225543</v>
+        <v>3062.581015650575</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1230348813500436</v>
+        <v>0.1238769275286723</v>
       </c>
       <c r="T19">
-        <v>1.50545159472141</v>
+        <v>1.52186464204261</v>
       </c>
       <c r="U19">
         <v>0.05943661666253409</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.387454141970243</v>
+        <v>6.032595578527451</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1109403476978604</v>
+        <v>0.1109205471466326</v>
       </c>
       <c r="C20">
-        <v>39152.97435528877</v>
+        <v>38692.33411642384</v>
       </c>
       <c r="D20">
-        <v>46379.33644359243</v>
+        <v>46393.4385429666</v>
       </c>
       <c r="E20">
-        <v>3842.328264394405</v>
+        <v>4317.070602633498</v>
       </c>
       <c r="F20">
-        <v>8545.362088303666</v>
+        <v>9020.104426542759</v>
       </c>
       <c r="G20">
         <v>1319</v>
@@ -2933,28 +2933,28 @@
         <v>3064</v>
       </c>
       <c r="M20">
-        <v>507.9074106850567</v>
+        <v>536.1244890564489</v>
       </c>
       <c r="N20">
-        <v>2556.092589314943</v>
+        <v>2527.875510943551</v>
       </c>
       <c r="O20">
-        <v>319.5115736643679</v>
+        <v>315.9844388679439</v>
       </c>
       <c r="P20">
-        <v>2236.581015650575</v>
+        <v>2211.891072075607</v>
       </c>
       <c r="Q20">
-        <v>3062.581015650575</v>
+        <v>3037.891072075607</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1238769275286723</v>
+        <v>0.1247397649709708</v>
       </c>
       <c r="T20">
-        <v>1.52186464204261</v>
+        <v>1.538682949791494</v>
       </c>
       <c r="U20">
         <v>0.05943661666253409</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.032595578527452</v>
+        <v>5.715090548078638</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1109205471466326</v>
+        <v>0.1110407465954048</v>
       </c>
       <c r="C21">
-        <v>38692.33411642384</v>
+        <v>38132.11658008354</v>
       </c>
       <c r="D21">
-        <v>46393.4385429666</v>
+        <v>46307.96334486539</v>
       </c>
       <c r="E21">
-        <v>4317.070602633498</v>
+        <v>4791.812940872592</v>
       </c>
       <c r="F21">
-        <v>9020.104426542759</v>
+        <v>9494.846764781852</v>
       </c>
       <c r="G21">
         <v>1319</v>
@@ -3015,45 +3015,45 @@
         <v>3064</v>
       </c>
       <c r="M21">
-        <v>536.1244890564489</v>
+        <v>571.9374448396665</v>
       </c>
       <c r="N21">
-        <v>2527.875510943551</v>
+        <v>2492.062555160333</v>
       </c>
       <c r="O21">
-        <v>315.9844388679439</v>
+        <v>311.5078193950417</v>
       </c>
       <c r="P21">
-        <v>2211.891072075607</v>
+        <v>2180.554735765292</v>
       </c>
       <c r="Q21">
-        <v>3037.891072075607</v>
+        <v>3006.554735765292</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1247397649709708</v>
+        <v>0.1256241733493267</v>
       </c>
       <c r="T21">
-        <v>1.538682949791494</v>
+        <v>1.5559217152341</v>
       </c>
       <c r="U21">
-        <v>0.05943661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.715090548078638</v>
+        <v>5.357229234849178</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1110407465954048</v>
+        <v>0.1110279460441771</v>
       </c>
       <c r="C22">
-        <v>38132.11658008354</v>
+        <v>37666.46187211642</v>
       </c>
       <c r="D22">
-        <v>46307.96334486539</v>
+        <v>46317.05097513736</v>
       </c>
       <c r="E22">
-        <v>4791.812940872592</v>
+        <v>5266.555279111683</v>
       </c>
       <c r="F22">
-        <v>9494.846764781852</v>
+        <v>9969.589103020944</v>
       </c>
       <c r="G22">
         <v>1319</v>
@@ -3097,28 +3097,28 @@
         <v>3064</v>
       </c>
       <c r="M22">
-        <v>571.9374448396665</v>
+        <v>600.5343170816496</v>
       </c>
       <c r="N22">
-        <v>2492.062555160333</v>
+        <v>2463.46568291835</v>
       </c>
       <c r="O22">
-        <v>311.5078193950417</v>
+        <v>307.9332103647938</v>
       </c>
       <c r="P22">
-        <v>2180.554735765292</v>
+        <v>2155.532472553557</v>
       </c>
       <c r="Q22">
-        <v>3006.554735765292</v>
+        <v>2981.532472553557</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1256241733493267</v>
+        <v>0.1265309718132107</v>
       </c>
       <c r="T22">
-        <v>1.5559217152341</v>
+        <v>1.573596905118292</v>
       </c>
       <c r="U22">
         <v>0.06023661666253409</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.357229234849178</v>
+        <v>5.102123080808742</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.111027946044177</v>
+        <v>0.1110151454929493</v>
       </c>
       <c r="C23">
-        <v>37666.46187211644</v>
+        <v>37200.81073162358</v>
       </c>
       <c r="D23">
-        <v>46317.05097513738</v>
+        <v>46326.14217288362</v>
       </c>
       <c r="E23">
-        <v>5266.555279111683</v>
+        <v>5741.297617350775</v>
       </c>
       <c r="F23">
-        <v>9969.589103020944</v>
+        <v>10444.33144126004</v>
       </c>
       <c r="G23">
         <v>1319</v>
@@ -3179,28 +3179,28 @@
         <v>3064</v>
       </c>
       <c r="M23">
-        <v>600.5343170816496</v>
+        <v>629.131189323633</v>
       </c>
       <c r="N23">
-        <v>2463.46568291835</v>
+        <v>2434.868810676367</v>
       </c>
       <c r="O23">
-        <v>307.9332103647938</v>
+        <v>304.3586013345459</v>
       </c>
       <c r="P23">
-        <v>2155.532472553557</v>
+        <v>2130.510209341821</v>
       </c>
       <c r="Q23">
-        <v>2981.532472553557</v>
+        <v>2956.510209341821</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1265309718132106</v>
+        <v>0.1274610215197583</v>
       </c>
       <c r="T23">
-        <v>1.573596905118292</v>
+        <v>1.591725304999514</v>
       </c>
       <c r="U23">
         <v>0.06023661666253409</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.102123080808742</v>
+        <v>4.870208395317436</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1110151454929493</v>
+        <v>0.1110023449417215</v>
       </c>
       <c r="C24">
-        <v>37200.81073162358</v>
+        <v>36735.16316070612</v>
       </c>
       <c r="D24">
-        <v>46326.14217288362</v>
+        <v>46335.23694020525</v>
       </c>
       <c r="E24">
-        <v>5741.297617350775</v>
+        <v>6216.039955589868</v>
       </c>
       <c r="F24">
-        <v>10444.33144126004</v>
+        <v>10919.07377949913</v>
       </c>
       <c r="G24">
         <v>1319</v>
@@ -3261,28 +3261,28 @@
         <v>3064</v>
       </c>
       <c r="M24">
-        <v>629.131189323633</v>
+        <v>657.7280615656164</v>
       </c>
       <c r="N24">
-        <v>2434.868810676367</v>
+        <v>2406.271938434384</v>
       </c>
       <c r="O24">
-        <v>304.3586013345459</v>
+        <v>300.783992304298</v>
       </c>
       <c r="P24">
-        <v>2130.510209341821</v>
+        <v>2105.487946130086</v>
       </c>
       <c r="Q24">
-        <v>2956.510209341821</v>
+        <v>2931.487946130086</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1274610215197583</v>
+        <v>0.1284152283615409</v>
       </c>
       <c r="T24">
-        <v>1.591725304999514</v>
+        <v>1.610324572410118</v>
       </c>
       <c r="U24">
         <v>0.06023661666253409</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.870208395317436</v>
+        <v>4.658460204216676</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1110023449417215</v>
+        <v>0.1109895443904937</v>
       </c>
       <c r="C25">
-        <v>36735.16316070612</v>
+        <v>36269.51916146678</v>
       </c>
       <c r="D25">
-        <v>46335.23694020525</v>
+        <v>46344.335279205</v>
       </c>
       <c r="E25">
-        <v>6216.039955589868</v>
+        <v>6690.782293828962</v>
       </c>
       <c r="F25">
-        <v>10919.07377949913</v>
+        <v>11393.81611773822</v>
       </c>
       <c r="G25">
         <v>1319</v>
@@ -3343,28 +3343,28 @@
         <v>3064</v>
       </c>
       <c r="M25">
-        <v>657.7280615656164</v>
+        <v>686.3249338075997</v>
       </c>
       <c r="N25">
-        <v>2406.271938434384</v>
+        <v>2377.6750661924</v>
       </c>
       <c r="O25">
-        <v>300.783992304298</v>
+        <v>297.20938327405</v>
       </c>
       <c r="P25">
-        <v>2105.487946130086</v>
+        <v>2080.46568291835</v>
       </c>
       <c r="Q25">
-        <v>2931.487946130086</v>
+        <v>2906.46568291835</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1284152283615409</v>
+        <v>0.1293945459096863</v>
       </c>
       <c r="T25">
-        <v>1.610324572410118</v>
+        <v>1.629413294226264</v>
       </c>
       <c r="U25">
         <v>0.06023661666253409</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.658460204216676</v>
+        <v>4.464357695707648</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1109895443904937</v>
+        <v>0.110976743839266</v>
       </c>
       <c r="C26">
-        <v>36269.51916146679</v>
+        <v>35803.87873600998</v>
       </c>
       <c r="D26">
-        <v>46344.33527920501</v>
+        <v>46353.43719198729</v>
       </c>
       <c r="E26">
-        <v>6690.78229382896</v>
+        <v>7165.524632068054</v>
       </c>
       <c r="F26">
-        <v>11393.81611773822</v>
+        <v>11868.55845597731</v>
       </c>
       <c r="G26">
         <v>1319</v>
@@ -3425,28 +3425,28 @@
         <v>3064</v>
       </c>
       <c r="M26">
-        <v>686.3249338075996</v>
+        <v>714.921806049583</v>
       </c>
       <c r="N26">
-        <v>2377.675066192401</v>
+        <v>2349.078193950417</v>
       </c>
       <c r="O26">
-        <v>297.2093832740501</v>
+        <v>293.6347742438021</v>
       </c>
       <c r="P26">
-        <v>2080.46568291835</v>
+        <v>2055.443419706615</v>
       </c>
       <c r="Q26">
-        <v>2906.46568291835</v>
+        <v>2881.443419706615</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1293945459096862</v>
+        <v>0.1303999785924488</v>
       </c>
       <c r="T26">
-        <v>1.629413294226264</v>
+        <v>1.649011048624175</v>
       </c>
       <c r="U26">
         <v>0.06023661666253409</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.464357695707649</v>
+        <v>4.285783387879342</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.110976743839266</v>
+        <v>0.1111914432880382</v>
       </c>
       <c r="C27">
-        <v>35803.87873600998</v>
+        <v>35176.94435377546</v>
       </c>
       <c r="D27">
-        <v>46353.43719198729</v>
+        <v>46201.24514799187</v>
       </c>
       <c r="E27">
-        <v>7165.524632068054</v>
+        <v>7640.266970307147</v>
       </c>
       <c r="F27">
-        <v>11868.55845597731</v>
+        <v>12343.30079421641</v>
       </c>
       <c r="G27">
         <v>1319</v>
@@ -3507,45 +3507,45 @@
         <v>3064</v>
       </c>
       <c r="M27">
-        <v>714.921806049583</v>
+        <v>755.8619790857828</v>
       </c>
       <c r="N27">
-        <v>2349.078193950417</v>
+        <v>2308.138020914217</v>
       </c>
       <c r="O27">
-        <v>293.6347742438021</v>
+        <v>288.5172526142771</v>
       </c>
       <c r="P27">
-        <v>2055.443419706615</v>
+        <v>2019.62076829994</v>
       </c>
       <c r="Q27">
-        <v>2881.443419706615</v>
+        <v>2845.62076829994</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1303999785924488</v>
+        <v>0.1314325851315022</v>
       </c>
       <c r="T27">
-        <v>1.649011048624175</v>
+        <v>1.669138472059867</v>
       </c>
       <c r="U27">
-        <v>0.06023661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.285783387879342</v>
+        <v>4.053650117056975</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1111914432880382</v>
+        <v>0.1111873927368104</v>
       </c>
       <c r="C28">
-        <v>35176.94435377546</v>
+        <v>34705.06404294602</v>
       </c>
       <c r="D28">
-        <v>46201.24514799187</v>
+        <v>46204.10717540152</v>
       </c>
       <c r="E28">
-        <v>7640.266970307147</v>
+        <v>8115.00930854624</v>
       </c>
       <c r="F28">
-        <v>12343.30079421641</v>
+        <v>12818.0431324555</v>
       </c>
       <c r="G28">
         <v>1319</v>
@@ -3589,28 +3589,28 @@
         <v>3064</v>
       </c>
       <c r="M28">
-        <v>755.8619790857828</v>
+        <v>784.9335936660052</v>
       </c>
       <c r="N28">
-        <v>2308.138020914217</v>
+        <v>2279.066406333995</v>
       </c>
       <c r="O28">
-        <v>288.5172526142771</v>
+        <v>284.8833007917493</v>
       </c>
       <c r="P28">
-        <v>2019.62076829994</v>
+        <v>1994.183105542245</v>
       </c>
       <c r="Q28">
-        <v>2845.62076829994</v>
+        <v>2820.183105542245</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1314325851315022</v>
+        <v>0.1324934822606667</v>
       </c>
       <c r="T28">
-        <v>1.669138472059867</v>
+        <v>1.689817331754071</v>
       </c>
       <c r="U28">
         <v>0.06123661666253409</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.053650117056975</v>
+        <v>3.903514927536346</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1111873927368104</v>
+        <v>0.1111833421855826</v>
       </c>
       <c r="C29">
-        <v>34705.06404294602</v>
+        <v>34233.18408672645</v>
       </c>
       <c r="D29">
-        <v>46204.10717540152</v>
+        <v>46206.96955742104</v>
       </c>
       <c r="E29">
-        <v>8115.00930854624</v>
+        <v>8589.751646785331</v>
       </c>
       <c r="F29">
-        <v>12818.0431324555</v>
+        <v>13292.78547069459</v>
       </c>
       <c r="G29">
         <v>1319</v>
@@ -3671,28 +3671,28 @@
         <v>3064</v>
       </c>
       <c r="M29">
-        <v>784.9335936660052</v>
+        <v>814.0052082462275</v>
       </c>
       <c r="N29">
-        <v>2279.066406333995</v>
+        <v>2249.994791753772</v>
       </c>
       <c r="O29">
-        <v>284.8833007917493</v>
+        <v>281.2493489692216</v>
       </c>
       <c r="P29">
-        <v>1994.183105542245</v>
+        <v>1968.745442784551</v>
       </c>
       <c r="Q29">
-        <v>2820.183105542245</v>
+        <v>2794.745442784551</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1324934822606667</v>
+        <v>0.1335838487545302</v>
       </c>
       <c r="T29">
-        <v>1.689817331754071</v>
+        <v>1.711070604217558</v>
       </c>
       <c r="U29">
         <v>0.06123661666253409</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.903514927536346</v>
+        <v>3.764103680124334</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1111833421855826</v>
+        <v>0.1111792916343548</v>
       </c>
       <c r="C30">
-        <v>34233.18408672645</v>
+        <v>33761.30448518263</v>
       </c>
       <c r="D30">
-        <v>46206.96955742104</v>
+        <v>46209.83229411631</v>
       </c>
       <c r="E30">
-        <v>8589.751646785331</v>
+        <v>9064.493985024426</v>
       </c>
       <c r="F30">
-        <v>13292.78547069459</v>
+        <v>13767.52780893369</v>
       </c>
       <c r="G30">
         <v>1319</v>
@@ -3753,28 +3753,28 @@
         <v>3064</v>
       </c>
       <c r="M30">
-        <v>814.0052082462275</v>
+        <v>843.07682282645</v>
       </c>
       <c r="N30">
-        <v>2249.994791753772</v>
+        <v>2220.92317717355</v>
       </c>
       <c r="O30">
-        <v>281.2493489692216</v>
+        <v>277.6153971466937</v>
       </c>
       <c r="P30">
-        <v>1968.745442784551</v>
+        <v>1943.307780026856</v>
       </c>
       <c r="Q30">
-        <v>2794.745442784551</v>
+        <v>2769.307780026856</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1335838487545302</v>
+        <v>0.1347049297975166</v>
       </c>
       <c r="T30">
-        <v>1.711070604217558</v>
+        <v>1.732922560412411</v>
       </c>
       <c r="U30">
         <v>0.06123661666253409</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.764103680124334</v>
+        <v>3.634307001499357</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1111792916343548</v>
+        <v>0.111175241083127</v>
       </c>
       <c r="C31">
-        <v>33761.30448518264</v>
+        <v>33289.42523838051</v>
       </c>
       <c r="D31">
-        <v>46209.83229411633</v>
+        <v>46212.69538555328</v>
       </c>
       <c r="E31">
-        <v>9064.493985024423</v>
+        <v>9539.236323263514</v>
       </c>
       <c r="F31">
-        <v>13767.52780893368</v>
+        <v>14242.27014717278</v>
       </c>
       <c r="G31">
         <v>1319</v>
@@ -3835,28 +3835,28 @@
         <v>3064</v>
       </c>
       <c r="M31">
-        <v>843.0768228264499</v>
+        <v>872.1484374066723</v>
       </c>
       <c r="N31">
-        <v>2220.92317717355</v>
+        <v>2191.851562593328</v>
       </c>
       <c r="O31">
-        <v>277.6153971466938</v>
+        <v>273.981445324166</v>
       </c>
       <c r="P31">
-        <v>1943.307780026857</v>
+        <v>1917.870117269162</v>
       </c>
       <c r="Q31">
-        <v>2769.307780026857</v>
+        <v>2743.870117269162</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1347049297975166</v>
+        <v>0.1358580417274455</v>
       </c>
       <c r="T31">
-        <v>1.732922560412411</v>
+        <v>1.755398858212831</v>
       </c>
       <c r="U31">
         <v>0.06123661666253409</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.634307001499358</v>
+        <v>3.513163434782712</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.111175241083127</v>
+        <v>0.1111711905318993</v>
       </c>
       <c r="C32">
-        <v>33289.42523838051</v>
+        <v>32817.54634638599</v>
       </c>
       <c r="D32">
-        <v>46212.69538555328</v>
+        <v>46215.55883179786</v>
       </c>
       <c r="E32">
-        <v>9539.236323263514</v>
+        <v>10013.97866150261</v>
       </c>
       <c r="F32">
-        <v>14242.27014717278</v>
+        <v>14717.01248541187</v>
       </c>
       <c r="G32">
         <v>1319</v>
@@ -3917,28 +3917,28 @@
         <v>3064</v>
       </c>
       <c r="M32">
-        <v>872.1484374066723</v>
+        <v>901.2200519868948</v>
       </c>
       <c r="N32">
-        <v>2191.851562593328</v>
+        <v>2162.779948013105</v>
       </c>
       <c r="O32">
-        <v>273.981445324166</v>
+        <v>270.3474935016382</v>
       </c>
       <c r="P32">
-        <v>1917.870117269162</v>
+        <v>1892.432454511467</v>
       </c>
       <c r="Q32">
-        <v>2743.870117269162</v>
+        <v>2718.432454511467</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1358580417274455</v>
+        <v>0.1370445771915752</v>
       </c>
       <c r="T32">
-        <v>1.755398858212831</v>
+        <v>1.778526642906018</v>
       </c>
       <c r="U32">
         <v>0.06123661666253409</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.513163434782712</v>
+        <v>3.399835582047785</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1111711905318993</v>
+        <v>0.1111671399806715</v>
       </c>
       <c r="C33">
-        <v>32817.54634638599</v>
+        <v>32345.66780926509</v>
       </c>
       <c r="D33">
-        <v>46215.55883179786</v>
+        <v>46218.42263291605</v>
       </c>
       <c r="E33">
-        <v>10013.97866150261</v>
+        <v>10488.7209997417</v>
       </c>
       <c r="F33">
-        <v>14717.01248541187</v>
+        <v>15191.75482365096</v>
       </c>
       <c r="G33">
         <v>1319</v>
@@ -3999,28 +3999,28 @@
         <v>3064</v>
       </c>
       <c r="M33">
-        <v>901.2200519868948</v>
+        <v>930.2916665671172</v>
       </c>
       <c r="N33">
-        <v>2162.779948013105</v>
+        <v>2133.708333432883</v>
       </c>
       <c r="O33">
-        <v>270.3474935016382</v>
+        <v>266.7135416791103</v>
       </c>
       <c r="P33">
-        <v>1892.432454511467</v>
+        <v>1866.994791753772</v>
       </c>
       <c r="Q33">
-        <v>2718.432454511467</v>
+        <v>2692.994791753772</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1370445771915752</v>
+        <v>0.1382660107575911</v>
       </c>
       <c r="T33">
-        <v>1.778526642906018</v>
+        <v>1.802334656560768</v>
       </c>
       <c r="U33">
         <v>0.06123661666253409</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.399835582047785</v>
+        <v>3.293590720108792</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1111671399806715</v>
+        <v>0.1111630894294437</v>
       </c>
       <c r="C34">
-        <v>32345.66780926509</v>
+        <v>31873.78962708373</v>
       </c>
       <c r="D34">
-        <v>46218.42263291605</v>
+        <v>46221.28678897378</v>
       </c>
       <c r="E34">
-        <v>10488.7209997417</v>
+        <v>10963.4633379808</v>
       </c>
       <c r="F34">
-        <v>15191.75482365096</v>
+        <v>15666.49716189006</v>
       </c>
       <c r="G34">
         <v>1319</v>
@@ -4081,28 +4081,28 @@
         <v>3064</v>
       </c>
       <c r="M34">
-        <v>930.2916665671172</v>
+        <v>959.3632811473396</v>
       </c>
       <c r="N34">
-        <v>2133.708333432883</v>
+        <v>2104.63671885266</v>
       </c>
       <c r="O34">
-        <v>266.7135416791103</v>
+        <v>263.0795898565825</v>
       </c>
       <c r="P34">
-        <v>1866.994791753772</v>
+        <v>1841.557128996078</v>
       </c>
       <c r="Q34">
-        <v>2692.994791753772</v>
+        <v>2667.557128996078</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1382660107575911</v>
+        <v>0.1395239050270702</v>
       </c>
       <c r="T34">
-        <v>1.802334656560768</v>
+        <v>1.826853357190287</v>
       </c>
       <c r="U34">
         <v>0.06123661666253409</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.293590720108792</v>
+        <v>3.193784940711556</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1111630894294437</v>
+        <v>0.1111590388782159</v>
       </c>
       <c r="C35">
-        <v>31873.78962708373</v>
+        <v>31401.91179990791</v>
       </c>
       <c r="D35">
-        <v>46221.28678897378</v>
+        <v>46224.15130003706</v>
       </c>
       <c r="E35">
-        <v>10963.4633379808</v>
+        <v>11438.20567621989</v>
       </c>
       <c r="F35">
-        <v>15666.49716189006</v>
+        <v>16141.23950012915</v>
       </c>
       <c r="G35">
         <v>1319</v>
@@ -4163,28 +4163,28 @@
         <v>3064</v>
       </c>
       <c r="M35">
-        <v>959.3632811473396</v>
+        <v>988.434895727562</v>
       </c>
       <c r="N35">
-        <v>2104.63671885266</v>
+        <v>2075.565104272438</v>
       </c>
       <c r="O35">
-        <v>263.0795898565825</v>
+        <v>259.4456380340548</v>
       </c>
       <c r="P35">
-        <v>1841.557128996078</v>
+        <v>1816.119466238383</v>
       </c>
       <c r="Q35">
-        <v>2667.557128996078</v>
+        <v>2642.119466238383</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1395239050270702</v>
+        <v>0.1408199173047152</v>
       </c>
       <c r="T35">
-        <v>1.826853357190287</v>
+        <v>1.852115048747974</v>
       </c>
       <c r="U35">
         <v>0.06123661666253409</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.193784940711556</v>
+        <v>3.099850089514157</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1111590388782159</v>
+        <v>0.1111549883269882</v>
       </c>
       <c r="C36">
-        <v>31401.91179990791</v>
+        <v>30930.03432780367</v>
       </c>
       <c r="D36">
-        <v>46224.15130003706</v>
+        <v>46227.01616617191</v>
       </c>
       <c r="E36">
-        <v>11438.20567621989</v>
+        <v>11912.94801445898</v>
       </c>
       <c r="F36">
-        <v>16141.23950012915</v>
+        <v>16615.98183836824</v>
       </c>
       <c r="G36">
         <v>1319</v>
@@ -4245,28 +4245,28 @@
         <v>3064</v>
       </c>
       <c r="M36">
-        <v>988.434895727562</v>
+        <v>1017.506510307785</v>
       </c>
       <c r="N36">
-        <v>2075.565104272438</v>
+        <v>2046.493489692215</v>
       </c>
       <c r="O36">
-        <v>259.4456380340548</v>
+        <v>255.8116862115269</v>
       </c>
       <c r="P36">
-        <v>1816.119466238383</v>
+        <v>1790.681803480689</v>
       </c>
       <c r="Q36">
-        <v>2642.119466238383</v>
+        <v>2616.681803480688</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1408199173047152</v>
+        <v>0.1421558068832109</v>
       </c>
       <c r="T36">
-        <v>1.852115048747974</v>
+        <v>1.87815402312282</v>
       </c>
       <c r="U36">
         <v>0.06123661666253409</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.099850089514157</v>
+        <v>3.011282944099467</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1111549883269882</v>
+        <v>0.1119384377757604</v>
       </c>
       <c r="C37">
-        <v>30930.03432780367</v>
+        <v>29907.70526765619</v>
       </c>
       <c r="D37">
-        <v>46227.01616617191</v>
+        <v>45679.42944426352</v>
       </c>
       <c r="E37">
-        <v>11912.94801445898</v>
+        <v>12387.69035269808</v>
       </c>
       <c r="F37">
-        <v>16615.98183836824</v>
+        <v>17090.72417660733</v>
       </c>
       <c r="G37">
         <v>1319</v>
@@ -4327,45 +4327,45 @@
         <v>3064</v>
       </c>
       <c r="M37">
-        <v>1017.506510307785</v>
+        <v>1089.304935329525</v>
       </c>
       <c r="N37">
-        <v>2046.493489692215</v>
+        <v>1974.695064670475</v>
       </c>
       <c r="O37">
-        <v>255.8116862115269</v>
+        <v>246.8368830838093</v>
       </c>
       <c r="P37">
-        <v>1790.681803480689</v>
+        <v>1727.858181586665</v>
       </c>
       <c r="Q37">
-        <v>2616.681803480688</v>
+        <v>2553.858181586666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1421558068832109</v>
+        <v>0.1435334430110346</v>
       </c>
       <c r="T37">
-        <v>1.87815402312282</v>
+        <v>1.905006715446879</v>
       </c>
       <c r="U37">
-        <v>0.06123661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.011282944099467</v>
+        <v>2.812802825567949</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1119384377757604</v>
+        <v>0.1119562622245326</v>
       </c>
       <c r="C38">
-        <v>29907.70526765617</v>
+        <v>29420.65554349931</v>
       </c>
       <c r="D38">
-        <v>45679.4294442635</v>
+        <v>45667.12205834574</v>
       </c>
       <c r="E38">
-        <v>12387.69035269807</v>
+        <v>12862.43269093717</v>
       </c>
       <c r="F38">
-        <v>17090.72417660733</v>
+        <v>17565.46651484643</v>
       </c>
       <c r="G38">
         <v>1319</v>
@@ -4409,28 +4409,28 @@
         <v>3064</v>
       </c>
       <c r="M38">
-        <v>1089.304935329525</v>
+        <v>1119.563405755345</v>
       </c>
       <c r="N38">
-        <v>1974.695064670475</v>
+        <v>1944.436594244655</v>
       </c>
       <c r="O38">
-        <v>246.8368830838094</v>
+        <v>243.0545742805818</v>
       </c>
       <c r="P38">
-        <v>1727.858181586666</v>
+        <v>1701.382019964073</v>
       </c>
       <c r="Q38">
-        <v>2553.858181586666</v>
+        <v>2527.382019964073</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1435334430110346</v>
+        <v>0.1449548136191067</v>
       </c>
       <c r="T38">
-        <v>1.905006715446879</v>
+        <v>1.932711874193925</v>
       </c>
       <c r="U38">
         <v>0.06373661666253409</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.812802825567949</v>
+        <v>2.736781127579626</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1119562622245326</v>
+        <v>0.1119740866733048</v>
       </c>
       <c r="C39">
-        <v>29420.65554349931</v>
+        <v>28933.61244950182</v>
       </c>
       <c r="D39">
-        <v>45667.12205834574</v>
+        <v>45654.82130258733</v>
       </c>
       <c r="E39">
-        <v>12862.43269093717</v>
+        <v>13337.17502917626</v>
       </c>
       <c r="F39">
-        <v>17565.46651484643</v>
+        <v>18040.20885308552</v>
       </c>
       <c r="G39">
         <v>1319</v>
@@ -4491,28 +4491,28 @@
         <v>3064</v>
       </c>
       <c r="M39">
-        <v>1119.563405755345</v>
+        <v>1149.821876181165</v>
       </c>
       <c r="N39">
-        <v>1944.436594244655</v>
+        <v>1914.178123818835</v>
       </c>
       <c r="O39">
-        <v>243.0545742805818</v>
+        <v>239.2722654773543</v>
       </c>
       <c r="P39">
-        <v>1701.382019964073</v>
+        <v>1674.90585834148</v>
       </c>
       <c r="Q39">
-        <v>2527.382019964073</v>
+        <v>2500.90585834148</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1449548136191067</v>
+        <v>0.1464220348919552</v>
       </c>
       <c r="T39">
-        <v>1.932711874193925</v>
+        <v>1.961310747739263</v>
       </c>
       <c r="U39">
         <v>0.06373661666253409</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.736781127579626</v>
+        <v>2.664760571590688</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1119740866733048</v>
+        <v>0.1119919111220771</v>
       </c>
       <c r="C40">
-        <v>28933.61244950182</v>
+        <v>28446.57598030748</v>
       </c>
       <c r="D40">
-        <v>45654.82130258733</v>
+        <v>45642.52717163209</v>
       </c>
       <c r="E40">
-        <v>13337.17502917626</v>
+        <v>13811.91736741535</v>
       </c>
       <c r="F40">
-        <v>18040.20885308552</v>
+        <v>18514.95119132461</v>
       </c>
       <c r="G40">
         <v>1319</v>
@@ -4573,28 +4573,28 @@
         <v>3064</v>
       </c>
       <c r="M40">
-        <v>1149.821876181165</v>
+        <v>1180.080346606986</v>
       </c>
       <c r="N40">
-        <v>1914.178123818835</v>
+        <v>1883.919653393014</v>
       </c>
       <c r="O40">
-        <v>239.2722654773543</v>
+        <v>235.4899566741268</v>
       </c>
       <c r="P40">
-        <v>1674.90585834148</v>
+        <v>1648.429696718887</v>
       </c>
       <c r="Q40">
-        <v>2500.90585834148</v>
+        <v>2474.429696718887</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1464220348919552</v>
+        <v>0.1479373617803071</v>
       </c>
       <c r="T40">
-        <v>1.961310747739263</v>
+        <v>1.990847289269694</v>
       </c>
       <c r="U40">
         <v>0.06373661666253409</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.664760571590688</v>
+        <v>2.596433377447338</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1119919111220771</v>
+        <v>0.1120097355708493</v>
       </c>
       <c r="C41">
-        <v>28446.57598030748</v>
+        <v>27959.54613056588</v>
       </c>
       <c r="D41">
-        <v>45642.52717163209</v>
+        <v>45630.23966012958</v>
       </c>
       <c r="E41">
-        <v>13811.91736741535</v>
+        <v>14286.65970565445</v>
       </c>
       <c r="F41">
-        <v>18514.95119132461</v>
+        <v>18989.6935295637</v>
       </c>
       <c r="G41">
         <v>1319</v>
@@ -4655,28 +4655,28 @@
         <v>3064</v>
       </c>
       <c r="M41">
-        <v>1180.080346606986</v>
+        <v>1210.338817032806</v>
       </c>
       <c r="N41">
-        <v>1883.919653393014</v>
+        <v>1853.661182967194</v>
       </c>
       <c r="O41">
-        <v>235.4899566741268</v>
+        <v>231.7076478708993</v>
       </c>
       <c r="P41">
-        <v>1648.429696718887</v>
+        <v>1621.953535096295</v>
       </c>
       <c r="Q41">
-        <v>2474.429696718887</v>
+        <v>2447.953535096295</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1479373617803071</v>
+        <v>0.1495031995649372</v>
       </c>
       <c r="T41">
-        <v>1.990847289269694</v>
+        <v>2.021368382184472</v>
       </c>
       <c r="U41">
         <v>0.06373661666253409</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.596433377447338</v>
+        <v>2.531522543011153</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1120097355708493</v>
+        <v>0.1132831850196215</v>
       </c>
       <c r="C42">
-        <v>27959.54613056588</v>
+        <v>26623.73294148236</v>
       </c>
       <c r="D42">
-        <v>45630.23966012958</v>
+        <v>44769.16880928515</v>
       </c>
       <c r="E42">
-        <v>14286.65970565445</v>
+        <v>14761.40204389354</v>
       </c>
       <c r="F42">
-        <v>18989.6935295637</v>
+        <v>19464.4358678028</v>
       </c>
       <c r="G42">
         <v>1319</v>
@@ -4737,45 +4737,45 @@
         <v>3064</v>
       </c>
       <c r="M42">
-        <v>1210.338817032806</v>
+        <v>1308.722812995936</v>
       </c>
       <c r="N42">
-        <v>1853.661182967194</v>
+        <v>1755.277187004064</v>
       </c>
       <c r="O42">
-        <v>231.7076478708993</v>
+        <v>219.4096483755081</v>
       </c>
       <c r="P42">
-        <v>1621.953535096295</v>
+        <v>1535.867538628556</v>
       </c>
       <c r="Q42">
-        <v>2447.953535096295</v>
+        <v>2361.867538628556</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1495031995649372</v>
+        <v>0.1511221165965041</v>
       </c>
       <c r="T42">
-        <v>2.021368382184472</v>
+        <v>2.052924088418396</v>
       </c>
       <c r="U42">
-        <v>0.06373661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971732</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.531522543011153</v>
+        <v>2.34121386864639</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1132831850196215</v>
+        <v>0.1133316344683937</v>
       </c>
       <c r="C43">
-        <v>26623.73294148236</v>
+        <v>26116.87170714554</v>
       </c>
       <c r="D43">
-        <v>44769.16880928515</v>
+        <v>44737.04991318742</v>
       </c>
       <c r="E43">
-        <v>14761.40204389354</v>
+        <v>15236.14438213263</v>
       </c>
       <c r="F43">
-        <v>19464.4358678028</v>
+        <v>19939.17820604189</v>
       </c>
       <c r="G43">
         <v>1319</v>
@@ -4819,28 +4819,28 @@
         <v>3064</v>
       </c>
       <c r="M43">
-        <v>1308.722812995936</v>
+        <v>1340.642881605592</v>
       </c>
       <c r="N43">
-        <v>1755.277187004064</v>
+        <v>1723.357118394408</v>
       </c>
       <c r="O43">
-        <v>219.4096483755081</v>
+        <v>215.4196397993009</v>
       </c>
       <c r="P43">
-        <v>1535.867538628556</v>
+        <v>1507.937478595107</v>
       </c>
       <c r="Q43">
-        <v>2361.867538628556</v>
+        <v>2333.937478595107</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1511221165965041</v>
+        <v>0.1527968583532973</v>
       </c>
       <c r="T43">
-        <v>2.052924088418396</v>
+        <v>2.085567922453489</v>
       </c>
       <c r="U43">
         <v>0.06723661666253408</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.34121386864639</v>
+        <v>2.285470681297666</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1133316344683937</v>
+        <v>0.114433583917166</v>
       </c>
       <c r="C44">
-        <v>26116.87170714554</v>
+        <v>24923.85174623369</v>
       </c>
       <c r="D44">
-        <v>44737.04991318742</v>
+        <v>44018.77229051467</v>
       </c>
       <c r="E44">
-        <v>15236.14438213263</v>
+        <v>15710.88672037172</v>
       </c>
       <c r="F44">
-        <v>19939.17820604189</v>
+        <v>20413.92054428098</v>
       </c>
       <c r="G44">
         <v>1319</v>
@@ -4901,45 +4901,45 @@
         <v>3064</v>
       </c>
       <c r="M44">
-        <v>1340.642881605592</v>
+        <v>1429.721927739236</v>
       </c>
       <c r="N44">
-        <v>1723.357118394408</v>
+        <v>1634.278072260764</v>
       </c>
       <c r="O44">
-        <v>215.4196397993009</v>
+        <v>204.2847590325955</v>
       </c>
       <c r="P44">
-        <v>1507.937478595107</v>
+        <v>1429.993313228168</v>
       </c>
       <c r="Q44">
-        <v>2333.937478595107</v>
+        <v>2255.993313228169</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1527968583532973</v>
+        <v>0.15453036297875</v>
       </c>
       <c r="T44">
-        <v>2.085567922453489</v>
+        <v>2.119357154174024</v>
       </c>
       <c r="U44">
-        <v>0.06723661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.05883203957971732</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.285470681297666</v>
+        <v>2.143074076540873</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.114433583917166</v>
+        <v>0.1145065333659382</v>
       </c>
       <c r="C45">
-        <v>24923.85174623369</v>
+        <v>24402.37229265915</v>
       </c>
       <c r="D45">
-        <v>44018.77229051467</v>
+        <v>43972.03517517922</v>
       </c>
       <c r="E45">
-        <v>15710.88672037172</v>
+        <v>16185.62905861081</v>
       </c>
       <c r="F45">
-        <v>20413.92054428098</v>
+        <v>20888.66288252007</v>
       </c>
       <c r="G45">
         <v>1319</v>
@@ -4983,28 +4983,28 @@
         <v>3064</v>
       </c>
       <c r="M45">
-        <v>1429.721927739236</v>
+        <v>1462.971274895963</v>
       </c>
       <c r="N45">
-        <v>1634.278072260764</v>
+        <v>1601.028725104037</v>
       </c>
       <c r="O45">
-        <v>204.2847590325955</v>
+        <v>200.1285906380047</v>
       </c>
       <c r="P45">
-        <v>1429.993313228168</v>
+        <v>1400.900134466033</v>
       </c>
       <c r="Q45">
-        <v>2255.993313228169</v>
+        <v>2226.900134466033</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.15453036297875</v>
+        <v>0.1563257784836831</v>
       </c>
       <c r="T45">
-        <v>2.119357154174024</v>
+        <v>2.154353144170293</v>
       </c>
       <c r="U45">
         <v>0.07003661666253409</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.143074076540873</v>
+        <v>2.09436784752858</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1145065333659382</v>
+        <v>0.1145794828147104</v>
       </c>
       <c r="C46">
-        <v>24402.37229265915</v>
+        <v>23880.99198047566</v>
       </c>
       <c r="D46">
-        <v>43972.03517517922</v>
+        <v>43925.39720123482</v>
       </c>
       <c r="E46">
-        <v>16185.62905861081</v>
+        <v>16660.37139684991</v>
       </c>
       <c r="F46">
-        <v>20888.66288252007</v>
+        <v>21363.40522075917</v>
       </c>
       <c r="G46">
         <v>1319</v>
@@ -5065,28 +5065,28 @@
         <v>3064</v>
       </c>
       <c r="M46">
-        <v>1462.971274895963</v>
+        <v>1496.220622052689</v>
       </c>
       <c r="N46">
-        <v>1601.028725104037</v>
+        <v>1567.779377947311</v>
       </c>
       <c r="O46">
-        <v>200.1285906380047</v>
+        <v>195.9724222434138</v>
       </c>
       <c r="P46">
-        <v>1400.900134466033</v>
+        <v>1371.806955703897</v>
       </c>
       <c r="Q46">
-        <v>2226.900134466033</v>
+        <v>2197.806955703897</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1563257784836831</v>
+        <v>0.1581864818251593</v>
       </c>
       <c r="T46">
-        <v>2.154353144170293</v>
+        <v>2.190621715620971</v>
       </c>
       <c r="U46">
         <v>0.07003661666253409</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.09436784752858</v>
+        <v>2.047826339805722</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1145794828147104</v>
+        <v>0.1146524322634826</v>
       </c>
       <c r="C47">
-        <v>23880.99198047566</v>
+        <v>23359.71049456101</v>
       </c>
       <c r="D47">
-        <v>43925.39720123482</v>
+        <v>43878.85805355927</v>
       </c>
       <c r="E47">
-        <v>16660.37139684991</v>
+        <v>17135.113735089</v>
       </c>
       <c r="F47">
-        <v>21363.40522075917</v>
+        <v>21838.14755899826</v>
       </c>
       <c r="G47">
         <v>1319</v>
@@ -5147,28 +5147,28 @@
         <v>3064</v>
       </c>
       <c r="M47">
-        <v>1496.220622052689</v>
+        <v>1529.469969209416</v>
       </c>
       <c r="N47">
-        <v>1567.779377947311</v>
+        <v>1534.530030790584</v>
       </c>
       <c r="O47">
-        <v>195.9724222434138</v>
+        <v>191.816253848823</v>
       </c>
       <c r="P47">
-        <v>1371.806955703897</v>
+        <v>1342.713776941761</v>
       </c>
       <c r="Q47">
-        <v>2197.806955703897</v>
+        <v>2168.713776941761</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1581864818251593</v>
+        <v>0.1601161001052086</v>
       </c>
       <c r="T47">
-        <v>2.190621715620971</v>
+        <v>2.228233567495749</v>
       </c>
       <c r="U47">
         <v>0.07003661666253409</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.047826339805722</v>
+        <v>2.003308375896903</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1146524322634826</v>
+        <v>0.1179331317122548</v>
       </c>
       <c r="C48">
-        <v>23359.71049456101</v>
+        <v>20889.30621829171</v>
       </c>
       <c r="D48">
-        <v>43878.85805355927</v>
+        <v>41883.19611552906</v>
       </c>
       <c r="E48">
-        <v>17135.113735089</v>
+        <v>17609.85607332809</v>
       </c>
       <c r="F48">
-        <v>21838.14755899826</v>
+        <v>22312.88989723735</v>
       </c>
       <c r="G48">
         <v>1319</v>
@@ -5229,45 +5229,45 @@
         <v>3064</v>
       </c>
       <c r="M48">
-        <v>1529.469969209416</v>
+        <v>1736.759857564593</v>
       </c>
       <c r="N48">
-        <v>1534.530030790584</v>
+        <v>1327.240142435407</v>
       </c>
       <c r="O48">
-        <v>191.816253848823</v>
+        <v>165.9050178044258</v>
       </c>
       <c r="P48">
-        <v>1342.713776941761</v>
+        <v>1161.335124630981</v>
       </c>
       <c r="Q48">
-        <v>2168.713776941761</v>
+        <v>1987.335124630981</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1601161001052086</v>
+        <v>0.1621185341694107</v>
       </c>
       <c r="T48">
-        <v>2.228233567495749</v>
+        <v>2.267264734535612</v>
       </c>
       <c r="U48">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V48">
         <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971732</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.003308375896903</v>
+        <v>1.764204755570846</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1179331317122548</v>
+        <v>0.1197123311610271</v>
       </c>
       <c r="C49">
-        <v>20889.30621829171</v>
+        <v>19406.36188897727</v>
       </c>
       <c r="D49">
-        <v>41883.19611552906</v>
+        <v>40874.99412445371</v>
       </c>
       <c r="E49">
-        <v>17609.85607332809</v>
+        <v>18084.59841156719</v>
       </c>
       <c r="F49">
-        <v>22312.88989723735</v>
+        <v>22787.63223547645</v>
       </c>
       <c r="G49">
         <v>1319</v>
@@ -5311,45 +5311,45 @@
         <v>3064</v>
       </c>
       <c r="M49">
-        <v>1736.759857564593</v>
+        <v>1862.583960677943</v>
       </c>
       <c r="N49">
-        <v>1327.240142435407</v>
+        <v>1201.416039322057</v>
       </c>
       <c r="O49">
-        <v>165.9050178044258</v>
+        <v>150.1770049152571</v>
       </c>
       <c r="P49">
-        <v>1161.335124630981</v>
+        <v>1051.2390344068</v>
       </c>
       <c r="Q49">
-        <v>1987.335124630981</v>
+        <v>1877.2390344068</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1621185341694107</v>
+        <v>0.1641979849283899</v>
       </c>
       <c r="T49">
-        <v>2.267264734535612</v>
+        <v>2.307797100307778</v>
       </c>
       <c r="U49">
-        <v>0.07783661666253408</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.06810703957971732</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.764204755570846</v>
+        <v>1.645026514071755</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1197123311610271</v>
+        <v>0.1198876556097993</v>
       </c>
       <c r="C50">
-        <v>19406.36188897728</v>
+        <v>18834.89107749318</v>
       </c>
       <c r="D50">
-        <v>40874.99412445372</v>
+        <v>40778.26565120872</v>
       </c>
       <c r="E50">
-        <v>18084.59841156718</v>
+        <v>18559.34074980628</v>
       </c>
       <c r="F50">
-        <v>22787.63223547644</v>
+        <v>23262.37457371554</v>
       </c>
       <c r="G50">
         <v>1319</v>
@@ -5393,28 +5393,28 @@
         <v>3064</v>
       </c>
       <c r="M50">
-        <v>1862.583960677943</v>
+        <v>1901.387793192067</v>
       </c>
       <c r="N50">
-        <v>1201.416039322057</v>
+        <v>1162.612206807933</v>
       </c>
       <c r="O50">
-        <v>150.1770049152572</v>
+        <v>145.3265258509917</v>
       </c>
       <c r="P50">
-        <v>1051.2390344068</v>
+        <v>1017.285680956942</v>
       </c>
       <c r="Q50">
-        <v>1877.2390344068</v>
+        <v>1843.285680956942</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1641979849283899</v>
+        <v>0.1663589827759565</v>
       </c>
       <c r="T50">
-        <v>2.307797100307778</v>
+        <v>2.349918970620029</v>
       </c>
       <c r="U50">
         <v>0.0817366166625341</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.645026514071755</v>
+        <v>1.611454544396822</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1198876556097993</v>
+        <v>0.1200629800585715</v>
       </c>
       <c r="C51">
-        <v>18834.89107749318</v>
+        <v>18263.87699064465</v>
       </c>
       <c r="D51">
-        <v>40778.26565120872</v>
+        <v>40681.99390259928</v>
       </c>
       <c r="E51">
-        <v>18559.34074980628</v>
+        <v>19034.08308804537</v>
       </c>
       <c r="F51">
-        <v>23262.37457371554</v>
+        <v>23737.11691195463</v>
       </c>
       <c r="G51">
         <v>1319</v>
@@ -5475,28 +5475,28 @@
         <v>3064</v>
       </c>
       <c r="M51">
-        <v>1901.387793192067</v>
+        <v>1940.191625706191</v>
       </c>
       <c r="N51">
-        <v>1162.612206807933</v>
+        <v>1123.808374293809</v>
       </c>
       <c r="O51">
-        <v>145.3265258509917</v>
+        <v>140.4760467867262</v>
       </c>
       <c r="P51">
-        <v>1017.285680956942</v>
+        <v>983.3323275070833</v>
       </c>
       <c r="Q51">
-        <v>1843.285680956942</v>
+        <v>1809.332327507083</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1663589827759565</v>
+        <v>0.1686064205374257</v>
       </c>
       <c r="T51">
-        <v>2.349918970620029</v>
+        <v>2.39372571574477</v>
       </c>
       <c r="U51">
         <v>0.0817366166625341</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.611454544396822</v>
+        <v>1.579225453508885</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1200629800585715</v>
+        <v>0.1202383045073437</v>
       </c>
       <c r="C52">
-        <v>18263.87699064465</v>
+        <v>17693.31640126277</v>
       </c>
       <c r="D52">
-        <v>40681.99390259928</v>
+        <v>40586.17565145649</v>
       </c>
       <c r="E52">
-        <v>19034.08308804537</v>
+        <v>19508.82542628446</v>
       </c>
       <c r="F52">
-        <v>23737.11691195463</v>
+        <v>24211.85925019372</v>
       </c>
       <c r="G52">
         <v>1319</v>
@@ -5557,28 +5557,28 @@
         <v>3064</v>
       </c>
       <c r="M52">
-        <v>1940.191625706191</v>
+        <v>1978.995458220314</v>
       </c>
       <c r="N52">
-        <v>1123.808374293809</v>
+        <v>1085.004541779686</v>
       </c>
       <c r="O52">
-        <v>140.4760467867262</v>
+        <v>135.6255677224607</v>
       </c>
       <c r="P52">
-        <v>983.3323275070833</v>
+        <v>949.378974057225</v>
       </c>
       <c r="Q52">
-        <v>1809.332327507083</v>
+        <v>1775.378974057225</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1686064205374257</v>
+        <v>0.1709455904524243</v>
       </c>
       <c r="T52">
-        <v>2.39372571574477</v>
+        <v>2.439320491282766</v>
       </c>
       <c r="U52">
         <v>0.0817366166625341</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.579225453508885</v>
+        <v>1.548260248538123</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1202383045073437</v>
+        <v>0.120413628956116</v>
       </c>
       <c r="C53">
-        <v>17693.31640126277</v>
+        <v>17123.20611251092</v>
       </c>
       <c r="D53">
-        <v>40586.17565145649</v>
+        <v>40490.80770094374</v>
       </c>
       <c r="E53">
-        <v>19508.82542628446</v>
+        <v>19983.56776452356</v>
       </c>
       <c r="F53">
-        <v>24211.85925019372</v>
+        <v>24686.60158843282</v>
       </c>
       <c r="G53">
         <v>1319</v>
@@ -5639,28 +5639,28 @@
         <v>3064</v>
       </c>
       <c r="M53">
-        <v>1978.995458220314</v>
+        <v>2017.799290734438</v>
       </c>
       <c r="N53">
-        <v>1085.004541779686</v>
+        <v>1046.200709265562</v>
       </c>
       <c r="O53">
-        <v>135.6255677224607</v>
+        <v>130.7750886581952</v>
       </c>
       <c r="P53">
-        <v>949.378974057225</v>
+        <v>915.4256206073665</v>
       </c>
       <c r="Q53">
-        <v>1775.378974057225</v>
+        <v>1741.425620607366</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1709455904524243</v>
+        <v>0.1733822257805478</v>
       </c>
       <c r="T53">
-        <v>2.439320491282766</v>
+        <v>2.486815049134844</v>
       </c>
       <c r="U53">
         <v>0.0817366166625341</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.548260248538123</v>
+        <v>1.518486012989313</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.120413628956116</v>
+        <v>0.1271742034048882</v>
       </c>
       <c r="C54">
-        <v>17123.20611251092</v>
+        <v>13284.48466911102</v>
       </c>
       <c r="D54">
-        <v>40490.80770094374</v>
+        <v>37126.82859578293</v>
       </c>
       <c r="E54">
-        <v>19983.56776452356</v>
+        <v>20458.31010276265</v>
       </c>
       <c r="F54">
-        <v>24686.60158843282</v>
+        <v>25161.34392667191</v>
       </c>
       <c r="G54">
         <v>1319</v>
@@ -5721,45 +5721,45 @@
         <v>3064</v>
       </c>
       <c r="M54">
-        <v>2017.799290734438</v>
+        <v>2413.894207007303</v>
       </c>
       <c r="N54">
-        <v>1046.200709265562</v>
+        <v>650.1057929926969</v>
       </c>
       <c r="O54">
-        <v>130.7750886581952</v>
+        <v>81.26322412408712</v>
       </c>
       <c r="P54">
-        <v>915.4256206073665</v>
+        <v>568.8425688686098</v>
       </c>
       <c r="Q54">
-        <v>1741.425620607366</v>
+        <v>1394.84256886861</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1733822257805478</v>
+        <v>0.1759225477183787</v>
       </c>
       <c r="T54">
-        <v>2.486815049134844</v>
+        <v>2.536330652001905</v>
       </c>
       <c r="U54">
-        <v>0.0817366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V54">
         <v>0.125</v>
       </c>
       <c r="W54">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971733</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.518486012989313</v>
+        <v>1.26931826221112</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1271742034048882</v>
+        <v>0.1415040891807923</v>
       </c>
       <c r="C55">
-        <v>13284.48466911102</v>
+        <v>7250.6986415881</v>
       </c>
       <c r="D55">
-        <v>37126.82859578293</v>
+        <v>31567.78490649911</v>
       </c>
       <c r="E55">
-        <v>20458.31010276265</v>
+        <v>20933.05244100174</v>
       </c>
       <c r="F55">
-        <v>25161.34392667191</v>
+        <v>25636.086264911</v>
       </c>
       <c r="G55">
         <v>1319</v>
@@ -5803,45 +5803,45 @@
         <v>3064</v>
       </c>
       <c r="M55">
-        <v>2413.894207007303</v>
+        <v>3192.631447900877</v>
       </c>
       <c r="N55">
-        <v>650.1057929926969</v>
+        <v>-128.631447900877</v>
       </c>
       <c r="O55">
-        <v>81.26322412408712</v>
+        <v>-16.07893098760962</v>
       </c>
       <c r="P55">
-        <v>568.8425688686098</v>
+        <v>-112.5525169132674</v>
       </c>
       <c r="Q55">
-        <v>1394.84256886861</v>
+        <v>713.4474830867326</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1759225477183787</v>
+        <v>0.1789605440822764</v>
       </c>
       <c r="T55">
-        <v>2.536330652001905</v>
+        <v>2.59554685575393</v>
       </c>
       <c r="U55">
-        <v>0.09593661666253409</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V55">
-        <v>0.125</v>
+        <v>0.1199637372023691</v>
       </c>
       <c r="W55">
-        <v>0.08394453957971733</v>
+        <v>0.1095967387091577</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.26931826221112</v>
+        <v>0.9597098976189529</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1415040891807923</v>
+        <v>0.1422914553474176</v>
       </c>
       <c r="C56">
-        <v>7250.6986415881</v>
+        <v>6518.364522800231</v>
       </c>
       <c r="D56">
-        <v>31567.78490649911</v>
+        <v>31310.19312595033</v>
       </c>
       <c r="E56">
-        <v>20933.05244100174</v>
+        <v>21407.79477924083</v>
       </c>
       <c r="F56">
-        <v>25636.086264911</v>
+        <v>26110.82860315009</v>
       </c>
       <c r="G56">
         <v>1319</v>
@@ -5885,37 +5885,37 @@
         <v>3064</v>
       </c>
       <c r="M56">
-        <v>3192.631447900877</v>
+        <v>3251.754252491634</v>
       </c>
       <c r="N56">
-        <v>-128.631447900877</v>
+        <v>-187.7542524916339</v>
       </c>
       <c r="O56">
-        <v>-16.07893098760962</v>
+        <v>-23.46928156145424</v>
       </c>
       <c r="P56">
-        <v>-112.5525169132674</v>
+        <v>-164.2849709301797</v>
       </c>
       <c r="Q56">
-        <v>713.4474830867326</v>
+        <v>661.7150290698203</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1789605440822764</v>
+        <v>0.1819196672841048</v>
       </c>
       <c r="T56">
-        <v>2.59554685575393</v>
+        <v>2.653225674770684</v>
       </c>
       <c r="U56">
         <v>0.1245366166625341</v>
       </c>
       <c r="V56">
-        <v>0.1199637372023691</v>
+        <v>0.1177825783441442</v>
       </c>
       <c r="W56">
-        <v>0.1095967387091577</v>
+        <v>0.1098683728537645</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9597098976189529</v>
+        <v>0.9422606267531538</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1422914553474176</v>
+        <v>0.1430788215140429</v>
       </c>
       <c r="C57">
-        <v>6518.364522800231</v>
+        <v>5790.200254132855</v>
       </c>
       <c r="D57">
-        <v>31310.19312595033</v>
+        <v>31056.77119552204</v>
       </c>
       <c r="E57">
-        <v>21407.79477924083</v>
+        <v>21882.53711747993</v>
       </c>
       <c r="F57">
-        <v>26110.82860315009</v>
+        <v>26585.57094138919</v>
       </c>
       <c r="G57">
         <v>1319</v>
@@ -5967,37 +5967,37 @@
         <v>3064</v>
       </c>
       <c r="M57">
-        <v>3251.754252491634</v>
+        <v>3310.877057082391</v>
       </c>
       <c r="N57">
-        <v>-187.7542524916339</v>
+        <v>-246.8770570823908</v>
       </c>
       <c r="O57">
-        <v>-23.46928156145424</v>
+        <v>-30.85963213529885</v>
       </c>
       <c r="P57">
-        <v>-164.2849709301797</v>
+        <v>-216.017424947092</v>
       </c>
       <c r="Q57">
-        <v>661.7150290698203</v>
+        <v>609.982575052908</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1819196672841048</v>
+        <v>0.1850132960860162</v>
       </c>
       <c r="T57">
-        <v>2.653225674770684</v>
+        <v>2.713526258288199</v>
       </c>
       <c r="U57">
         <v>0.1245366166625341</v>
       </c>
       <c r="V57">
-        <v>0.1177825783441442</v>
+        <v>0.1156793180165702</v>
       </c>
       <c r="W57">
-        <v>0.1098683728537645</v>
+        <v>0.1101303057789211</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9422606267531538</v>
+        <v>0.9254345441325618</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1430788215140429</v>
+        <v>0.1438661876806683</v>
       </c>
       <c r="C58">
-        <v>5790.200254132855</v>
+        <v>5066.105397331437</v>
       </c>
       <c r="D58">
-        <v>31056.77119552204</v>
+        <v>30807.41867695972</v>
       </c>
       <c r="E58">
-        <v>21882.53711747993</v>
+        <v>22357.27945571902</v>
       </c>
       <c r="F58">
-        <v>26585.57094138919</v>
+        <v>27060.31327962828</v>
       </c>
       <c r="G58">
         <v>1319</v>
@@ -6049,37 +6049,37 @@
         <v>3064</v>
       </c>
       <c r="M58">
-        <v>3310.877057082391</v>
+        <v>3369.999861673148</v>
       </c>
       <c r="N58">
-        <v>-246.8770570823908</v>
+        <v>-305.9998616731482</v>
       </c>
       <c r="O58">
-        <v>-30.85963213529885</v>
+        <v>-38.24998270914352</v>
       </c>
       <c r="P58">
-        <v>-216.017424947092</v>
+        <v>-267.7498789640047</v>
       </c>
       <c r="Q58">
-        <v>609.982575052908</v>
+        <v>558.2501210359953</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1850132960860162</v>
+        <v>0.1882508145996446</v>
       </c>
       <c r="T58">
-        <v>2.713526258288199</v>
+        <v>2.776631520108856</v>
       </c>
       <c r="U58">
         <v>0.1245366166625341</v>
       </c>
       <c r="V58">
-        <v>0.1156793180165702</v>
+        <v>0.1136498562969813</v>
       </c>
       <c r="W58">
-        <v>0.1101303057789211</v>
+        <v>0.1103830480751249</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9254345441325618</v>
+        <v>0.90919885037585</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1438661876806683</v>
+        <v>0.1446535538472937</v>
       </c>
       <c r="C59">
-        <v>5066.105397331437</v>
+        <v>4345.982714094622</v>
       </c>
       <c r="D59">
-        <v>30807.41867695972</v>
+        <v>30562.03833196199</v>
       </c>
       <c r="E59">
-        <v>22357.27945571902</v>
+        <v>22832.02179395811</v>
       </c>
       <c r="F59">
-        <v>27060.31327962828</v>
+        <v>27535.05561786737</v>
       </c>
       <c r="G59">
         <v>1319</v>
@@ -6131,37 +6131,37 @@
         <v>3064</v>
       </c>
       <c r="M59">
-        <v>3369.999861673148</v>
+        <v>3429.122666263905</v>
       </c>
       <c r="N59">
-        <v>-305.9998616731482</v>
+        <v>-365.1226662639051</v>
       </c>
       <c r="O59">
-        <v>-38.24998270914352</v>
+        <v>-45.64033328298814</v>
       </c>
       <c r="P59">
-        <v>-267.7498789640047</v>
+        <v>-319.482332980917</v>
       </c>
       <c r="Q59">
-        <v>558.2501210359953</v>
+        <v>506.517667019083</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1882508145996446</v>
+        <v>0.1916425006615409</v>
       </c>
       <c r="T59">
-        <v>2.776631520108856</v>
+        <v>2.842741794397162</v>
       </c>
       <c r="U59">
         <v>0.1245366166625341</v>
       </c>
       <c r="V59">
-        <v>0.1136498562969813</v>
+        <v>0.1116903760159988</v>
       </c>
       <c r="W59">
-        <v>0.1103830480751249</v>
+        <v>0.1106270751197354</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.90919885037585</v>
+        <v>0.8935230081279906</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1446535538472937</v>
+        <v>0.145440920013919</v>
       </c>
       <c r="C60">
-        <v>4345.982714094625</v>
+        <v>3629.738039643344</v>
       </c>
       <c r="D60">
-        <v>30562.03833196199</v>
+        <v>30320.5359957498</v>
       </c>
       <c r="E60">
-        <v>22832.02179395811</v>
+        <v>23306.7641321972</v>
       </c>
       <c r="F60">
-        <v>27535.05561786737</v>
+        <v>28009.79795610646</v>
       </c>
       <c r="G60">
         <v>1319</v>
@@ -6213,37 +6213,37 @@
         <v>3064</v>
       </c>
       <c r="M60">
-        <v>3429.122666263905</v>
+        <v>3488.245470854662</v>
       </c>
       <c r="N60">
-        <v>-365.1226662639046</v>
+        <v>-424.2454708546616</v>
       </c>
       <c r="O60">
-        <v>-45.64033328298808</v>
+        <v>-53.0306838568327</v>
       </c>
       <c r="P60">
-        <v>-319.4823329809166</v>
+        <v>-371.2147869978289</v>
       </c>
       <c r="Q60">
-        <v>506.5176670190834</v>
+        <v>454.7852130021711</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1916425006615408</v>
+        <v>0.1951996348240174</v>
       </c>
       <c r="T60">
-        <v>2.842741794397161</v>
+        <v>2.912076960114165</v>
       </c>
       <c r="U60">
         <v>0.1245366166625341</v>
       </c>
       <c r="V60">
-        <v>0.1116903760159988</v>
+        <v>0.1097973187953887</v>
       </c>
       <c r="W60">
-        <v>0.1106270751197354</v>
+        <v>0.1108628300611387</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8935230081279907</v>
+        <v>0.8783785503631095</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.145440920013919</v>
+        <v>0.1462282861805443</v>
       </c>
       <c r="C61">
-        <v>3629.738039643344</v>
+        <v>2917.280162237523</v>
       </c>
       <c r="D61">
-        <v>30320.5359957498</v>
+        <v>30082.82045658307</v>
       </c>
       <c r="E61">
-        <v>23306.7641321972</v>
+        <v>23781.50647043629</v>
       </c>
       <c r="F61">
-        <v>28009.79795610646</v>
+        <v>28484.54029434555</v>
       </c>
       <c r="G61">
         <v>1319</v>
@@ -6295,37 +6295,37 @@
         <v>3064</v>
       </c>
       <c r="M61">
-        <v>3488.245470854662</v>
+        <v>3547.368275445418</v>
       </c>
       <c r="N61">
-        <v>-424.2454708546616</v>
+        <v>-483.368275445418</v>
       </c>
       <c r="O61">
-        <v>-53.0306838568327</v>
+        <v>-60.42103443067725</v>
       </c>
       <c r="P61">
-        <v>-371.2147869978289</v>
+        <v>-422.9472410147408</v>
       </c>
       <c r="Q61">
-        <v>454.7852130021711</v>
+        <v>403.0527589852592</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1951996348240174</v>
+        <v>0.1989346256946178</v>
       </c>
       <c r="T61">
-        <v>2.912076960114165</v>
+        <v>2.984878884117018</v>
       </c>
       <c r="U61">
         <v>0.1245366166625341</v>
       </c>
       <c r="V61">
-        <v>0.1097973187953887</v>
+        <v>0.1079673634821322</v>
       </c>
       <c r="W61">
-        <v>0.1108628300611387</v>
+        <v>0.1110907265044953</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8783785503631095</v>
+        <v>0.8637389078570579</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1462282861805443</v>
+        <v>0.1470156523471697</v>
       </c>
       <c r="C62">
-        <v>2917.280162237523</v>
+        <v>2208.520708316213</v>
       </c>
       <c r="D62">
-        <v>30082.82045658307</v>
+        <v>29848.80334090086</v>
       </c>
       <c r="E62">
-        <v>23781.50647043629</v>
+        <v>24256.24880867539</v>
       </c>
       <c r="F62">
-        <v>28484.54029434555</v>
+        <v>28959.28263258465</v>
       </c>
       <c r="G62">
         <v>1319</v>
@@ -6377,37 +6377,37 @@
         <v>3064</v>
       </c>
       <c r="M62">
-        <v>3547.368275445418</v>
+        <v>3606.491080036175</v>
       </c>
       <c r="N62">
-        <v>-483.368275445418</v>
+        <v>-542.4910800361754</v>
       </c>
       <c r="O62">
-        <v>-60.42103443067725</v>
+        <v>-67.81138500452192</v>
       </c>
       <c r="P62">
-        <v>-422.9472410147408</v>
+        <v>-474.6796950316535</v>
       </c>
       <c r="Q62">
-        <v>403.0527589852592</v>
+        <v>351.3203049683465</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1989346256946178</v>
+        <v>0.2028611545585824</v>
       </c>
       <c r="T62">
-        <v>2.984878884117018</v>
+        <v>3.06141424012002</v>
       </c>
       <c r="U62">
         <v>0.1245366166625341</v>
       </c>
       <c r="V62">
-        <v>0.1079673634821322</v>
+        <v>0.1061974067037366</v>
       </c>
       <c r="W62">
-        <v>0.1110907265044953</v>
+        <v>0.1113111509333156</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8637389078570579</v>
+        <v>0.8495792536298928</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1470156523471697</v>
+        <v>0.147803018513795</v>
       </c>
       <c r="C63">
-        <v>2208.520708316213</v>
+        <v>1503.374032957428</v>
       </c>
       <c r="D63">
-        <v>29848.80334090086</v>
+        <v>29618.39900378117</v>
       </c>
       <c r="E63">
-        <v>24256.24880867539</v>
+        <v>24730.99114691448</v>
       </c>
       <c r="F63">
-        <v>28959.28263258465</v>
+        <v>29434.02497082374</v>
       </c>
       <c r="G63">
         <v>1319</v>
@@ -6459,37 +6459,37 @@
         <v>3064</v>
       </c>
       <c r="M63">
-        <v>3606.491080036175</v>
+        <v>3665.613884626932</v>
       </c>
       <c r="N63">
-        <v>-542.4910800361754</v>
+        <v>-601.6138846269323</v>
       </c>
       <c r="O63">
-        <v>-67.81138500452192</v>
+        <v>-75.20173557836654</v>
       </c>
       <c r="P63">
-        <v>-474.6796950316535</v>
+        <v>-526.4121490485658</v>
       </c>
       <c r="Q63">
-        <v>351.3203049683465</v>
+        <v>299.5878509514342</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2028611545585824</v>
+        <v>0.2069943428364399</v>
       </c>
       <c r="T63">
-        <v>3.06141424012002</v>
+        <v>3.141977772754757</v>
       </c>
       <c r="U63">
         <v>0.1245366166625341</v>
       </c>
       <c r="V63">
-        <v>0.1061974067037366</v>
+        <v>0.1044845453052892</v>
       </c>
       <c r="W63">
-        <v>0.1113111509333156</v>
+        <v>0.1115244648966901</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8495792536298928</v>
+        <v>0.835876362442314</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.147803018513795</v>
+        <v>0.1485903846804204</v>
       </c>
       <c r="C64">
-        <v>1503.374032957428</v>
+        <v>801.7571153723111</v>
       </c>
       <c r="D64">
-        <v>29618.39900378117</v>
+        <v>29391.52442443514</v>
       </c>
       <c r="E64">
-        <v>24730.99114691448</v>
+        <v>25205.73348515357</v>
       </c>
       <c r="F64">
-        <v>29434.02497082374</v>
+        <v>29908.76730906283</v>
       </c>
       <c r="G64">
         <v>1319</v>
@@ -6541,37 +6541,37 @@
         <v>3064</v>
       </c>
       <c r="M64">
-        <v>3665.613884626932</v>
+        <v>3724.736689217689</v>
       </c>
       <c r="N64">
-        <v>-601.6138846269323</v>
+        <v>-660.7366892176892</v>
       </c>
       <c r="O64">
-        <v>-75.20173557836654</v>
+        <v>-82.59208615221115</v>
       </c>
       <c r="P64">
-        <v>-526.4121490485658</v>
+        <v>-578.1446030654781</v>
       </c>
       <c r="Q64">
-        <v>299.5878509514342</v>
+        <v>247.8553969345219</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2069943428364399</v>
+        <v>0.2113509466968842</v>
       </c>
       <c r="T64">
-        <v>3.141977772754757</v>
+        <v>3.226896090937318</v>
       </c>
       <c r="U64">
         <v>0.1245366166625341</v>
       </c>
       <c r="V64">
-        <v>0.1044845453052892</v>
+        <v>0.1028260604591735</v>
       </c>
       <c r="W64">
-        <v>0.1115244648966901</v>
+        <v>0.1117310069882115</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.835876362442314</v>
+        <v>0.8226084836733883</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1485903846804204</v>
+        <v>0.1493777508470457</v>
       </c>
       <c r="C65">
-        <v>801.7571153723111</v>
+        <v>103.5894591658798</v>
       </c>
       <c r="D65">
-        <v>29391.52442443514</v>
+        <v>29168.09910646781</v>
       </c>
       <c r="E65">
-        <v>25205.73348515357</v>
+        <v>25680.47582339267</v>
       </c>
       <c r="F65">
-        <v>29908.76730906283</v>
+        <v>30383.50964730193</v>
       </c>
       <c r="G65">
         <v>1319</v>
@@ -6623,37 +6623,37 @@
         <v>3064</v>
       </c>
       <c r="M65">
-        <v>3724.736689217689</v>
+        <v>3783.859493808447</v>
       </c>
       <c r="N65">
-        <v>-660.7366892176892</v>
+        <v>-719.8594938084466</v>
       </c>
       <c r="O65">
-        <v>-82.59208615221115</v>
+        <v>-89.98243672605582</v>
       </c>
       <c r="P65">
-        <v>-578.1446030654781</v>
+        <v>-629.8770570823908</v>
       </c>
       <c r="Q65">
-        <v>247.8553969345219</v>
+        <v>196.1229429176092</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2113509466968842</v>
+        <v>0.215949584105131</v>
       </c>
       <c r="T65">
-        <v>3.226896090937318</v>
+        <v>3.316532093463354</v>
       </c>
       <c r="U65">
         <v>0.1245366166625341</v>
       </c>
       <c r="V65">
-        <v>0.1028260604591735</v>
+        <v>0.1012194032644989</v>
       </c>
       <c r="W65">
-        <v>0.1117310069882115</v>
+        <v>0.1119310946393727</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8226084836733883</v>
+        <v>0.8097552261159915</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1493777508470457</v>
+        <v>0.1692784916206388</v>
       </c>
       <c r="C66">
-        <v>103.5894591658798</v>
+        <v>-5072.107446607519</v>
       </c>
       <c r="D66">
-        <v>29168.09910646781</v>
+        <v>24467.1445389335</v>
       </c>
       <c r="E66">
-        <v>25680.47582339267</v>
+        <v>26155.21816163176</v>
       </c>
       <c r="F66">
-        <v>30383.50964730193</v>
+        <v>30858.25198554102</v>
       </c>
       <c r="G66">
         <v>1319</v>
@@ -6705,45 +6705,45 @@
         <v>3064</v>
       </c>
       <c r="M66">
-        <v>3783.859493808447</v>
+        <v>4713.18500439146</v>
       </c>
       <c r="N66">
-        <v>-719.8594938084466</v>
+        <v>-1649.18500439146</v>
       </c>
       <c r="O66">
-        <v>-89.98243672605582</v>
+        <v>-206.1481255489325</v>
       </c>
       <c r="P66">
-        <v>-629.8770570823908</v>
+        <v>-1443.036878842528</v>
       </c>
       <c r="Q66">
-        <v>196.1229429176092</v>
+        <v>-617.0368788425276</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.215949584105131</v>
+        <v>0.2230492139566139</v>
       </c>
       <c r="T66">
-        <v>3.316532093463354</v>
+        <v>3.454917093802851</v>
       </c>
       <c r="U66">
-        <v>0.1245366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V66">
-        <v>0.1012194032644989</v>
+        <v>0.08126139747180385</v>
       </c>
       <c r="W66">
-        <v>0.1119310946393727</v>
+        <v>0.1403250257474214</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8097552261159915</v>
+        <v>0.6500911797744308</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1692784916206388</v>
+        <v>0.2068914943597964</v>
       </c>
       <c r="C67">
-        <v>-5072.107446607519</v>
+        <v>-11259.6453499981</v>
       </c>
       <c r="D67">
-        <v>24467.1445389335</v>
+        <v>18754.34897378201</v>
       </c>
       <c r="E67">
-        <v>26155.21816163176</v>
+        <v>26629.96049987085</v>
       </c>
       <c r="F67">
-        <v>30858.25198554102</v>
+        <v>31332.99432378011</v>
       </c>
       <c r="G67">
         <v>1319</v>
@@ -6787,45 +6787,45 @@
         <v>3064</v>
       </c>
       <c r="M67">
-        <v>4713.18500439146</v>
+        <v>6477.677236404686</v>
       </c>
       <c r="N67">
-        <v>-1649.18500439146</v>
+        <v>-3413.677236404686</v>
       </c>
       <c r="O67">
-        <v>-206.1481255489325</v>
+        <v>-426.7096545505857</v>
       </c>
       <c r="P67">
-        <v>-1443.036878842528</v>
+        <v>-2986.9675818541</v>
       </c>
       <c r="Q67">
-        <v>-617.0368788425276</v>
+        <v>-2160.9675818541</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2230492139566139</v>
+        <v>0.2309201807569035</v>
       </c>
       <c r="T67">
-        <v>3.454917093802851</v>
+        <v>3.608336886963296</v>
       </c>
       <c r="U67">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.08126139747180385</v>
+        <v>0.05912613210295996</v>
       </c>
       <c r="W67">
-        <v>0.1403250257474214</v>
+        <v>0.1945130801552261</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.6500911797744308</v>
+        <v>0.4730090568236797</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2068914943597964</v>
+        <v>0.2085008605264217</v>
       </c>
       <c r="C68">
-        <v>-11259.6453499981</v>
+        <v>-11919.8975535067</v>
       </c>
       <c r="D68">
-        <v>18754.34897378201</v>
+        <v>18568.8391085125</v>
       </c>
       <c r="E68">
-        <v>26629.96049987085</v>
+        <v>27104.70283810994</v>
       </c>
       <c r="F68">
-        <v>31332.99432378011</v>
+        <v>31807.7366620192</v>
       </c>
       <c r="G68">
         <v>1319</v>
@@ -6869,37 +6869,37 @@
         <v>3064</v>
       </c>
       <c r="M68">
-        <v>6477.677236404686</v>
+        <v>6575.823861198696</v>
       </c>
       <c r="N68">
-        <v>-3413.677236404686</v>
+        <v>-3511.823861198696</v>
       </c>
       <c r="O68">
-        <v>-426.7096545505857</v>
+        <v>-438.977982649837</v>
       </c>
       <c r="P68">
-        <v>-2986.9675818541</v>
+        <v>-3072.845878548859</v>
       </c>
       <c r="Q68">
-        <v>-2160.9675818541</v>
+        <v>-2246.845878548859</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2309201807569035</v>
+        <v>0.2365298832040824</v>
       </c>
       <c r="T68">
-        <v>3.608336886963296</v>
+        <v>3.717680428992487</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.05912613210295996</v>
+        <v>0.05824365251933369</v>
       </c>
       <c r="W68">
-        <v>0.1945130801552261</v>
+        <v>0.1946955209986188</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4730090568236797</v>
+        <v>0.4659492201546694</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2085008605264217</v>
+        <v>0.2101102266930471</v>
       </c>
       <c r="C69">
-        <v>-11919.8975535067</v>
+        <v>-12576.51573731063</v>
       </c>
       <c r="D69">
-        <v>18568.8391085125</v>
+        <v>18386.96326294766</v>
       </c>
       <c r="E69">
-        <v>27104.70283810994</v>
+        <v>27579.44517634904</v>
       </c>
       <c r="F69">
-        <v>31807.7366620192</v>
+        <v>32282.4790002583</v>
       </c>
       <c r="G69">
         <v>1319</v>
@@ -6951,37 +6951,37 @@
         <v>3064</v>
       </c>
       <c r="M69">
-        <v>6575.823861198696</v>
+        <v>6673.970485992706</v>
       </c>
       <c r="N69">
-        <v>-3511.823861198696</v>
+        <v>-3609.970485992706</v>
       </c>
       <c r="O69">
-        <v>-438.977982649837</v>
+        <v>-451.2463107490883</v>
       </c>
       <c r="P69">
-        <v>-3072.845878548859</v>
+        <v>-3158.724175243618</v>
       </c>
       <c r="Q69">
-        <v>-2246.845878548859</v>
+        <v>-2332.724175243618</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2365298832040824</v>
+        <v>0.2424901920542099</v>
       </c>
       <c r="T69">
-        <v>3.717680428992487</v>
+        <v>3.833857942398502</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.05824365251933369</v>
+        <v>0.05738712821757878</v>
       </c>
       <c r="W69">
-        <v>0.1946955209986188</v>
+        <v>0.1948725959348528</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4659492201546694</v>
+        <v>0.4590970257406303</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2101102266930471</v>
+        <v>0.2117195928596725</v>
       </c>
       <c r="C70">
-        <v>-12576.51573731063</v>
+        <v>-13229.60564784277</v>
       </c>
       <c r="D70">
-        <v>18386.96326294766</v>
+        <v>18208.61569065462</v>
       </c>
       <c r="E70">
-        <v>27579.44517634904</v>
+        <v>28054.18751458813</v>
       </c>
       <c r="F70">
-        <v>32282.4790002583</v>
+        <v>32757.22133849739</v>
       </c>
       <c r="G70">
         <v>1319</v>
@@ -7033,37 +7033,37 @@
         <v>3064</v>
       </c>
       <c r="M70">
-        <v>6673.970485992706</v>
+        <v>6772.117110786718</v>
       </c>
       <c r="N70">
-        <v>-3609.970485992706</v>
+        <v>-3708.117110786718</v>
       </c>
       <c r="O70">
-        <v>-451.2463107490883</v>
+        <v>-463.5146388483397</v>
       </c>
       <c r="P70">
-        <v>-3158.724175243618</v>
+        <v>-3244.602471938378</v>
       </c>
       <c r="Q70">
-        <v>-2332.724175243618</v>
+        <v>-2418.602471938378</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2424901920542099</v>
+        <v>0.2488350369591845</v>
       </c>
       <c r="T70">
-        <v>3.833857942398502</v>
+        <v>3.957530779250066</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05738712821757878</v>
+        <v>0.05655543070717908</v>
       </c>
       <c r="W70">
-        <v>0.1948725959348528</v>
+        <v>0.1950445382642395</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4590970257406303</v>
+        <v>0.4524434456574327</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2117195928596725</v>
+        <v>0.2133289590262978</v>
       </c>
       <c r="C71">
-        <v>-13229.60564784277</v>
+        <v>-13879.26896812547</v>
       </c>
       <c r="D71">
-        <v>18208.61569065462</v>
+        <v>18033.69470861102</v>
       </c>
       <c r="E71">
-        <v>28054.18751458813</v>
+        <v>28528.92985282723</v>
       </c>
       <c r="F71">
-        <v>32757.22133849739</v>
+        <v>33231.96367673649</v>
       </c>
       <c r="G71">
         <v>1319</v>
@@ -7115,37 +7115,37 @@
         <v>3064</v>
       </c>
       <c r="M71">
-        <v>6772.117110786718</v>
+        <v>6870.263735580728</v>
       </c>
       <c r="N71">
-        <v>-3708.117110786718</v>
+        <v>-3806.263735580728</v>
       </c>
       <c r="O71">
-        <v>-463.5146388483397</v>
+        <v>-475.782966947591</v>
       </c>
       <c r="P71">
-        <v>-3244.602471938378</v>
+        <v>-3330.480768633137</v>
       </c>
       <c r="Q71">
-        <v>-2418.602471938378</v>
+        <v>-2504.480768633137</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2488350369591845</v>
+        <v>0.2556028715244906</v>
       </c>
       <c r="T71">
-        <v>3.957530779250066</v>
+        <v>4.089448471891735</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05655543070717908</v>
+        <v>0.05574749598279081</v>
       </c>
       <c r="W71">
-        <v>0.1950445382642395</v>
+        <v>0.1952115679556437</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4524434456574327</v>
+        <v>0.4459799678623264</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2133289590262978</v>
+        <v>0.2149383251929232</v>
       </c>
       <c r="C72">
-        <v>-13879.26896812547</v>
+        <v>-14525.60351108922</v>
       </c>
       <c r="D72">
-        <v>18033.69470861102</v>
+        <v>17862.10250388636</v>
       </c>
       <c r="E72">
-        <v>28528.92985282723</v>
+        <v>29003.67219106632</v>
       </c>
       <c r="F72">
-        <v>33231.96367673649</v>
+        <v>33706.70601497558</v>
       </c>
       <c r="G72">
         <v>1319</v>
@@ -7197,37 +7197,37 @@
         <v>3064</v>
       </c>
       <c r="M72">
-        <v>6870.263735580728</v>
+        <v>6968.410360374738</v>
       </c>
       <c r="N72">
-        <v>-3806.263735580728</v>
+        <v>-3904.410360374738</v>
       </c>
       <c r="O72">
-        <v>-475.782966947591</v>
+        <v>-488.0512950468423</v>
       </c>
       <c r="P72">
-        <v>-3330.480768633137</v>
+        <v>-3416.359065327896</v>
       </c>
       <c r="Q72">
-        <v>-2504.480768633137</v>
+        <v>-2590.359065327896</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2556028715244906</v>
+        <v>0.2628374533011972</v>
       </c>
       <c r="T72">
-        <v>4.089448471891735</v>
+        <v>4.230463936439727</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.05574749598279081</v>
+        <v>0.05496231998303319</v>
       </c>
       <c r="W72">
-        <v>0.1952115679556437</v>
+        <v>0.1953738925853182</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4459799678623264</v>
+        <v>0.4396985598642655</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2149383251929231</v>
+        <v>0.2165476913595484</v>
       </c>
       <c r="C73">
-        <v>-14525.6035110892</v>
+        <v>-15168.70340195848</v>
       </c>
       <c r="D73">
-        <v>17862.10250388637</v>
+        <v>17693.74495125618</v>
       </c>
       <c r="E73">
-        <v>29003.67219106631</v>
+        <v>29478.4145293054</v>
       </c>
       <c r="F73">
-        <v>33706.70601497557</v>
+        <v>34181.44835321466</v>
       </c>
       <c r="G73">
         <v>1319</v>
@@ -7279,37 +7279,37 @@
         <v>3064</v>
       </c>
       <c r="M73">
-        <v>6968.410360374737</v>
+        <v>7066.556985168747</v>
       </c>
       <c r="N73">
-        <v>-3904.410360374737</v>
+        <v>-4002.556985168747</v>
       </c>
       <c r="O73">
-        <v>-488.0512950468421</v>
+        <v>-500.3196231460934</v>
       </c>
       <c r="P73">
-        <v>-3416.359065327895</v>
+        <v>-3502.237362022654</v>
       </c>
       <c r="Q73">
-        <v>-2590.359065327895</v>
+        <v>-2676.237362022654</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2628374533011971</v>
+        <v>0.270588790919097</v>
       </c>
       <c r="T73">
-        <v>4.230463936439724</v>
+        <v>4.381551934169715</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.0549623199830332</v>
+        <v>0.0541989544277133</v>
       </c>
       <c r="W73">
-        <v>0.1953738925853182</v>
+        <v>0.1955317081975018</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4396985598642656</v>
+        <v>0.4335916354217064</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2165476913595484</v>
+        <v>0.2181570575261738</v>
       </c>
       <c r="C74">
-        <v>-15168.70340195848</v>
+        <v>-15808.65925041966</v>
       </c>
       <c r="D74">
-        <v>17693.74495125618</v>
+        <v>17528.53144103409</v>
       </c>
       <c r="E74">
-        <v>29478.4145293054</v>
+        <v>29953.15686754449</v>
       </c>
       <c r="F74">
-        <v>34181.44835321466</v>
+        <v>34656.19069145375</v>
       </c>
       <c r="G74">
         <v>1319</v>
@@ -7361,37 +7361,37 @@
         <v>3064</v>
       </c>
       <c r="M74">
-        <v>7066.556985168747</v>
+        <v>7164.703609962758</v>
       </c>
       <c r="N74">
-        <v>-4002.556985168747</v>
+        <v>-4100.703609962758</v>
       </c>
       <c r="O74">
-        <v>-500.3196231460934</v>
+        <v>-512.5879512453447</v>
       </c>
       <c r="P74">
-        <v>-3502.237362022654</v>
+        <v>-3588.115658717413</v>
       </c>
       <c r="Q74">
-        <v>-2676.237362022654</v>
+        <v>-2762.115658717413</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.270588790919097</v>
+        <v>0.2789143016938784</v>
       </c>
       <c r="T74">
-        <v>4.381551934169715</v>
+        <v>4.54383163543526</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.0541989544277133</v>
+        <v>0.05345650299719668</v>
       </c>
       <c r="W74">
-        <v>0.1955317081975018</v>
+        <v>0.195685200094283</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4335916354217064</v>
+        <v>0.4276520239775734</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2181570575261738</v>
+        <v>0.2197664236927991</v>
       </c>
       <c r="C75">
-        <v>-15808.65925041966</v>
+        <v>-16445.55831323249</v>
       </c>
       <c r="D75">
-        <v>17528.53144103409</v>
+        <v>17366.37471646037</v>
       </c>
       <c r="E75">
-        <v>29953.15686754449</v>
+        <v>30427.89920578359</v>
       </c>
       <c r="F75">
-        <v>34656.19069145375</v>
+        <v>35130.93302969285</v>
       </c>
       <c r="G75">
         <v>1319</v>
@@ -7443,37 +7443,37 @@
         <v>3064</v>
       </c>
       <c r="M75">
-        <v>7164.703609962758</v>
+        <v>7262.850234756769</v>
       </c>
       <c r="N75">
-        <v>-4100.703609962758</v>
+        <v>-4198.850234756769</v>
       </c>
       <c r="O75">
-        <v>-512.5879512453447</v>
+        <v>-524.8562793445961</v>
       </c>
       <c r="P75">
-        <v>-3588.115658717413</v>
+        <v>-3673.993955412173</v>
       </c>
       <c r="Q75">
-        <v>-2762.115658717413</v>
+        <v>-2847.993955412173</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2789143016938784</v>
+        <v>0.2878802363744122</v>
       </c>
       <c r="T75">
-        <v>4.54383163543526</v>
+        <v>4.718594390644308</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.05345650299719668</v>
+        <v>0.05273411782155887</v>
       </c>
       <c r="W75">
-        <v>0.195685200094283</v>
+        <v>0.1958345435614216</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4276520239775734</v>
+        <v>0.421872942572471</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2197664236927991</v>
+        <v>0.2213757898594245</v>
       </c>
       <c r="C76">
-        <v>-16445.55831323249</v>
+        <v>-17079.48464789834</v>
       </c>
       <c r="D76">
-        <v>17366.37471646037</v>
+        <v>17207.1907200336</v>
       </c>
       <c r="E76">
-        <v>30427.89920578359</v>
+        <v>30902.64154402268</v>
       </c>
       <c r="F76">
-        <v>35130.93302969285</v>
+        <v>35605.67536793194</v>
       </c>
       <c r="G76">
         <v>1319</v>
@@ -7525,37 +7525,37 @@
         <v>3064</v>
       </c>
       <c r="M76">
-        <v>7262.850234756769</v>
+        <v>7360.996859550779</v>
       </c>
       <c r="N76">
-        <v>-4198.850234756769</v>
+        <v>-4296.996859550779</v>
       </c>
       <c r="O76">
-        <v>-524.8562793445961</v>
+        <v>-537.1246074438474</v>
       </c>
       <c r="P76">
-        <v>-3673.993955412173</v>
+        <v>-3759.872252106932</v>
       </c>
       <c r="Q76">
-        <v>-2847.993955412173</v>
+        <v>-2933.872252106932</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2878802363744122</v>
+        <v>0.2975634458293887</v>
       </c>
       <c r="T76">
-        <v>4.718594390644308</v>
+        <v>4.907338166270081</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.05273411782155887</v>
+        <v>0.05203099625060476</v>
       </c>
       <c r="W76">
-        <v>0.1958345435614216</v>
+        <v>0.1959799045361031</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.421872942572471</v>
+        <v>0.416247970004838</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2213757898594245</v>
+        <v>0.2229851560260498</v>
       </c>
       <c r="C77">
-        <v>-17079.48464789834</v>
+        <v>-17710.51925795405</v>
       </c>
       <c r="D77">
-        <v>17207.1907200336</v>
+        <v>17050.89844821699</v>
       </c>
       <c r="E77">
-        <v>30902.64154402268</v>
+        <v>31377.38388226178</v>
       </c>
       <c r="F77">
-        <v>35605.67536793194</v>
+        <v>36080.41770617104</v>
       </c>
       <c r="G77">
         <v>1319</v>
@@ -7607,37 +7607,37 @@
         <v>3064</v>
       </c>
       <c r="M77">
-        <v>7360.996859550779</v>
+        <v>7459.14348434479</v>
       </c>
       <c r="N77">
-        <v>-4296.996859550779</v>
+        <v>-4395.14348434479</v>
       </c>
       <c r="O77">
-        <v>-537.1246074438474</v>
+        <v>-549.3929355430987</v>
       </c>
       <c r="P77">
-        <v>-3759.872252106932</v>
+        <v>-3845.750548801691</v>
       </c>
       <c r="Q77">
-        <v>-2933.872252106932</v>
+        <v>-3019.750548801691</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2975634458293887</v>
+        <v>0.3080535894056132</v>
       </c>
       <c r="T77">
-        <v>4.907338166270081</v>
+        <v>5.111810589864668</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.05203099625060476</v>
+        <v>0.05134637787888627</v>
       </c>
       <c r="W77">
-        <v>0.1959799045361031</v>
+        <v>0.1961214402219772</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.416247970004838</v>
+        <v>0.4107710230310903</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2229851560260498</v>
+        <v>0.2245945221926751</v>
       </c>
       <c r="C78">
-        <v>-17710.51925795405</v>
+        <v>-18338.74023041859</v>
       </c>
       <c r="D78">
-        <v>17050.89844821699</v>
+        <v>16897.41981399154</v>
       </c>
       <c r="E78">
-        <v>31377.38388226178</v>
+        <v>31852.12622050087</v>
       </c>
       <c r="F78">
-        <v>36080.41770617104</v>
+        <v>36555.16004441013</v>
       </c>
       <c r="G78">
         <v>1319</v>
@@ -7689,37 +7689,37 @@
         <v>3064</v>
       </c>
       <c r="M78">
-        <v>7459.14348434479</v>
+        <v>7557.290109138799</v>
       </c>
       <c r="N78">
-        <v>-4395.14348434479</v>
+        <v>-4493.290109138799</v>
       </c>
       <c r="O78">
-        <v>-549.3929355430987</v>
+        <v>-561.6612636423499</v>
       </c>
       <c r="P78">
-        <v>-3845.750548801691</v>
+        <v>-3931.62884549645</v>
       </c>
       <c r="Q78">
-        <v>-3019.750548801691</v>
+        <v>-3105.62884549645</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3080535894056132</v>
+        <v>0.3194559193797703</v>
       </c>
       <c r="T78">
-        <v>5.111810589864668</v>
+        <v>5.33406322420661</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.05134637787888627</v>
+        <v>0.05067954180253711</v>
       </c>
       <c r="W78">
-        <v>0.1961214402219772</v>
+        <v>0.1962592996562701</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4107710230310903</v>
+        <v>0.4054363344202968</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2245945221926751</v>
+        <v>0.2262038883593005</v>
       </c>
       <c r="C79">
-        <v>-18338.74023041859</v>
+        <v>-18964.22286588311</v>
       </c>
       <c r="D79">
-        <v>16897.41981399154</v>
+        <v>16746.67951676611</v>
       </c>
       <c r="E79">
-        <v>31852.12622050087</v>
+        <v>32326.86855873996</v>
       </c>
       <c r="F79">
-        <v>36555.16004441013</v>
+        <v>37029.90238264922</v>
       </c>
       <c r="G79">
         <v>1319</v>
@@ -7771,37 +7771,37 @@
         <v>3064</v>
       </c>
       <c r="M79">
-        <v>7557.290109138799</v>
+        <v>7655.436733932809</v>
       </c>
       <c r="N79">
-        <v>-4493.290109138799</v>
+        <v>-4591.436733932809</v>
       </c>
       <c r="O79">
-        <v>-561.6612636423499</v>
+        <v>-573.9295917416011</v>
       </c>
       <c r="P79">
-        <v>-3931.62884549645</v>
+        <v>-4017.507142191208</v>
       </c>
       <c r="Q79">
-        <v>-3105.62884549645</v>
+        <v>-3191.507142191208</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3194559193797703</v>
+        <v>0.3318948248061235</v>
       </c>
       <c r="T79">
-        <v>5.33406322420661</v>
+        <v>5.576520643488729</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.05067954180253711</v>
+        <v>0.05002980408711997</v>
       </c>
       <c r="W79">
-        <v>0.1962592996562701</v>
+        <v>0.1963936242332735</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4054363344202968</v>
+        <v>0.4002384326969598</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2262038883593005</v>
+        <v>0.2278132545259259</v>
       </c>
       <c r="C80">
-        <v>-18964.22286588311</v>
+        <v>-19587.03980169917</v>
       </c>
       <c r="D80">
-        <v>16746.67951676611</v>
+        <v>16598.60491918914</v>
       </c>
       <c r="E80">
-        <v>32326.86855873996</v>
+        <v>32801.61089697906</v>
       </c>
       <c r="F80">
-        <v>37029.90238264922</v>
+        <v>37504.64472088832</v>
       </c>
       <c r="G80">
         <v>1319</v>
@@ -7853,37 +7853,37 @@
         <v>3064</v>
       </c>
       <c r="M80">
-        <v>7655.436733932809</v>
+        <v>7753.583358726822</v>
       </c>
       <c r="N80">
-        <v>-4591.436733932809</v>
+        <v>-4689.583358726822</v>
       </c>
       <c r="O80">
-        <v>-573.9295917416011</v>
+        <v>-586.1979198408527</v>
       </c>
       <c r="P80">
-        <v>-4017.507142191208</v>
+        <v>-4103.385438885969</v>
       </c>
       <c r="Q80">
-        <v>-3191.507142191208</v>
+        <v>-3277.385438885969</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3318948248061235</v>
+        <v>0.3455183878921294</v>
       </c>
       <c r="T80">
-        <v>5.576520643488729</v>
+        <v>5.842069245559621</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.05002980408711997</v>
+        <v>0.04939651542778932</v>
       </c>
       <c r="W80">
-        <v>0.1963936242332735</v>
+        <v>0.1965245481880743</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4002384326969598</v>
+        <v>0.3951721234223146</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2278132545259259</v>
+        <v>0.2294226206925512</v>
       </c>
       <c r="C81">
-        <v>-19587.03980169917</v>
+        <v>-20207.26112868907</v>
       </c>
       <c r="D81">
-        <v>16598.60491918914</v>
+        <v>16453.12593043834</v>
       </c>
       <c r="E81">
-        <v>32801.61089697906</v>
+        <v>33276.35323521815</v>
       </c>
       <c r="F81">
-        <v>37504.64472088832</v>
+        <v>37979.38705912741</v>
       </c>
       <c r="G81">
         <v>1319</v>
@@ -7935,37 +7935,37 @@
         <v>3064</v>
       </c>
       <c r="M81">
-        <v>7753.583358726822</v>
+        <v>7851.729983520831</v>
       </c>
       <c r="N81">
-        <v>-4689.583358726822</v>
+        <v>-4787.729983520831</v>
       </c>
       <c r="O81">
-        <v>-586.1979198408527</v>
+        <v>-598.4662479401039</v>
       </c>
       <c r="P81">
-        <v>-4103.385438885969</v>
+        <v>-4189.263735580727</v>
       </c>
       <c r="Q81">
-        <v>-3277.385438885969</v>
+        <v>-3363.263735580727</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3455183878921294</v>
+        <v>0.3605043072867359</v>
       </c>
       <c r="T81">
-        <v>5.842069245559621</v>
+        <v>6.134172707837603</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04939651542778932</v>
+        <v>0.04877905898494196</v>
       </c>
       <c r="W81">
-        <v>0.1965245481880743</v>
+        <v>0.196652199044005</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3951721234223146</v>
+        <v>0.3902324718795357</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2294226206925512</v>
+        <v>0.2310319868591765</v>
       </c>
       <c r="C82">
-        <v>-20207.26112868907</v>
+        <v>-20824.95450177186</v>
       </c>
       <c r="D82">
-        <v>16453.12593043834</v>
+        <v>16310.17489559465</v>
       </c>
       <c r="E82">
-        <v>33276.35323521815</v>
+        <v>33751.09557345724</v>
       </c>
       <c r="F82">
-        <v>37979.38705912741</v>
+        <v>38454.1293973665</v>
       </c>
       <c r="G82">
         <v>1319</v>
@@ -8017,37 +8017,37 @@
         <v>3064</v>
       </c>
       <c r="M82">
-        <v>7851.729983520831</v>
+        <v>7949.876608314842</v>
       </c>
       <c r="N82">
-        <v>-4787.729983520831</v>
+        <v>-4885.876608314842</v>
       </c>
       <c r="O82">
-        <v>-598.4662479401039</v>
+        <v>-610.7345760393553</v>
       </c>
       <c r="P82">
-        <v>-4189.263735580727</v>
+        <v>-4275.142032275487</v>
       </c>
       <c r="Q82">
-        <v>-3363.263735580727</v>
+        <v>-3449.142032275487</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3605043072867359</v>
+        <v>0.3770676918807747</v>
       </c>
       <c r="T82">
-        <v>6.134172707837603</v>
+        <v>6.457023902986951</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04877905898494196</v>
+        <v>0.04817684838018959</v>
       </c>
       <c r="W82">
-        <v>0.196652199044005</v>
+        <v>0.1967766980269498</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3902324718795357</v>
+        <v>0.3854147870415167</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2310319868591765</v>
+        <v>0.2326413530258019</v>
       </c>
       <c r="C83">
-        <v>-20824.95450177186</v>
+        <v>-21440.18524487219</v>
       </c>
       <c r="D83">
-        <v>16310.17489559465</v>
+        <v>16169.6864907334</v>
       </c>
       <c r="E83">
-        <v>33751.09557345724</v>
+        <v>34225.83791169633</v>
       </c>
       <c r="F83">
-        <v>38454.1293973665</v>
+        <v>38928.87173560559</v>
       </c>
       <c r="G83">
         <v>1319</v>
@@ -8099,37 +8099,37 @@
         <v>3064</v>
       </c>
       <c r="M83">
-        <v>7949.876608314842</v>
+        <v>8048.023233108852</v>
       </c>
       <c r="N83">
-        <v>-4885.876608314842</v>
+        <v>-4984.023233108852</v>
       </c>
       <c r="O83">
-        <v>-610.7345760393553</v>
+        <v>-623.0029041386065</v>
       </c>
       <c r="P83">
-        <v>-4275.142032275487</v>
+        <v>-4361.020328970246</v>
       </c>
       <c r="Q83">
-        <v>-3449.142032275487</v>
+        <v>-3535.020328970246</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3770676918807747</v>
+        <v>0.3954714525408177</v>
       </c>
       <c r="T83">
-        <v>6.457023902986951</v>
+        <v>6.815747453152893</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04817684838018959</v>
+        <v>0.04758932583896777</v>
       </c>
       <c r="W83">
-        <v>0.1967766980269498</v>
+        <v>0.196898160449335</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3854147870415167</v>
+        <v>0.3807146067117422</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2326413530258019</v>
+        <v>0.2342507191924272</v>
       </c>
       <c r="C84">
-        <v>-21440.18524487219</v>
+        <v>-22053.01645045359</v>
       </c>
       <c r="D84">
-        <v>16169.6864907334</v>
+        <v>16031.59762339109</v>
       </c>
       <c r="E84">
-        <v>34225.83791169633</v>
+        <v>34700.58024993542</v>
       </c>
       <c r="F84">
-        <v>38928.87173560559</v>
+        <v>39403.61407384468</v>
       </c>
       <c r="G84">
         <v>1319</v>
@@ -8181,37 +8181,37 @@
         <v>3064</v>
       </c>
       <c r="M84">
-        <v>8048.023233108852</v>
+        <v>8146.169857902862</v>
       </c>
       <c r="N84">
-        <v>-4984.023233108852</v>
+        <v>-5082.169857902862</v>
       </c>
       <c r="O84">
-        <v>-623.0029041386065</v>
+        <v>-635.2712322378577</v>
       </c>
       <c r="P84">
-        <v>-4361.020328970246</v>
+        <v>-4446.898625665004</v>
       </c>
       <c r="Q84">
-        <v>-3535.020328970246</v>
+        <v>-3620.898625665004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3954714525408177</v>
+        <v>0.416040361513807</v>
       </c>
       <c r="T84">
-        <v>6.815747453152893</v>
+        <v>7.216673773926592</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04758932583896777</v>
+        <v>0.04701596046741394</v>
       </c>
       <c r="W84">
-        <v>0.196898160449335</v>
+        <v>0.1970166960663615</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3807146067117422</v>
+        <v>0.3761276837393115</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2342507191924272</v>
+        <v>0.2358600853590526</v>
       </c>
       <c r="C85">
-        <v>-22053.01645045359</v>
+        <v>-22663.5090739948</v>
       </c>
       <c r="D85">
-        <v>16031.59762339109</v>
+        <v>15895.84733808897</v>
       </c>
       <c r="E85">
-        <v>34700.58024993542</v>
+        <v>35175.32258817452</v>
       </c>
       <c r="F85">
-        <v>39403.61407384468</v>
+        <v>39878.35641208378</v>
       </c>
       <c r="G85">
         <v>1319</v>
@@ -8263,37 +8263,37 @@
         <v>3064</v>
       </c>
       <c r="M85">
-        <v>8146.169857902862</v>
+        <v>8244.316482696871</v>
       </c>
       <c r="N85">
-        <v>-5082.169857902862</v>
+        <v>-5180.316482696871</v>
       </c>
       <c r="O85">
-        <v>-635.2712322378577</v>
+        <v>-647.5395603371089</v>
       </c>
       <c r="P85">
-        <v>-4446.898625665004</v>
+        <v>-4532.776922359762</v>
       </c>
       <c r="Q85">
-        <v>-3620.898625665004</v>
+        <v>-3706.776922359762</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.416040361513807</v>
+        <v>0.43918038410842</v>
       </c>
       <c r="T85">
-        <v>7.216673773926592</v>
+        <v>7.667715884797006</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04701596046741394</v>
+        <v>0.04645624665232569</v>
       </c>
       <c r="W85">
-        <v>0.1970166960663615</v>
+        <v>0.1971324094067921</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3761276837393115</v>
+        <v>0.3716499732186055</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2358600853590526</v>
+        <v>0.2374694515256779</v>
       </c>
       <c r="C86">
-        <v>-22663.5090739948</v>
+        <v>-23271.72202370656</v>
       </c>
       <c r="D86">
-        <v>15895.84733808897</v>
+        <v>15762.37672661631</v>
       </c>
       <c r="E86">
-        <v>35175.32258817452</v>
+        <v>35650.06492641361</v>
       </c>
       <c r="F86">
-        <v>39878.35641208378</v>
+        <v>40353.09875032287</v>
       </c>
       <c r="G86">
         <v>1319</v>
@@ -8345,37 +8345,37 @@
         <v>3064</v>
       </c>
       <c r="M86">
-        <v>8244.316482696871</v>
+        <v>8342.463107490883</v>
       </c>
       <c r="N86">
-        <v>-5180.316482696871</v>
+        <v>-5278.463107490883</v>
       </c>
       <c r="O86">
-        <v>-647.5395603371089</v>
+        <v>-659.8078884363604</v>
       </c>
       <c r="P86">
-        <v>-4532.776922359762</v>
+        <v>-4618.655219054523</v>
       </c>
       <c r="Q86">
-        <v>-3706.776922359762</v>
+        <v>-3792.655219054523</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4391803841084198</v>
+        <v>0.4654057430489812</v>
       </c>
       <c r="T86">
-        <v>7.667715884797001</v>
+        <v>8.178896943783469</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04645624665232569</v>
+        <v>0.04590970257406302</v>
       </c>
       <c r="W86">
-        <v>0.1971324094067921</v>
+        <v>0.1972454000803891</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3716499732186055</v>
+        <v>0.3672776205925042</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2374694515256779</v>
+        <v>0.2390788176923033</v>
       </c>
       <c r="C87">
-        <v>-23271.72202370656</v>
+        <v>-23877.71224576603</v>
       </c>
       <c r="D87">
-        <v>15762.37672661631</v>
+        <v>15631.12884279593</v>
       </c>
       <c r="E87">
-        <v>35650.06492641361</v>
+        <v>36124.8072646527</v>
       </c>
       <c r="F87">
-        <v>40353.09875032287</v>
+        <v>40827.84108856196</v>
       </c>
       <c r="G87">
         <v>1319</v>
@@ -8427,37 +8427,37 @@
         <v>3064</v>
       </c>
       <c r="M87">
-        <v>8342.463107490883</v>
+        <v>8440.609732284893</v>
       </c>
       <c r="N87">
-        <v>-5278.463107490883</v>
+        <v>-5376.609732284893</v>
       </c>
       <c r="O87">
-        <v>-659.8078884363604</v>
+        <v>-672.0762165356116</v>
       </c>
       <c r="P87">
-        <v>-4618.655219054523</v>
+        <v>-4704.533515749281</v>
       </c>
       <c r="Q87">
-        <v>-3792.655219054523</v>
+        <v>-3878.533515749281</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4654057430489812</v>
+        <v>0.4953775818381941</v>
       </c>
       <c r="T87">
-        <v>8.178896943783469</v>
+        <v>8.763103868339432</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04590970257406302</v>
+        <v>0.04537586882320183</v>
       </c>
       <c r="W87">
-        <v>0.1972454000803891</v>
+        <v>0.1973557630639024</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3672776205925042</v>
+        <v>0.3630069505856146</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2390788176923033</v>
+        <v>0.2406881838589285</v>
       </c>
       <c r="C88">
-        <v>-23877.71224576603</v>
+        <v>-24481.53480532816</v>
       </c>
       <c r="D88">
-        <v>15631.12884279593</v>
+        <v>15502.04862147289</v>
       </c>
       <c r="E88">
-        <v>36124.8072646527</v>
+        <v>36599.54960289179</v>
       </c>
       <c r="F88">
-        <v>40827.84108856196</v>
+        <v>41302.58342680105</v>
       </c>
       <c r="G88">
         <v>1319</v>
@@ -8509,37 +8509,37 @@
         <v>3064</v>
       </c>
       <c r="M88">
-        <v>8440.609732284893</v>
+        <v>8538.756357078903</v>
       </c>
       <c r="N88">
-        <v>-5376.609732284893</v>
+        <v>-5474.756357078903</v>
       </c>
       <c r="O88">
-        <v>-672.0762165356116</v>
+        <v>-684.3445446348628</v>
       </c>
       <c r="P88">
-        <v>-4704.533515749281</v>
+        <v>-4790.411812444039</v>
       </c>
       <c r="Q88">
-        <v>-3878.533515749281</v>
+        <v>-3964.411812444039</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4953775818381941</v>
+        <v>0.5299604727488243</v>
       </c>
       <c r="T88">
-        <v>8.763103868339432</v>
+        <v>9.437188781288617</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04537586882320183</v>
+        <v>0.04485430711259032</v>
       </c>
       <c r="W88">
-        <v>0.1973557630639024</v>
+        <v>0.1974635889673349</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3630069505856146</v>
+        <v>0.3588344569007226</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2406881838589285</v>
+        <v>0.2422975500255539</v>
       </c>
       <c r="C89">
-        <v>-24481.53480532816</v>
+        <v>-25083.24296355603</v>
       </c>
       <c r="D89">
-        <v>15502.04862147289</v>
+        <v>15375.08280148412</v>
       </c>
       <c r="E89">
-        <v>36599.54960289179</v>
+        <v>37074.29194113088</v>
       </c>
       <c r="F89">
-        <v>41302.58342680105</v>
+        <v>41777.32576504014</v>
       </c>
       <c r="G89">
         <v>1319</v>
@@ -8591,37 +8591,37 @@
         <v>3064</v>
       </c>
       <c r="M89">
-        <v>8538.756357078903</v>
+        <v>8636.902981872912</v>
       </c>
       <c r="N89">
-        <v>-5474.756357078903</v>
+        <v>-5572.902981872912</v>
       </c>
       <c r="O89">
-        <v>-684.3445446348628</v>
+        <v>-696.612872734114</v>
       </c>
       <c r="P89">
-        <v>-4790.411812444039</v>
+        <v>-4876.290109138798</v>
       </c>
       <c r="Q89">
-        <v>-3964.411812444039</v>
+        <v>-4050.290109138798</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5299604727488243</v>
+        <v>0.5703071788112264</v>
       </c>
       <c r="T89">
-        <v>9.437188781288617</v>
+        <v>10.22362117972934</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04485430711259032</v>
+        <v>0.04434459907721998</v>
       </c>
       <c r="W89">
-        <v>0.1974635889673349</v>
+        <v>0.1975689642820531</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3588344569007226</v>
+        <v>0.3547567926177598</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2422975500255539</v>
+        <v>0.2439069161921792</v>
       </c>
       <c r="C90">
-        <v>-25083.24296355603</v>
+        <v>-25682.88825089645</v>
       </c>
       <c r="D90">
-        <v>15375.08280148412</v>
+        <v>15250.17985238279</v>
       </c>
       <c r="E90">
-        <v>37074.29194113088</v>
+        <v>37549.03427936998</v>
       </c>
       <c r="F90">
-        <v>41777.32576504014</v>
+        <v>42252.06810327924</v>
       </c>
       <c r="G90">
         <v>1319</v>
@@ -8673,37 +8673,37 @@
         <v>3064</v>
       </c>
       <c r="M90">
-        <v>8636.902981872912</v>
+        <v>8735.049606666924</v>
       </c>
       <c r="N90">
-        <v>-5572.902981872912</v>
+        <v>-5671.049606666924</v>
       </c>
       <c r="O90">
-        <v>-696.612872734114</v>
+        <v>-708.8812008333655</v>
       </c>
       <c r="P90">
-        <v>-4876.290109138798</v>
+        <v>-4962.168405833559</v>
       </c>
       <c r="Q90">
-        <v>-4050.290109138798</v>
+        <v>-4136.168405833559</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5703071788112264</v>
+        <v>0.6179896496122471</v>
       </c>
       <c r="T90">
-        <v>10.22362117972934</v>
+        <v>11.15304128697746</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04434459907721998</v>
+        <v>0.04384634515500401</v>
       </c>
       <c r="W90">
-        <v>0.1975689642820531</v>
+        <v>0.1976719716121709</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3547567926177598</v>
+        <v>0.3507707612400321</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2439069161921792</v>
+        <v>0.2455162823588046</v>
       </c>
       <c r="C91">
-        <v>-25682.88825089645</v>
+        <v>-26280.52053681283</v>
       </c>
       <c r="D91">
-        <v>15250.17985238279</v>
+        <v>15127.2899047055</v>
       </c>
       <c r="E91">
-        <v>37549.03427936998</v>
+        <v>38023.77661760907</v>
       </c>
       <c r="F91">
-        <v>42252.06810327924</v>
+        <v>42726.81044151833</v>
       </c>
       <c r="G91">
         <v>1319</v>
@@ -8755,37 +8755,37 @@
         <v>3064</v>
       </c>
       <c r="M91">
-        <v>8735.049606666924</v>
+        <v>8833.196231460935</v>
       </c>
       <c r="N91">
-        <v>-5671.049606666924</v>
+        <v>-5769.196231460935</v>
       </c>
       <c r="O91">
-        <v>-708.8812008333655</v>
+        <v>-721.1495289326169</v>
       </c>
       <c r="P91">
-        <v>-4962.168405833559</v>
+        <v>-5048.046702528319</v>
       </c>
       <c r="Q91">
-        <v>-4136.168405833559</v>
+        <v>-4222.046702528319</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6179896496122471</v>
+        <v>0.6752086145734718</v>
       </c>
       <c r="T91">
-        <v>11.15304128697746</v>
+        <v>12.26834541567521</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04384634515500401</v>
+        <v>0.04335916354217063</v>
       </c>
       <c r="W91">
-        <v>0.1976719716121709</v>
+        <v>0.1977726898905083</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3507707612400321</v>
+        <v>0.3468733083373651</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2455162823588046</v>
+        <v>0.24712564852543</v>
       </c>
       <c r="C92">
-        <v>-26280.52053681283</v>
+        <v>-26876.18809617342</v>
       </c>
       <c r="D92">
-        <v>15127.2899047055</v>
+        <v>15006.364683584</v>
       </c>
       <c r="E92">
-        <v>38023.77661760907</v>
+        <v>38498.51895584817</v>
       </c>
       <c r="F92">
-        <v>42726.81044151833</v>
+        <v>43201.55277975743</v>
       </c>
       <c r="G92">
         <v>1319</v>
@@ -8837,37 +8837,37 @@
         <v>3064</v>
       </c>
       <c r="M92">
-        <v>8833.196231460935</v>
+        <v>8931.342856254945</v>
       </c>
       <c r="N92">
-        <v>-5769.196231460935</v>
+        <v>-5867.342856254945</v>
       </c>
       <c r="O92">
-        <v>-721.1495289326169</v>
+        <v>-733.4178570318682</v>
       </c>
       <c r="P92">
-        <v>-5048.046702528319</v>
+        <v>-5133.924999223077</v>
       </c>
       <c r="Q92">
-        <v>-4222.046702528319</v>
+        <v>-4307.924999223077</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6752086145734718</v>
+        <v>0.7451429050816354</v>
       </c>
       <c r="T92">
-        <v>12.26834541567521</v>
+        <v>13.63149490630579</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04335916354217063</v>
+        <v>0.0428826892175314</v>
       </c>
       <c r="W92">
-        <v>0.1977726898905083</v>
+        <v>0.1978711945803107</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3468733083373651</v>
+        <v>0.3430615137402512</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.24712564852543</v>
+        <v>0.2487350146920553</v>
       </c>
       <c r="C93">
-        <v>-26876.18809617342</v>
+        <v>-27469.93767248057</v>
       </c>
       <c r="D93">
-        <v>15006.364683584</v>
+        <v>14887.35744551595</v>
       </c>
       <c r="E93">
-        <v>38498.51895584817</v>
+        <v>38973.26129408726</v>
       </c>
       <c r="F93">
-        <v>43201.55277975743</v>
+        <v>43676.29511799652</v>
       </c>
       <c r="G93">
         <v>1319</v>
@@ -8919,37 +8919,37 @@
         <v>3064</v>
       </c>
       <c r="M93">
-        <v>8931.342856254945</v>
+        <v>9029.489481048955</v>
       </c>
       <c r="N93">
-        <v>-5867.342856254945</v>
+        <v>-5965.489481048955</v>
       </c>
       <c r="O93">
-        <v>-733.4178570318682</v>
+        <v>-745.6861851311194</v>
       </c>
       <c r="P93">
-        <v>-5133.924999223077</v>
+        <v>-5219.803295917835</v>
       </c>
       <c r="Q93">
-        <v>-4307.924999223077</v>
+        <v>-4393.803295917835</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7451429050816354</v>
+        <v>0.8325607682168401</v>
       </c>
       <c r="T93">
-        <v>13.63149490630579</v>
+        <v>15.33543176959401</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.0428826892175314</v>
+        <v>0.04241657303038432</v>
       </c>
       <c r="W93">
-        <v>0.1978711945803107</v>
+        <v>0.1979675578638131</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3430615137402512</v>
+        <v>0.3393325842430746</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2487350146920553</v>
+        <v>0.2503443808586806</v>
       </c>
       <c r="C94">
-        <v>-27469.93767248057</v>
+        <v>-28061.81453811508</v>
       </c>
       <c r="D94">
-        <v>14887.35744551595</v>
+        <v>14770.22291812052</v>
       </c>
       <c r="E94">
-        <v>38973.26129408726</v>
+        <v>39448.00363232635</v>
       </c>
       <c r="F94">
-        <v>43676.29511799652</v>
+        <v>44151.03745623561</v>
       </c>
       <c r="G94">
         <v>1319</v>
@@ -9001,37 +9001,37 @@
         <v>3064</v>
       </c>
       <c r="M94">
-        <v>9029.489481048955</v>
+        <v>9127.636105842965</v>
       </c>
       <c r="N94">
-        <v>-5965.489481048955</v>
+        <v>-6063.636105842965</v>
       </c>
       <c r="O94">
-        <v>-745.6861851311194</v>
+        <v>-757.9545132303706</v>
       </c>
       <c r="P94">
-        <v>-5219.803295917835</v>
+        <v>-5305.681592612595</v>
       </c>
       <c r="Q94">
-        <v>-4393.803295917835</v>
+        <v>-4479.681592612595</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8325607682168401</v>
+        <v>0.9449551636763888</v>
       </c>
       <c r="T94">
-        <v>15.33543176959401</v>
+        <v>17.52620773667887</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.04241657303038432</v>
+        <v>0.04196048084726191</v>
       </c>
       <c r="W94">
-        <v>0.1979675578638131</v>
+        <v>0.1980618488186381</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3393325842430746</v>
+        <v>0.3356838467780953</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2503443808586806</v>
+        <v>0.2519537470253059</v>
       </c>
       <c r="C95">
-        <v>-28061.81453811508</v>
+        <v>-28651.86255175876</v>
       </c>
       <c r="D95">
-        <v>14770.22291812052</v>
+        <v>14654.91724271595</v>
       </c>
       <c r="E95">
-        <v>39448.00363232635</v>
+        <v>39922.74597056545</v>
       </c>
       <c r="F95">
-        <v>44151.03745623561</v>
+        <v>44625.77979447471</v>
       </c>
       <c r="G95">
         <v>1319</v>
@@ -9083,37 +9083,37 @@
         <v>3064</v>
       </c>
       <c r="M95">
-        <v>9127.636105842965</v>
+        <v>9225.782730636976</v>
       </c>
       <c r="N95">
-        <v>-6063.636105842965</v>
+        <v>-6161.782730636976</v>
       </c>
       <c r="O95">
-        <v>-757.9545132303706</v>
+        <v>-770.222841329622</v>
       </c>
       <c r="P95">
-        <v>-5305.681592612595</v>
+        <v>-5391.559889307355</v>
       </c>
       <c r="Q95">
-        <v>-4479.681592612595</v>
+        <v>-4565.559889307355</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9449551636763888</v>
+        <v>1.094814357622454</v>
       </c>
       <c r="T95">
-        <v>17.52620773667887</v>
+        <v>20.44724235945869</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.04196048084726191</v>
+        <v>0.0415140927531421</v>
       </c>
       <c r="W95">
-        <v>0.1980618488186381</v>
+        <v>0.1981541335829349</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3356838467780953</v>
+        <v>0.3321127420251367</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2519537470253059</v>
+        <v>0.2535631131919314</v>
       </c>
       <c r="C96">
-        <v>-28651.86255175876</v>
+        <v>-29240.12421314803</v>
       </c>
       <c r="D96">
-        <v>14654.91724271595</v>
+        <v>14541.39791956577</v>
       </c>
       <c r="E96">
-        <v>39922.74597056545</v>
+        <v>40397.48830880454</v>
       </c>
       <c r="F96">
-        <v>44625.77979447471</v>
+        <v>45100.5221327138</v>
       </c>
       <c r="G96">
         <v>1319</v>
@@ -9165,37 +9165,37 @@
         <v>3064</v>
       </c>
       <c r="M96">
-        <v>9225.782730636976</v>
+        <v>9323.929355430988</v>
       </c>
       <c r="N96">
-        <v>-6161.782730636976</v>
+        <v>-6259.929355430988</v>
       </c>
       <c r="O96">
-        <v>-770.222841329622</v>
+        <v>-782.4911694288735</v>
       </c>
       <c r="P96">
-        <v>-5391.559889307355</v>
+        <v>-5477.438186002115</v>
       </c>
       <c r="Q96">
-        <v>-4565.559889307355</v>
+        <v>-4651.438186002115</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.094814357622454</v>
+        <v>1.304617229146946</v>
       </c>
       <c r="T96">
-        <v>20.44724235945869</v>
+        <v>24.53669083135044</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.0415140927531421</v>
+        <v>0.04107710230310901</v>
       </c>
       <c r="W96">
-        <v>0.1981541335829349</v>
+        <v>0.1982444755100886</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3321127420251367</v>
+        <v>0.3286168184248721</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2535631131919314</v>
+        <v>0.2551724793585566</v>
       </c>
       <c r="C97">
-        <v>-29240.12421314803</v>
+        <v>-29826.64071530246</v>
       </c>
       <c r="D97">
-        <v>14541.39791956577</v>
+        <v>14429.62375565043</v>
       </c>
       <c r="E97">
-        <v>40397.48830880454</v>
+        <v>40872.23064704363</v>
       </c>
       <c r="F97">
-        <v>45100.5221327138</v>
+        <v>45575.26447095289</v>
       </c>
       <c r="G97">
         <v>1319</v>
@@ -9247,37 +9247,37 @@
         <v>3064</v>
       </c>
       <c r="M97">
-        <v>9323.929355430988</v>
+        <v>9422.075980224998</v>
       </c>
       <c r="N97">
-        <v>-6259.929355430988</v>
+        <v>-6358.075980224998</v>
       </c>
       <c r="O97">
-        <v>-782.4911694288735</v>
+        <v>-794.7594975281247</v>
       </c>
       <c r="P97">
-        <v>-5477.438186002115</v>
+        <v>-5563.316482696873</v>
       </c>
       <c r="Q97">
-        <v>-4651.438186002115</v>
+        <v>-4737.316482696873</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.304617229146946</v>
+        <v>1.619321536433682</v>
       </c>
       <c r="T97">
-        <v>24.53669083135044</v>
+        <v>30.67086353918806</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.04107710230310901</v>
+        <v>0.04064921582078497</v>
       </c>
       <c r="W97">
-        <v>0.1982444755100886</v>
+        <v>0.1983329353137599</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3286168184248721</v>
+        <v>0.3251937265662798</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2551724793585566</v>
+        <v>0.256781845525182</v>
       </c>
       <c r="C98">
-        <v>-29826.64071530246</v>
+        <v>-30411.45199436283</v>
       </c>
       <c r="D98">
-        <v>14429.62375565043</v>
+        <v>14319.55481482914</v>
       </c>
       <c r="E98">
-        <v>40872.23064704362</v>
+        <v>41346.97298528271</v>
       </c>
       <c r="F98">
-        <v>45575.26447095288</v>
+        <v>46050.00680919197</v>
       </c>
       <c r="G98">
         <v>1319</v>
@@ -9329,37 +9329,37 @@
         <v>3064</v>
       </c>
       <c r="M98">
-        <v>9422.075980224996</v>
+        <v>9520.222605019006</v>
       </c>
       <c r="N98">
-        <v>-6358.075980224996</v>
+        <v>-6456.222605019006</v>
       </c>
       <c r="O98">
-        <v>-794.7594975281245</v>
+        <v>-807.0278256273757</v>
       </c>
       <c r="P98">
-        <v>-5563.316482696871</v>
+        <v>-5649.19477939163</v>
       </c>
       <c r="Q98">
-        <v>-4737.316482696871</v>
+        <v>-4823.19477939163</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.619321536433678</v>
+        <v>2.143828715244904</v>
       </c>
       <c r="T98">
-        <v>30.67086353918798</v>
+        <v>40.89448471891731</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.04064921582078498</v>
+        <v>0.04023015174015833</v>
       </c>
       <c r="W98">
-        <v>0.1983329353137599</v>
+        <v>0.1984195712039534</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3251937265662798</v>
+        <v>0.3218412139212666</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.256781845525182</v>
+        <v>0.2583912116918073</v>
       </c>
       <c r="C99">
-        <v>-30411.45199436283</v>
+        <v>-30994.5967771655</v>
       </c>
       <c r="D99">
-        <v>14319.55481482914</v>
+        <v>14211.15237026558</v>
       </c>
       <c r="E99">
-        <v>41346.97298528271</v>
+        <v>41821.71532352181</v>
       </c>
       <c r="F99">
-        <v>46050.00680919197</v>
+        <v>46524.74914743107</v>
       </c>
       <c r="G99">
         <v>1319</v>
@@ -9411,37 +9411,37 @@
         <v>3064</v>
       </c>
       <c r="M99">
-        <v>9520.222605019006</v>
+        <v>9618.369229813017</v>
       </c>
       <c r="N99">
-        <v>-6456.222605019006</v>
+        <v>-6554.369229813017</v>
       </c>
       <c r="O99">
-        <v>-807.0278256273757</v>
+        <v>-819.2961537266272</v>
       </c>
       <c r="P99">
-        <v>-5649.19477939163</v>
+        <v>-5735.07307608639</v>
       </c>
       <c r="Q99">
-        <v>-4823.19477939163</v>
+        <v>-4909.07307608639</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.143828715244904</v>
+        <v>3.192843072867356</v>
       </c>
       <c r="T99">
-        <v>40.89448471891731</v>
+        <v>61.34172707837596</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.04023015174015833</v>
+        <v>0.03981963998770773</v>
       </c>
       <c r="W99">
-        <v>0.1984195712039534</v>
+        <v>0.1985044390147552</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3218412139212666</v>
+        <v>0.3185571199016618</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2583912116918073</v>
+        <v>0.2600005778584327</v>
       </c>
       <c r="C100">
-        <v>-30994.5967771655</v>
+        <v>-31576.11262667205</v>
       </c>
       <c r="D100">
-        <v>14211.15237026558</v>
+        <v>14104.37885899812</v>
       </c>
       <c r="E100">
-        <v>41821.71532352181</v>
+        <v>42296.45766176091</v>
       </c>
       <c r="F100">
-        <v>46524.74914743107</v>
+        <v>46999.49148567017</v>
       </c>
       <c r="G100">
         <v>1319</v>
@@ -9493,37 +9493,37 @@
         <v>3064</v>
       </c>
       <c r="M100">
-        <v>9618.369229813017</v>
+        <v>9716.515854607029</v>
       </c>
       <c r="N100">
-        <v>-6554.369229813017</v>
+        <v>-6652.515854607029</v>
       </c>
       <c r="O100">
-        <v>-819.2961537266272</v>
+        <v>-831.5644818258786</v>
       </c>
       <c r="P100">
-        <v>-5735.07307608639</v>
+        <v>-5820.95137278115</v>
       </c>
       <c r="Q100">
-        <v>-4909.07307608639</v>
+        <v>-4994.95137278115</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.192843072867356</v>
+        <v>6.339886145734711</v>
       </c>
       <c r="T100">
-        <v>61.34172707837596</v>
+        <v>122.6834541567519</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03981963998770773</v>
+        <v>0.0394174214019733</v>
       </c>
       <c r="W100">
-        <v>0.1985044390147552</v>
+        <v>0.1985875923243288</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3185571199016618</v>
+        <v>0.3153393712157864</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2600005778584327</v>
-      </c>
-      <c r="C101">
-        <v>-31576.11262667205</v>
-      </c>
-      <c r="D101">
-        <v>14104.37885899812</v>
-      </c>
-      <c r="E101">
-        <v>42296.45766176091</v>
-      </c>
-      <c r="F101">
-        <v>46999.49148567017</v>
-      </c>
-      <c r="G101">
-        <v>1319</v>
-      </c>
-      <c r="H101">
-        <v>42771.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3890</v>
-      </c>
-      <c r="K101">
-        <v>826</v>
-      </c>
-      <c r="L101">
-        <v>3064</v>
-      </c>
-      <c r="M101">
-        <v>9716.515854607029</v>
-      </c>
-      <c r="N101">
-        <v>-6652.515854607029</v>
-      </c>
-      <c r="O101">
-        <v>-831.5644818258786</v>
-      </c>
-      <c r="P101">
-        <v>-5820.95137278115</v>
-      </c>
-      <c r="Q101">
-        <v>-4994.95137278115</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.339886145734711</v>
-      </c>
-      <c r="T101">
-        <v>122.6834541567519</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.0394174214019733</v>
-      </c>
-      <c r="W101">
-        <v>0.1985875923243288</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3153393712157864</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
